--- a/scraper_terrenos/terrenos_final.xlsx
+++ b/scraper_terrenos/terrenos_final.xlsx
@@ -466,7 +466,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>https://terreno.mercadolibre.com.mx/MLM-3835159420-lotes-de-terreno-desde-104-m2-en-venta-cerca-del-aeropuerto-de-toluca-en-la-constitucion-toltepec-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=1&amp;type=item&amp;tracking_id=52b27256-ef9e-4304-a16d-deed8b69cffe&amp;price_drop=not_apply</t>
+          <t>https://terreno.mercadolibre.com.mx/MLM-3835159420-lotes-de-terreno-desde-104-m2-en-venta-cerca-del-aeropuerto-de-toluca-en-la-constitucion-toltepec-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=1&amp;type=item&amp;tracking_id=6da87cc9-ea4e-43ef-accd-6e90e2809fd5&amp;price_drop=not_apply</t>
         </is>
       </c>
     </row>
@@ -486,7 +486,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>https://terreno.mercadolibre.com.mx/MLM-2810992285-construye-tu-residencia-en-la-zona-de-mayor-proyeccion-de-toluca-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=2&amp;type=item&amp;float_highlight=recent_publication&amp;tracking_id=52b27256-ef9e-4304-a16d-deed8b69cffe&amp;price_drop=not_apply</t>
+          <t>https://terreno.mercadolibre.com.mx/MLM-2810992285-construye-tu-residencia-en-la-zona-de-mayor-proyeccion-de-toluca-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=2&amp;type=item&amp;float_highlight=recent_publication&amp;tracking_id=6da87cc9-ea4e-43ef-accd-6e90e2809fd5&amp;price_drop=not_apply</t>
         </is>
       </c>
     </row>
@@ -506,7 +506,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>https://terreno.mercadolibre.com.mx/MLM-3847495816-el-mejor-terreno-del-condominio-puede-ser-tuyo-a-un-precio-de-oportunidad-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=3&amp;type=item&amp;tracking_id=52b27256-ef9e-4304-a16d-deed8b69cffe&amp;price_drop=not_apply</t>
+          <t>https://terreno.mercadolibre.com.mx/MLM-3847495816-el-mejor-terreno-del-condominio-puede-ser-tuyo-a-un-precio-de-oportunidad-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=3&amp;type=item&amp;tracking_id=6da87cc9-ea4e-43ef-accd-6e90e2809fd5&amp;price_drop=not_apply</t>
         </is>
       </c>
     </row>
@@ -517,7 +517,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>7600000</v>
+        <v>649000</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -526,7 +526,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>https://terreno.mercadolibre.com.mx/MLM-2231593183-terreno-en-venta-en-san-mateo-oxtotitlan-toluca-mexico-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=4&amp;type=item&amp;tracking_id=52b27256-ef9e-4304-a16d-deed8b69cffe&amp;price_drop=not_apply</t>
+          <t>https://terreno.mercadolibre.com.mx/MLM-2753915589-terreno-bardeado-en-cacalomacan-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=4&amp;type=item&amp;tracking_id=6da87cc9-ea4e-43ef-accd-6e90e2809fd5&amp;price_drop=false</t>
         </is>
       </c>
     </row>
@@ -537,7 +537,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>649000</v>
+        <v>7600000</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -546,7 +546,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>https://terreno.mercadolibre.com.mx/MLM-2753915589-terreno-bardeado-en-cacalomacan-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=5&amp;type=item&amp;tracking_id=52b27256-ef9e-4304-a16d-deed8b69cffe&amp;price_drop=false</t>
+          <t>https://terreno.mercadolibre.com.mx/MLM-2231593183-terreno-en-venta-en-san-mateo-oxtotitlan-toluca-mexico-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=5&amp;type=item&amp;tracking_id=6da87cc9-ea4e-43ef-accd-6e90e2809fd5&amp;price_drop=not_apply</t>
         </is>
       </c>
     </row>
@@ -566,7 +566,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>https://terreno.mercadolibre.com.mx/MLM-2716356593-terreno-en-venta-en-colonia-nueva-santa-maria-de-las-rosas-toluca-estado-de-mexico-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=6&amp;type=item&amp;tracking_id=52b27256-ef9e-4304-a16d-deed8b69cffe&amp;price_drop=not_apply</t>
+          <t>https://terreno.mercadolibre.com.mx/MLM-2716356593-terreno-en-venta-en-colonia-nueva-santa-maria-de-las-rosas-toluca-estado-de-mexico-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=6&amp;type=item&amp;tracking_id=6da87cc9-ea4e-43ef-accd-6e90e2809fd5&amp;price_drop=not_apply</t>
         </is>
       </c>
     </row>
@@ -586,7 +586,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>https://terreno.mercadolibre.com.mx/MLM-4660497978-terreno-en-venta-en-toluca-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=7&amp;type=item&amp;tracking_id=52b27256-ef9e-4304-a16d-deed8b69cffe&amp;price_drop=not_apply</t>
+          <t>https://terreno.mercadolibre.com.mx/MLM-4660497978-terreno-en-venta-en-toluca-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=7&amp;type=item&amp;tracking_id=6da87cc9-ea4e-43ef-accd-6e90e2809fd5&amp;price_drop=not_apply</t>
         </is>
       </c>
     </row>
@@ -606,7 +606,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>https://terreno.mercadolibre.com.mx/MLM-4388186170-terreno-industrial-en-venta-en-toluca-san-cayetano-a-un-lado-de-la-caseta-el-dorado-cerca-puerta-mexico-recinto-aduanal-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=8&amp;type=item&amp;tracking_id=52b27256-ef9e-4304-a16d-deed8b69cffe&amp;price_drop=not_apply</t>
+          <t>https://terreno.mercadolibre.com.mx/MLM-4388186170-terreno-industrial-en-venta-en-toluca-san-cayetano-a-un-lado-de-la-caseta-el-dorado-cerca-puerta-mexico-recinto-aduanal-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=8&amp;type=item&amp;tracking_id=6da87cc9-ea4e-43ef-accd-6e90e2809fd5&amp;price_drop=not_apply</t>
         </is>
       </c>
     </row>
@@ -626,7 +626,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>https://terreno.mercadolibre.com.mx/MLM-2716629645-terreno-industrial-en-venta-en-palmillas-son-13-hectareas-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=9&amp;type=item&amp;tracking_id=52b27256-ef9e-4304-a16d-deed8b69cffe&amp;price_drop=not_apply</t>
+          <t>https://terreno.mercadolibre.com.mx/MLM-2716629645-terreno-industrial-en-venta-en-palmillas-son-13-hectareas-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=9&amp;type=item&amp;tracking_id=6da87cc9-ea4e-43ef-accd-6e90e2809fd5&amp;price_drop=not_apply</t>
         </is>
       </c>
     </row>
@@ -646,7 +646,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>https://terreno.mercadolibre.com.mx/MLM-2748643873-terreno-en-venta-a-pie-de-carretera-toluca-atlacomulco-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=10&amp;type=item&amp;tracking_id=52b27256-ef9e-4304-a16d-deed8b69cffe&amp;price_drop=not_apply</t>
+          <t>https://terreno.mercadolibre.com.mx/MLM-2748643873-terreno-en-venta-a-pie-de-carretera-toluca-atlacomulco-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=10&amp;type=item&amp;tracking_id=6da87cc9-ea4e-43ef-accd-6e90e2809fd5&amp;price_drop=not_apply</t>
         </is>
       </c>
     </row>
@@ -666,7 +666,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>https://terreno.mercadolibre.com.mx/MLM-4790479866-terreno-regular-con-infraestructura-lista-base-solida-para-tu-proyecto-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=11&amp;type=item&amp;tracking_id=52b27256-ef9e-4304-a16d-deed8b69cffe&amp;price_drop=not_apply</t>
+          <t>https://terreno.mercadolibre.com.mx/MLM-4790479866-terreno-regular-con-infraestructura-lista-base-solida-para-tu-proyecto-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=11&amp;type=item&amp;tracking_id=6da87cc9-ea4e-43ef-accd-6e90e2809fd5&amp;price_drop=not_apply</t>
         </is>
       </c>
     </row>
@@ -686,7 +686,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>https://terreno.mercadolibre.com.mx/MLM-5015164202-venta-terreno-lotes-palmillas-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=12&amp;type=item&amp;tracking_id=52b27256-ef9e-4304-a16d-deed8b69cffe&amp;price_drop=not_apply</t>
+          <t>https://terreno.mercadolibre.com.mx/MLM-5015164202-venta-terreno-lotes-palmillas-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=12&amp;type=item&amp;tracking_id=6da87cc9-ea4e-43ef-accd-6e90e2809fd5&amp;price_drop=not_apply</t>
         </is>
       </c>
     </row>
@@ -706,7 +706,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>https://terreno.mercadolibre.com.mx/MLM-4416680104-terreno-en-venta-sobre-calzada-del-pacifico-cacalomacan-por-ocho-cedros-toluca-cas-23000-m2-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=13&amp;type=item&amp;tracking_id=52b27256-ef9e-4304-a16d-deed8b69cffe&amp;price_drop=not_apply</t>
+          <t>https://terreno.mercadolibre.com.mx/MLM-4416680104-terreno-en-venta-sobre-calzada-del-pacifico-cacalomacan-por-ocho-cedros-toluca-cas-23000-m2-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=13&amp;type=item&amp;tracking_id=6da87cc9-ea4e-43ef-accd-6e90e2809fd5&amp;price_drop=not_apply</t>
         </is>
       </c>
     </row>
@@ -726,7 +726,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://terreno.mercadolibre.com.mx/MLM-2736455271-terreno-de-2-hectareas-en-zona-urbana-santa-maria-totoltepec-estado-de-mexico-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=14&amp;type=item&amp;tracking_id=52b27256-ef9e-4304-a16d-deed8b69cffe&amp;price_drop=not_apply</t>
+          <t>https://terreno.mercadolibre.com.mx/MLM-2736455271-terreno-de-2-hectareas-en-zona-urbana-santa-maria-totoltepec-estado-de-mexico-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=14&amp;type=item&amp;tracking_id=6da87cc9-ea4e-43ef-accd-6e90e2809fd5&amp;price_drop=not_apply</t>
         </is>
       </c>
     </row>
@@ -737,7 +737,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1831680</v>
+        <v>299999</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -746,7 +746,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://terreno.mercadolibre.com.mx/MLM-2804712255-venta-terreno-paraje-san-rafael-en-toluca-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=15&amp;type=item&amp;float_highlight=recent_publication&amp;tracking_id=52b27256-ef9e-4304-a16d-deed8b69cffe&amp;price_drop=not_apply</t>
+          <t>https://terreno.mercadolibre.com.mx/MLM-5082958514-lotes-a-10-min-de-paideia-propiedad-desde-230-m-en-adelante-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=15&amp;type=item&amp;float_highlight=recent_publication&amp;tracking_id=6da87cc9-ea4e-43ef-accd-6e90e2809fd5&amp;price_drop=not_apply</t>
         </is>
       </c>
     </row>
@@ -757,7 +757,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1485000</v>
+        <v>1831680</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -766,7 +766,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>https://terreno.mercadolibre.com.mx/MLM-2187928841-venta-terreno-cerrillo-vista-hermosa-toluca-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=16&amp;type=item&amp;tracking_id=52b27256-ef9e-4304-a16d-deed8b69cffe&amp;price_drop=not_apply</t>
+          <t>https://terreno.mercadolibre.com.mx/MLM-2804712255-venta-terreno-paraje-san-rafael-en-toluca-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=16&amp;type=item&amp;float_highlight=recent_publication&amp;tracking_id=6da87cc9-ea4e-43ef-accd-6e90e2809fd5&amp;price_drop=not_apply</t>
         </is>
       </c>
     </row>
@@ -777,7 +777,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>4805040</v>
+        <v>1485000</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -786,7 +786,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>https://terreno.mercadolibre.com.mx/MLM-3705026808-venta-de-terreno-en-cacalomacan-a-20-min-centro-toluca-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=17&amp;type=item&amp;tracking_id=52b27256-ef9e-4304-a16d-deed8b69cffe&amp;price_drop=not_apply</t>
+          <t>https://terreno.mercadolibre.com.mx/MLM-2187928841-venta-terreno-cerrillo-vista-hermosa-toluca-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=17&amp;type=item&amp;tracking_id=6da87cc9-ea4e-43ef-accd-6e90e2809fd5&amp;price_drop=not_apply</t>
         </is>
       </c>
     </row>
@@ -797,7 +797,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1920000</v>
+        <v>4805040</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -806,7 +806,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>https://terreno.mercadolibre.com.mx/MLM-4119789692-terreno-en-venta-residencial-ex-hacienda-san-jose-toluca-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=18&amp;type=item&amp;tracking_id=52b27256-ef9e-4304-a16d-deed8b69cffe&amp;price_drop=not_apply</t>
+          <t>https://terreno.mercadolibre.com.mx/MLM-3705026808-venta-de-terreno-en-cacalomacan-a-20-min-centro-toluca-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=18&amp;type=item&amp;tracking_id=6da87cc9-ea4e-43ef-accd-6e90e2809fd5&amp;price_drop=not_apply</t>
         </is>
       </c>
     </row>
@@ -817,7 +817,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1244380</v>
+        <v>1920000</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -826,7 +826,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>https://terreno.mercadolibre.com.mx/MLM-4826508826-venta-de-lote-de-terreno-residencial-cerca-de-galerias-metepec-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=19&amp;type=item&amp;tracking_id=52b27256-ef9e-4304-a16d-deed8b69cffe&amp;price_drop=not_apply</t>
+          <t>https://terreno.mercadolibre.com.mx/MLM-4119789692-terreno-en-venta-residencial-ex-hacienda-san-jose-toluca-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=19&amp;type=item&amp;tracking_id=6da87cc9-ea4e-43ef-accd-6e90e2809fd5&amp;price_drop=not_apply</t>
         </is>
       </c>
     </row>
@@ -837,7 +837,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>8565858</v>
+        <v>1244380</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -846,7 +846,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>https://terreno.mercadolibre.com.mx/MLM-4080298834-terreno-en-venta-en-san-miguel-zacango-toluca-mexico-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=20&amp;type=item&amp;tracking_id=52b27256-ef9e-4304-a16d-deed8b69cffe&amp;price_drop=not_apply</t>
+          <t>https://terreno.mercadolibre.com.mx/MLM-4826508826-venta-de-lote-de-terreno-residencial-cerca-de-galerias-metepec-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=20&amp;type=item&amp;tracking_id=6da87cc9-ea4e-43ef-accd-6e90e2809fd5&amp;price_drop=not_apply</t>
         </is>
       </c>
     </row>
@@ -857,7 +857,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>8500000</v>
+        <v>8565858</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -866,7 +866,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>https://terreno.mercadolibre.com.mx/MLM-2310439697-se-vende-terreno-en-toluca-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=21&amp;type=item&amp;tracking_id=52b27256-ef9e-4304-a16d-deed8b69cffe&amp;price_drop=not_apply</t>
+          <t>https://terreno.mercadolibre.com.mx/MLM-4080298834-terreno-en-venta-en-san-miguel-zacango-toluca-mexico-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=21&amp;type=item&amp;tracking_id=6da87cc9-ea4e-43ef-accd-6e90e2809fd5&amp;price_drop=not_apply</t>
         </is>
       </c>
     </row>
@@ -877,7 +877,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1300000</v>
+        <v>8500000</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -886,7 +886,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>https://terreno.mercadolibre.com.mx/MLM-4495237624-lote-disponible-en-conjunto-ambar-toluca-edo-mex-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=22&amp;type=item&amp;tracking_id=52b27256-ef9e-4304-a16d-deed8b69cffe&amp;price_drop=not_apply</t>
+          <t>https://terreno.mercadolibre.com.mx/MLM-2310439697-se-vende-terreno-en-toluca-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=22&amp;type=item&amp;tracking_id=6da87cc9-ea4e-43ef-accd-6e90e2809fd5&amp;price_drop=not_apply</t>
         </is>
       </c>
     </row>
@@ -897,7 +897,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1200000</v>
+        <v>1300000</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -906,7 +906,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>https://terreno.mercadolibre.com.mx/MLM-2485559517-terreno-en-venta-en-toluca-san-andres-cuexcontitlan-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=23&amp;type=item&amp;tracking_id=52b27256-ef9e-4304-a16d-deed8b69cffe&amp;price_drop=not_apply</t>
+          <t>https://terreno.mercadolibre.com.mx/MLM-4495237624-lote-disponible-en-conjunto-ambar-toluca-edo-mex-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=23&amp;type=item&amp;tracking_id=6da87cc9-ea4e-43ef-accd-6e90e2809fd5&amp;price_drop=not_apply</t>
         </is>
       </c>
     </row>
@@ -917,7 +917,7 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>38634000</v>
+        <v>1200000</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -926,7 +926,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>https://terreno.mercadolibre.com.mx/MLM-2431684449-terreno-en-toluca-25756-m2-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=24&amp;type=item&amp;tracking_id=52b27256-ef9e-4304-a16d-deed8b69cffe&amp;price_drop=not_apply</t>
+          <t>https://terreno.mercadolibre.com.mx/MLM-2485559517-terreno-en-venta-en-toluca-san-andres-cuexcontitlan-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=24&amp;type=item&amp;tracking_id=6da87cc9-ea4e-43ef-accd-6e90e2809fd5&amp;price_drop=not_apply</t>
         </is>
       </c>
     </row>
@@ -937,7 +937,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>5625000</v>
+        <v>38634000</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -946,7 +946,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>https://terreno.mercadolibre.com.mx/MLM-2323267483-terreno-en-venta-2250m2-en-san-felipe-tlalmimilolpan-toluca-mexico-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=25&amp;type=item&amp;tracking_id=52b27256-ef9e-4304-a16d-deed8b69cffe&amp;price_drop=not_apply</t>
+          <t>https://terreno.mercadolibre.com.mx/MLM-2431684449-terreno-en-toluca-25756-m2-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=25&amp;type=item&amp;tracking_id=6da87cc9-ea4e-43ef-accd-6e90e2809fd5&amp;price_drop=not_apply</t>
         </is>
       </c>
     </row>
@@ -957,7 +957,7 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>25650000</v>
+        <v>5625000</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -966,7 +966,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>https://terreno.mercadolibre.com.mx/MLM-4169951646-terreno-en-venta-por-las-torres-toluca-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=26&amp;type=item&amp;tracking_id=52b27256-ef9e-4304-a16d-deed8b69cffe&amp;price_drop=not_apply</t>
+          <t>https://terreno.mercadolibre.com.mx/MLM-2323267483-terreno-en-venta-2250m2-en-san-felipe-tlalmimilolpan-toluca-mexico-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=26&amp;type=item&amp;tracking_id=6da87cc9-ea4e-43ef-accd-6e90e2809fd5&amp;price_drop=not_apply</t>
         </is>
       </c>
     </row>
@@ -977,7 +977,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>4800000</v>
+        <v>25650000</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -986,7 +986,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>https://terreno.mercadolibre.com.mx/MLM-4416373342-terreno-en-venta-en-san-lorenzo-tepaltitlan-centro-toluca-mexico-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=27&amp;type=item&amp;tracking_id=52b27256-ef9e-4304-a16d-deed8b69cffe&amp;price_drop=not_apply</t>
+          <t>https://terreno.mercadolibre.com.mx/MLM-4169951646-terreno-en-venta-por-las-torres-toluca-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=27&amp;type=item&amp;tracking_id=6da87cc9-ea4e-43ef-accd-6e90e2809fd5&amp;price_drop=not_apply</t>
         </is>
       </c>
     </row>
@@ -997,7 +997,7 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>14490000</v>
+        <v>4800000</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -1006,7 +1006,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>https://terreno.mercadolibre.com.mx/MLM-2584697469-oportunidad-de-inversion-terreno-de-9993-m-cerca-de-parque-toluca-2000-ideal-para-naves-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=28&amp;type=item&amp;tracking_id=52b27256-ef9e-4304-a16d-deed8b69cffe&amp;price_drop=not_apply</t>
+          <t>https://terreno.mercadolibre.com.mx/MLM-4416373342-terreno-en-venta-en-san-lorenzo-tepaltitlan-centro-toluca-mexico-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=28&amp;type=item&amp;tracking_id=6da87cc9-ea4e-43ef-accd-6e90e2809fd5&amp;price_drop=not_apply</t>
         </is>
       </c>
     </row>
@@ -1017,7 +1017,7 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>24520000</v>
+        <v>14490000</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -1026,7 +1026,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>https://terreno.mercadolibre.com.mx/MLM-4169951774-terreno-en-venta-por-las-torres-toluca-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=29&amp;type=item&amp;tracking_id=52b27256-ef9e-4304-a16d-deed8b69cffe&amp;price_drop=not_apply</t>
+          <t>https://terreno.mercadolibre.com.mx/MLM-2584697469-oportunidad-de-inversion-terreno-de-9993-m-cerca-de-parque-toluca-2000-ideal-para-naves-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=29&amp;type=item&amp;tracking_id=6da87cc9-ea4e-43ef-accd-6e90e2809fd5&amp;price_drop=not_apply</t>
         </is>
       </c>
     </row>
@@ -1037,7 +1037,7 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>12024000</v>
+        <v>24520000</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -1046,7 +1046,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>https://terreno.mercadolibre.com.mx/MLM-2323192153-terreno-en-venta-8016-m2-en-san-felipe-tlalmimilolpan-toluca-mexico-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=30&amp;type=item&amp;tracking_id=52b27256-ef9e-4304-a16d-deed8b69cffe&amp;price_drop=not_apply</t>
+          <t>https://terreno.mercadolibre.com.mx/MLM-4169951774-terreno-en-venta-por-las-torres-toluca-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=30&amp;type=item&amp;tracking_id=6da87cc9-ea4e-43ef-accd-6e90e2809fd5&amp;price_drop=not_apply</t>
         </is>
       </c>
     </row>
@@ -1057,7 +1057,7 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>13650000</v>
+        <v>12024000</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>https://terreno.mercadolibre.com.mx/MLM-2487732477-terreno-en-venta-por-las-torres-toluca-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=31&amp;type=item&amp;tracking_id=52b27256-ef9e-4304-a16d-deed8b69cffe&amp;price_drop=not_apply</t>
+          <t>https://terreno.mercadolibre.com.mx/MLM-2323192153-terreno-en-venta-8016-m2-en-san-felipe-tlalmimilolpan-toluca-mexico-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=31&amp;type=item&amp;tracking_id=6da87cc9-ea4e-43ef-accd-6e90e2809fd5&amp;price_drop=not_apply</t>
         </is>
       </c>
     </row>
@@ -1077,7 +1077,7 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>4725000</v>
+        <v>13650000</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -1086,7 +1086,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>https://terreno.mercadolibre.com.mx/MLM-2318168399-terreno-en-venta-en-cacalomacan-a-2-cuadras-de-jinetes-cerca-de-calz-pacifico-y-colegio-paideia-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=32&amp;type=item&amp;tracking_id=52b27256-ef9e-4304-a16d-deed8b69cffe&amp;price_drop=not_apply</t>
+          <t>https://terreno.mercadolibre.com.mx/MLM-2487732477-terreno-en-venta-por-las-torres-toluca-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=32&amp;type=item&amp;tracking_id=6da87cc9-ea4e-43ef-accd-6e90e2809fd5&amp;price_drop=not_apply</t>
         </is>
       </c>
     </row>
@@ -1097,7 +1097,7 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>11500000</v>
+        <v>4725000</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -1106,7 +1106,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>https://terreno.mercadolibre.com.mx/MLM-4080259510-terreno-en-venta-en-san-martin-toltepec-toluca-mexico-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=33&amp;type=item&amp;tracking_id=52b27256-ef9e-4304-a16d-deed8b69cffe&amp;price_drop=not_apply</t>
+          <t>https://terreno.mercadolibre.com.mx/MLM-2318168399-terreno-en-venta-en-cacalomacan-a-2-cuadras-de-jinetes-cerca-de-calz-pacifico-y-colegio-paideia-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=33&amp;type=item&amp;tracking_id=6da87cc9-ea4e-43ef-accd-6e90e2809fd5&amp;price_drop=not_apply</t>
         </is>
       </c>
     </row>
@@ -1117,7 +1117,7 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>1840590</v>
+        <v>11500000</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -1126,7 +1126,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>https://terreno.mercadolibre.com.mx/MLM-4080239968-terreno-en-venta-toluca-cerca-del-aeropuerto-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=34&amp;type=item&amp;tracking_id=52b27256-ef9e-4304-a16d-deed8b69cffe&amp;price_drop=not_apply</t>
+          <t>https://terreno.mercadolibre.com.mx/MLM-4080259510-terreno-en-venta-en-san-martin-toltepec-toluca-mexico-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=34&amp;type=item&amp;tracking_id=6da87cc9-ea4e-43ef-accd-6e90e2809fd5&amp;price_drop=not_apply</t>
         </is>
       </c>
     </row>
@@ -1137,7 +1137,7 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>8500000</v>
+        <v>1840590</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -1146,7 +1146,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>https://terreno.mercadolibre.com.mx/MLM-2343423083-terreno-en-san-pedro-totoltepec-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=35&amp;type=item&amp;tracking_id=52b27256-ef9e-4304-a16d-deed8b69cffe&amp;price_drop=not_apply</t>
+          <t>https://terreno.mercadolibre.com.mx/MLM-4080239968-terreno-en-venta-toluca-cerca-del-aeropuerto-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=35&amp;type=item&amp;tracking_id=6da87cc9-ea4e-43ef-accd-6e90e2809fd5&amp;price_drop=not_apply</t>
         </is>
       </c>
     </row>
@@ -1157,7 +1157,7 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>35000000</v>
+        <v>8500000</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -1166,7 +1166,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>https://terreno.mercadolibre.com.mx/MLM-2370231281-terreno-en-venta-en-toluca-reforma-y-ferr-nac-independencia-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=36&amp;type=item&amp;tracking_id=52b27256-ef9e-4304-a16d-deed8b69cffe&amp;price_drop=not_apply</t>
+          <t>https://terreno.mercadolibre.com.mx/MLM-2343423083-terreno-en-san-pedro-totoltepec-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=36&amp;type=item&amp;tracking_id=6da87cc9-ea4e-43ef-accd-6e90e2809fd5&amp;price_drop=not_apply</t>
         </is>
       </c>
     </row>
@@ -1177,7 +1177,7 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>2450000</v>
+        <v>35000000</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -1186,7 +1186,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>https://terreno.mercadolibre.com.mx/MLM-2343569515-terreno-en-santa-maria-totoltepec-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=37&amp;type=item&amp;tracking_id=52b27256-ef9e-4304-a16d-deed8b69cffe&amp;price_drop=not_apply</t>
+          <t>https://terreno.mercadolibre.com.mx/MLM-2370231281-terreno-en-venta-en-toluca-reforma-y-ferr-nac-independencia-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=37&amp;type=item&amp;tracking_id=6da87cc9-ea4e-43ef-accd-6e90e2809fd5&amp;price_drop=not_apply</t>
         </is>
       </c>
     </row>
@@ -1197,7 +1197,7 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>50000000</v>
+        <v>2450000</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -1206,7 +1206,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>https://terreno.mercadolibre.com.mx/MLM-4558160588-terreno-en-venta-en-cipres-toluca-estado-de-mexico-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=38&amp;type=item&amp;tracking_id=52b27256-ef9e-4304-a16d-deed8b69cffe&amp;price_drop=not_apply</t>
+          <t>https://terreno.mercadolibre.com.mx/MLM-2343569515-terreno-en-santa-maria-totoltepec-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=38&amp;type=item&amp;tracking_id=6da87cc9-ea4e-43ef-accd-6e90e2809fd5&amp;price_drop=not_apply</t>
         </is>
       </c>
     </row>
@@ -1217,7 +1217,7 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>203547204</v>
+        <v>50000000</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -1226,7 +1226,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>https://terreno.mercadolibre.com.mx/MLM-4261794654-terreno-en-venta-en-industrial-en-toluca-estado-de-mexico-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=39&amp;type=item&amp;tracking_id=52b27256-ef9e-4304-a16d-deed8b69cffe&amp;price_drop=not_apply</t>
+          <t>https://terreno.mercadolibre.com.mx/MLM-4558160588-terreno-en-venta-en-cipres-toluca-estado-de-mexico-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=39&amp;type=item&amp;tracking_id=6da87cc9-ea4e-43ef-accd-6e90e2809fd5&amp;price_drop=not_apply</t>
         </is>
       </c>
     </row>
@@ -1237,7 +1237,7 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>14571000</v>
+        <v>203547204</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -1246,7 +1246,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>https://terreno.mercadolibre.com.mx/MLM-4261807760-se-vende-terreno-carretera-mexico-toluca-lerma-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=40&amp;type=item&amp;tracking_id=52b27256-ef9e-4304-a16d-deed8b69cffe&amp;price_drop=not_apply</t>
+          <t>https://terreno.mercadolibre.com.mx/MLM-4261794654-terreno-en-venta-en-industrial-en-toluca-estado-de-mexico-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=40&amp;type=item&amp;tracking_id=6da87cc9-ea4e-43ef-accd-6e90e2809fd5&amp;price_drop=not_apply</t>
         </is>
       </c>
     </row>
@@ -1257,7 +1257,7 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>222618909</v>
+        <v>14571000</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -1266,7 +1266,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>https://terreno.mercadolibre.com.mx/MLM-4261859654-terreno-en-venta-industrial-en-toluca-estado-de-mexico-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=41&amp;type=item&amp;tracking_id=52b27256-ef9e-4304-a16d-deed8b69cffe&amp;price_drop=not_apply</t>
+          <t>https://terreno.mercadolibre.com.mx/MLM-4261807760-se-vende-terreno-carretera-mexico-toluca-lerma-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=41&amp;type=item&amp;tracking_id=6da87cc9-ea4e-43ef-accd-6e90e2809fd5&amp;price_drop=not_apply</t>
         </is>
       </c>
     </row>
@@ -1277,7 +1277,7 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>1870000</v>
+        <v>222618909</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -1286,7 +1286,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>https://terreno.mercadolibre.com.mx/MLM-2811993671-terreno-en-venta-en-residencial-hacienda-san-jose-en-toluca-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=42&amp;type=item&amp;float_highlight=recent_publication&amp;tracking_id=52b27256-ef9e-4304-a16d-deed8b69cffe&amp;price_drop=not_apply</t>
+          <t>https://terreno.mercadolibre.com.mx/MLM-4261859654-terreno-en-venta-industrial-en-toluca-estado-de-mexico-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=42&amp;type=item&amp;tracking_id=6da87cc9-ea4e-43ef-accd-6e90e2809fd5&amp;price_drop=not_apply</t>
         </is>
       </c>
     </row>
@@ -1297,7 +1297,7 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>700000</v>
+        <v>1870000</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -1306,7 +1306,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>https://terreno.mercadolibre.com.mx/MLM-5058024988-terreno-en-venta-en-san-lorenzo-tepaltitlan-toluca-estado-de-mexico-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=43&amp;type=item&amp;float_highlight=recent_publication&amp;tracking_id=52b27256-ef9e-4304-a16d-deed8b69cffe&amp;price_drop=not_apply</t>
+          <t>https://terreno.mercadolibre.com.mx/MLM-2811993671-terreno-en-venta-en-residencial-hacienda-san-jose-en-toluca-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=43&amp;type=item&amp;float_highlight=recent_publication&amp;tracking_id=6da87cc9-ea4e-43ef-accd-6e90e2809fd5&amp;price_drop=not_apply</t>
         </is>
       </c>
     </row>
@@ -1317,7 +1317,7 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>3240000</v>
+        <v>132000000</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -1326,7 +1326,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>https://terreno.mercadolibre.com.mx/MLM-5058177406-terreno-en-venta-en-san-francisco-totoltepec-toluca-estado-de-mexico-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=44&amp;type=item&amp;float_highlight=recent_publication&amp;tracking_id=52b27256-ef9e-4304-a16d-deed8b69cffe&amp;price_drop=not_apply</t>
+          <t>https://terreno.mercadolibre.com.mx/MLM-5064030156-terreno-en-venta-en-parque-industrial-el-coecillo-toluca-estado-de-mexico-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=44&amp;type=item&amp;float_highlight=recent_publication&amp;tracking_id=6da87cc9-ea4e-43ef-accd-6e90e2809fd5&amp;price_drop=not_apply</t>
         </is>
       </c>
     </row>
@@ -1337,7 +1337,7 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>132000000</v>
+        <v>279450</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -1346,7 +1346,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>https://terreno.mercadolibre.com.mx/MLM-5064030156-terreno-en-venta-en-parque-industrial-el-coecillo-toluca-estado-de-mexico-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=45&amp;type=item&amp;float_highlight=recent_publication&amp;tracking_id=52b27256-ef9e-4304-a16d-deed8b69cffe&amp;price_drop=not_apply</t>
+          <t>https://terreno.mercadolibre.com.mx/MLM-5060346586-ultimos-2-lotes-en-venta-en-san-cayetano-muy-cerca-de-la-unsa-en-toluca-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=45&amp;type=item&amp;float_highlight=recent_publication&amp;tracking_id=6da87cc9-ea4e-43ef-accd-6e90e2809fd5&amp;price_drop=not_apply</t>
         </is>
       </c>
     </row>
@@ -1357,7 +1357,7 @@
         </is>
       </c>
       <c r="B47" t="n">
-        <v>279450</v>
+        <v>23500000</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -1366,7 +1366,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>https://terreno.mercadolibre.com.mx/MLM-5060346586-ultimos-2-lotes-en-venta-en-san-cayetano-muy-cerca-de-la-unsa-en-toluca-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=46&amp;type=item&amp;float_highlight=recent_publication&amp;tracking_id=52b27256-ef9e-4304-a16d-deed8b69cffe&amp;price_drop=not_apply</t>
+          <t>https://terreno.mercadolibre.com.mx/MLM-4950598656-terreno-comercial-en-venta-en-san-bernardino-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=46&amp;type=item&amp;tracking_id=6da87cc9-ea4e-43ef-accd-6e90e2809fd5&amp;price_drop=not_apply</t>
         </is>
       </c>
     </row>
@@ -1377,7 +1377,7 @@
         </is>
       </c>
       <c r="B48" t="n">
-        <v>9215400</v>
+        <v>8760000</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -1386,7 +1386,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>https://terreno.mercadolibre.com.mx/MLM-5047581202-terreno-comercial-en-venta-en-santa-cruz-otzacatipan-toluca-mexico-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=47&amp;type=item&amp;float_highlight=recent_publication&amp;tracking_id=52b27256-ef9e-4304-a16d-deed8b69cffe&amp;price_drop=not_apply</t>
+          <t>https://terreno.mercadolibre.com.mx/MLM-4761562052-terreno-comercial-en-venta-en-santa-maria-totoltepec-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=47&amp;type=item&amp;tracking_id=6da87cc9-ea4e-43ef-accd-6e90e2809fd5&amp;price_drop=not_apply</t>
         </is>
       </c>
     </row>
@@ -1397,7 +1397,7 @@
         </is>
       </c>
       <c r="B49" t="n">
-        <v>8502990</v>
+        <v>26320000</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -1406,7 +1406,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>https://terreno.mercadolibre.com.mx/MLM-5047581198-terreno-comercial-en-venta-en-santa-cruz-otzacatipan-toluca-mexico-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=48&amp;type=item&amp;float_highlight=recent_publication&amp;tracking_id=52b27256-ef9e-4304-a16d-deed8b69cffe&amp;price_drop=not_apply</t>
+          <t>https://terreno.mercadolibre.com.mx/MLM-4790443980-terreno-residencial-en-venta-en-la-venta-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=48&amp;type=item&amp;tracking_id=6da87cc9-ea4e-43ef-accd-6e90e2809fd5&amp;price_drop=not_apply</t>
         </is>
       </c>
     </row>
@@ -1426,7 +1426,7 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>https://terreno.mercadolibre.com.mx/MLM-3835159420-lotes-de-terreno-desde-104-m2-en-venta-cerca-del-aeropuerto-de-toluca-en-la-constitucion-toltepec-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=1&amp;type=item&amp;tracking_id=ee737872-1b04-44c7-b466-ef90db8b4927&amp;price_drop=not_apply</t>
+          <t>https://terreno.mercadolibre.com.mx/MLM-3835159420-lotes-de-terreno-desde-104-m2-en-venta-cerca-del-aeropuerto-de-toluca-en-la-constitucion-toltepec-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=1&amp;type=item&amp;tracking_id=0b5ffd07-b636-4489-bf5a-81c4a52af9df&amp;price_drop=not_apply</t>
         </is>
       </c>
     </row>
@@ -1446,7 +1446,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>https://terreno.mercadolibre.com.mx/MLM-2810992285-construye-tu-residencia-en-la-zona-de-mayor-proyeccion-de-toluca-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=2&amp;type=item&amp;float_highlight=recent_publication&amp;tracking_id=ee737872-1b04-44c7-b466-ef90db8b4927&amp;price_drop=not_apply</t>
+          <t>https://terreno.mercadolibre.com.mx/MLM-2810992285-construye-tu-residencia-en-la-zona-de-mayor-proyeccion-de-toluca-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=2&amp;type=item&amp;float_highlight=recent_publication&amp;tracking_id=0b5ffd07-b636-4489-bf5a-81c4a52af9df&amp;price_drop=not_apply</t>
         </is>
       </c>
     </row>
@@ -1466,7 +1466,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>https://terreno.mercadolibre.com.mx/MLM-3847495816-el-mejor-terreno-del-condominio-puede-ser-tuyo-a-un-precio-de-oportunidad-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=3&amp;type=item&amp;tracking_id=ee737872-1b04-44c7-b466-ef90db8b4927&amp;price_drop=not_apply</t>
+          <t>https://terreno.mercadolibre.com.mx/MLM-3847495816-el-mejor-terreno-del-condominio-puede-ser-tuyo-a-un-precio-de-oportunidad-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=3&amp;type=item&amp;tracking_id=0b5ffd07-b636-4489-bf5a-81c4a52af9df&amp;price_drop=not_apply</t>
         </is>
       </c>
     </row>
@@ -1477,7 +1477,7 @@
         </is>
       </c>
       <c r="B53" t="n">
-        <v>7600000</v>
+        <v>649000</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -1486,7 +1486,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>https://terreno.mercadolibre.com.mx/MLM-2231593183-terreno-en-venta-en-san-mateo-oxtotitlan-toluca-mexico-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=4&amp;type=item&amp;tracking_id=ee737872-1b04-44c7-b466-ef90db8b4927&amp;price_drop=not_apply</t>
+          <t>https://terreno.mercadolibre.com.mx/MLM-2753915589-terreno-bardeado-en-cacalomacan-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=4&amp;type=item&amp;tracking_id=0b5ffd07-b636-4489-bf5a-81c4a52af9df&amp;price_drop=false</t>
         </is>
       </c>
     </row>
@@ -1497,7 +1497,7 @@
         </is>
       </c>
       <c r="B54" t="n">
-        <v>649000</v>
+        <v>7600000</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -1506,7 +1506,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>https://terreno.mercadolibre.com.mx/MLM-2753915589-terreno-bardeado-en-cacalomacan-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=5&amp;type=item&amp;tracking_id=ee737872-1b04-44c7-b466-ef90db8b4927&amp;price_drop=false</t>
+          <t>https://terreno.mercadolibre.com.mx/MLM-2231593183-terreno-en-venta-en-san-mateo-oxtotitlan-toluca-mexico-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=5&amp;type=item&amp;tracking_id=0b5ffd07-b636-4489-bf5a-81c4a52af9df&amp;price_drop=not_apply</t>
         </is>
       </c>
     </row>
@@ -1526,7 +1526,7 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>https://terreno.mercadolibre.com.mx/MLM-2716356593-terreno-en-venta-en-colonia-nueva-santa-maria-de-las-rosas-toluca-estado-de-mexico-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=6&amp;type=item&amp;tracking_id=ee737872-1b04-44c7-b466-ef90db8b4927&amp;price_drop=not_apply</t>
+          <t>https://terreno.mercadolibre.com.mx/MLM-2716356593-terreno-en-venta-en-colonia-nueva-santa-maria-de-las-rosas-toluca-estado-de-mexico-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=6&amp;type=item&amp;tracking_id=0b5ffd07-b636-4489-bf5a-81c4a52af9df&amp;price_drop=not_apply</t>
         </is>
       </c>
     </row>
@@ -1546,7 +1546,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>https://terreno.mercadolibre.com.mx/MLM-4660497978-terreno-en-venta-en-toluca-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=7&amp;type=item&amp;tracking_id=ee737872-1b04-44c7-b466-ef90db8b4927&amp;price_drop=not_apply</t>
+          <t>https://terreno.mercadolibre.com.mx/MLM-4660497978-terreno-en-venta-en-toluca-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=7&amp;type=item&amp;tracking_id=0b5ffd07-b636-4489-bf5a-81c4a52af9df&amp;price_drop=not_apply</t>
         </is>
       </c>
     </row>
@@ -1566,7 +1566,7 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>https://terreno.mercadolibre.com.mx/MLM-4388186170-terreno-industrial-en-venta-en-toluca-san-cayetano-a-un-lado-de-la-caseta-el-dorado-cerca-puerta-mexico-recinto-aduanal-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=8&amp;type=item&amp;tracking_id=ee737872-1b04-44c7-b466-ef90db8b4927&amp;price_drop=not_apply</t>
+          <t>https://terreno.mercadolibre.com.mx/MLM-4388186170-terreno-industrial-en-venta-en-toluca-san-cayetano-a-un-lado-de-la-caseta-el-dorado-cerca-puerta-mexico-recinto-aduanal-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=8&amp;type=item&amp;tracking_id=0b5ffd07-b636-4489-bf5a-81c4a52af9df&amp;price_drop=not_apply</t>
         </is>
       </c>
     </row>
@@ -1586,7 +1586,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>https://terreno.mercadolibre.com.mx/MLM-2716629645-terreno-industrial-en-venta-en-palmillas-son-13-hectareas-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=9&amp;type=item&amp;tracking_id=ee737872-1b04-44c7-b466-ef90db8b4927&amp;price_drop=not_apply</t>
+          <t>https://terreno.mercadolibre.com.mx/MLM-2716629645-terreno-industrial-en-venta-en-palmillas-son-13-hectareas-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=9&amp;type=item&amp;tracking_id=0b5ffd07-b636-4489-bf5a-81c4a52af9df&amp;price_drop=not_apply</t>
         </is>
       </c>
     </row>
@@ -1606,7 +1606,7 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>https://terreno.mercadolibre.com.mx/MLM-2748643873-terreno-en-venta-a-pie-de-carretera-toluca-atlacomulco-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=10&amp;type=item&amp;tracking_id=ee737872-1b04-44c7-b466-ef90db8b4927&amp;price_drop=not_apply</t>
+          <t>https://terreno.mercadolibre.com.mx/MLM-2748643873-terreno-en-venta-a-pie-de-carretera-toluca-atlacomulco-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=10&amp;type=item&amp;tracking_id=0b5ffd07-b636-4489-bf5a-81c4a52af9df&amp;price_drop=not_apply</t>
         </is>
       </c>
     </row>
@@ -1626,7 +1626,7 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>https://terreno.mercadolibre.com.mx/MLM-4790479866-terreno-regular-con-infraestructura-lista-base-solida-para-tu-proyecto-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=11&amp;type=item&amp;tracking_id=ee737872-1b04-44c7-b466-ef90db8b4927&amp;price_drop=not_apply</t>
+          <t>https://terreno.mercadolibre.com.mx/MLM-4790479866-terreno-regular-con-infraestructura-lista-base-solida-para-tu-proyecto-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=11&amp;type=item&amp;tracking_id=0b5ffd07-b636-4489-bf5a-81c4a52af9df&amp;price_drop=not_apply</t>
         </is>
       </c>
     </row>
@@ -1646,7 +1646,7 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>https://terreno.mercadolibre.com.mx/MLM-5015164202-venta-terreno-lotes-palmillas-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=12&amp;type=item&amp;tracking_id=ee737872-1b04-44c7-b466-ef90db8b4927&amp;price_drop=not_apply</t>
+          <t>https://terreno.mercadolibre.com.mx/MLM-5015164202-venta-terreno-lotes-palmillas-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=12&amp;type=item&amp;tracking_id=0b5ffd07-b636-4489-bf5a-81c4a52af9df&amp;price_drop=not_apply</t>
         </is>
       </c>
     </row>
@@ -1666,7 +1666,7 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>https://terreno.mercadolibre.com.mx/MLM-4416680104-terreno-en-venta-sobre-calzada-del-pacifico-cacalomacan-por-ocho-cedros-toluca-cas-23000-m2-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=13&amp;type=item&amp;tracking_id=ee737872-1b04-44c7-b466-ef90db8b4927&amp;price_drop=not_apply</t>
+          <t>https://terreno.mercadolibre.com.mx/MLM-4416680104-terreno-en-venta-sobre-calzada-del-pacifico-cacalomacan-por-ocho-cedros-toluca-cas-23000-m2-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=13&amp;type=item&amp;tracking_id=0b5ffd07-b636-4489-bf5a-81c4a52af9df&amp;price_drop=not_apply</t>
         </is>
       </c>
     </row>
@@ -1686,7 +1686,7 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>https://terreno.mercadolibre.com.mx/MLM-2736455271-terreno-de-2-hectareas-en-zona-urbana-santa-maria-totoltepec-estado-de-mexico-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=14&amp;type=item&amp;tracking_id=ee737872-1b04-44c7-b466-ef90db8b4927&amp;price_drop=not_apply</t>
+          <t>https://terreno.mercadolibre.com.mx/MLM-2736455271-terreno-de-2-hectareas-en-zona-urbana-santa-maria-totoltepec-estado-de-mexico-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=14&amp;type=item&amp;tracking_id=0b5ffd07-b636-4489-bf5a-81c4a52af9df&amp;price_drop=not_apply</t>
         </is>
       </c>
     </row>
@@ -1697,7 +1697,7 @@
         </is>
       </c>
       <c r="B64" t="n">
-        <v>1831680</v>
+        <v>299999</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -1706,7 +1706,7 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>https://terreno.mercadolibre.com.mx/MLM-2804712255-venta-terreno-paraje-san-rafael-en-toluca-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=15&amp;type=item&amp;float_highlight=recent_publication&amp;tracking_id=ee737872-1b04-44c7-b466-ef90db8b4927&amp;price_drop=not_apply</t>
+          <t>https://terreno.mercadolibre.com.mx/MLM-5082958514-lotes-a-10-min-de-paideia-propiedad-desde-230-m-en-adelante-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=15&amp;type=item&amp;float_highlight=recent_publication&amp;tracking_id=0b5ffd07-b636-4489-bf5a-81c4a52af9df&amp;price_drop=not_apply</t>
         </is>
       </c>
     </row>
@@ -1717,7 +1717,7 @@
         </is>
       </c>
       <c r="B65" t="n">
-        <v>1485000</v>
+        <v>1831680</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -1726,7 +1726,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>https://terreno.mercadolibre.com.mx/MLM-2187928841-venta-terreno-cerrillo-vista-hermosa-toluca-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=16&amp;type=item&amp;tracking_id=ee737872-1b04-44c7-b466-ef90db8b4927&amp;price_drop=not_apply</t>
+          <t>https://terreno.mercadolibre.com.mx/MLM-2804712255-venta-terreno-paraje-san-rafael-en-toluca-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=16&amp;type=item&amp;float_highlight=recent_publication&amp;tracking_id=0b5ffd07-b636-4489-bf5a-81c4a52af9df&amp;price_drop=not_apply</t>
         </is>
       </c>
     </row>
@@ -1737,7 +1737,7 @@
         </is>
       </c>
       <c r="B66" t="n">
-        <v>4805040</v>
+        <v>1485000</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -1746,7 +1746,7 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>https://terreno.mercadolibre.com.mx/MLM-3705026808-venta-de-terreno-en-cacalomacan-a-20-min-centro-toluca-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=17&amp;type=item&amp;tracking_id=ee737872-1b04-44c7-b466-ef90db8b4927&amp;price_drop=not_apply</t>
+          <t>https://terreno.mercadolibre.com.mx/MLM-2187928841-venta-terreno-cerrillo-vista-hermosa-toluca-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=17&amp;type=item&amp;tracking_id=0b5ffd07-b636-4489-bf5a-81c4a52af9df&amp;price_drop=not_apply</t>
         </is>
       </c>
     </row>
@@ -1757,7 +1757,7 @@
         </is>
       </c>
       <c r="B67" t="n">
-        <v>1920000</v>
+        <v>4805040</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -1766,7 +1766,7 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>https://terreno.mercadolibre.com.mx/MLM-4119789692-terreno-en-venta-residencial-ex-hacienda-san-jose-toluca-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=18&amp;type=item&amp;tracking_id=ee737872-1b04-44c7-b466-ef90db8b4927&amp;price_drop=not_apply</t>
+          <t>https://terreno.mercadolibre.com.mx/MLM-3705026808-venta-de-terreno-en-cacalomacan-a-20-min-centro-toluca-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=18&amp;type=item&amp;tracking_id=0b5ffd07-b636-4489-bf5a-81c4a52af9df&amp;price_drop=not_apply</t>
         </is>
       </c>
     </row>
@@ -1777,7 +1777,7 @@
         </is>
       </c>
       <c r="B68" t="n">
-        <v>1244380</v>
+        <v>1920000</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -1786,7 +1786,7 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>https://terreno.mercadolibre.com.mx/MLM-4826508826-venta-de-lote-de-terreno-residencial-cerca-de-galerias-metepec-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=19&amp;type=item&amp;tracking_id=ee737872-1b04-44c7-b466-ef90db8b4927&amp;price_drop=not_apply</t>
+          <t>https://terreno.mercadolibre.com.mx/MLM-4119789692-terreno-en-venta-residencial-ex-hacienda-san-jose-toluca-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=19&amp;type=item&amp;tracking_id=0b5ffd07-b636-4489-bf5a-81c4a52af9df&amp;price_drop=not_apply</t>
         </is>
       </c>
     </row>
@@ -1797,7 +1797,7 @@
         </is>
       </c>
       <c r="B69" t="n">
-        <v>8565858</v>
+        <v>1244380</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -1806,7 +1806,7 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>https://terreno.mercadolibre.com.mx/MLM-4080298834-terreno-en-venta-en-san-miguel-zacango-toluca-mexico-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=20&amp;type=item&amp;tracking_id=ee737872-1b04-44c7-b466-ef90db8b4927&amp;price_drop=not_apply</t>
+          <t>https://terreno.mercadolibre.com.mx/MLM-4826508826-venta-de-lote-de-terreno-residencial-cerca-de-galerias-metepec-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=20&amp;type=item&amp;tracking_id=0b5ffd07-b636-4489-bf5a-81c4a52af9df&amp;price_drop=not_apply</t>
         </is>
       </c>
     </row>
@@ -1817,7 +1817,7 @@
         </is>
       </c>
       <c r="B70" t="n">
-        <v>8500000</v>
+        <v>8565858</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -1826,7 +1826,7 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>https://terreno.mercadolibre.com.mx/MLM-2310439697-se-vende-terreno-en-toluca-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=21&amp;type=item&amp;tracking_id=ee737872-1b04-44c7-b466-ef90db8b4927&amp;price_drop=not_apply</t>
+          <t>https://terreno.mercadolibre.com.mx/MLM-4080298834-terreno-en-venta-en-san-miguel-zacango-toluca-mexico-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=21&amp;type=item&amp;tracking_id=0b5ffd07-b636-4489-bf5a-81c4a52af9df&amp;price_drop=not_apply</t>
         </is>
       </c>
     </row>
@@ -1837,7 +1837,7 @@
         </is>
       </c>
       <c r="B71" t="n">
-        <v>1300000</v>
+        <v>8500000</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -1846,7 +1846,7 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>https://terreno.mercadolibre.com.mx/MLM-4495237624-lote-disponible-en-conjunto-ambar-toluca-edo-mex-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=22&amp;type=item&amp;tracking_id=ee737872-1b04-44c7-b466-ef90db8b4927&amp;price_drop=not_apply</t>
+          <t>https://terreno.mercadolibre.com.mx/MLM-2310439697-se-vende-terreno-en-toluca-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=22&amp;type=item&amp;tracking_id=0b5ffd07-b636-4489-bf5a-81c4a52af9df&amp;price_drop=not_apply</t>
         </is>
       </c>
     </row>
@@ -1857,7 +1857,7 @@
         </is>
       </c>
       <c r="B72" t="n">
-        <v>1200000</v>
+        <v>1300000</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -1866,7 +1866,7 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>https://terreno.mercadolibre.com.mx/MLM-2485559517-terreno-en-venta-en-toluca-san-andres-cuexcontitlan-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=23&amp;type=item&amp;tracking_id=ee737872-1b04-44c7-b466-ef90db8b4927&amp;price_drop=not_apply</t>
+          <t>https://terreno.mercadolibre.com.mx/MLM-4495237624-lote-disponible-en-conjunto-ambar-toluca-edo-mex-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=23&amp;type=item&amp;tracking_id=0b5ffd07-b636-4489-bf5a-81c4a52af9df&amp;price_drop=not_apply</t>
         </is>
       </c>
     </row>
@@ -1877,7 +1877,7 @@
         </is>
       </c>
       <c r="B73" t="n">
-        <v>38634000</v>
+        <v>1200000</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -1886,7 +1886,7 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>https://terreno.mercadolibre.com.mx/MLM-2431684449-terreno-en-toluca-25756-m2-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=24&amp;type=item&amp;tracking_id=ee737872-1b04-44c7-b466-ef90db8b4927&amp;price_drop=not_apply</t>
+          <t>https://terreno.mercadolibre.com.mx/MLM-2485559517-terreno-en-venta-en-toluca-san-andres-cuexcontitlan-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=24&amp;type=item&amp;tracking_id=0b5ffd07-b636-4489-bf5a-81c4a52af9df&amp;price_drop=not_apply</t>
         </is>
       </c>
     </row>
@@ -1897,7 +1897,7 @@
         </is>
       </c>
       <c r="B74" t="n">
-        <v>5625000</v>
+        <v>38634000</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -1906,7 +1906,7 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>https://terreno.mercadolibre.com.mx/MLM-2323267483-terreno-en-venta-2250m2-en-san-felipe-tlalmimilolpan-toluca-mexico-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=25&amp;type=item&amp;tracking_id=ee737872-1b04-44c7-b466-ef90db8b4927&amp;price_drop=not_apply</t>
+          <t>https://terreno.mercadolibre.com.mx/MLM-2431684449-terreno-en-toluca-25756-m2-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=25&amp;type=item&amp;tracking_id=0b5ffd07-b636-4489-bf5a-81c4a52af9df&amp;price_drop=not_apply</t>
         </is>
       </c>
     </row>
@@ -1917,7 +1917,7 @@
         </is>
       </c>
       <c r="B75" t="n">
-        <v>25650000</v>
+        <v>5625000</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -1926,7 +1926,7 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>https://terreno.mercadolibre.com.mx/MLM-4169951646-terreno-en-venta-por-las-torres-toluca-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=26&amp;type=item&amp;tracking_id=ee737872-1b04-44c7-b466-ef90db8b4927&amp;price_drop=not_apply</t>
+          <t>https://terreno.mercadolibre.com.mx/MLM-2323267483-terreno-en-venta-2250m2-en-san-felipe-tlalmimilolpan-toluca-mexico-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=26&amp;type=item&amp;tracking_id=0b5ffd07-b636-4489-bf5a-81c4a52af9df&amp;price_drop=not_apply</t>
         </is>
       </c>
     </row>
@@ -1937,7 +1937,7 @@
         </is>
       </c>
       <c r="B76" t="n">
-        <v>4800000</v>
+        <v>25650000</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -1946,7 +1946,7 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>https://terreno.mercadolibre.com.mx/MLM-4416373342-terreno-en-venta-en-san-lorenzo-tepaltitlan-centro-toluca-mexico-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=27&amp;type=item&amp;tracking_id=ee737872-1b04-44c7-b466-ef90db8b4927&amp;price_drop=not_apply</t>
+          <t>https://terreno.mercadolibre.com.mx/MLM-4169951646-terreno-en-venta-por-las-torres-toluca-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=27&amp;type=item&amp;tracking_id=0b5ffd07-b636-4489-bf5a-81c4a52af9df&amp;price_drop=not_apply</t>
         </is>
       </c>
     </row>
@@ -1957,7 +1957,7 @@
         </is>
       </c>
       <c r="B77" t="n">
-        <v>14490000</v>
+        <v>4800000</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -1966,7 +1966,7 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>https://terreno.mercadolibre.com.mx/MLM-2584697469-oportunidad-de-inversion-terreno-de-9993-m-cerca-de-parque-toluca-2000-ideal-para-naves-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=28&amp;type=item&amp;tracking_id=ee737872-1b04-44c7-b466-ef90db8b4927&amp;price_drop=not_apply</t>
+          <t>https://terreno.mercadolibre.com.mx/MLM-4416373342-terreno-en-venta-en-san-lorenzo-tepaltitlan-centro-toluca-mexico-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=28&amp;type=item&amp;tracking_id=0b5ffd07-b636-4489-bf5a-81c4a52af9df&amp;price_drop=not_apply</t>
         </is>
       </c>
     </row>
@@ -1977,7 +1977,7 @@
         </is>
       </c>
       <c r="B78" t="n">
-        <v>24520000</v>
+        <v>14490000</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -1986,7 +1986,7 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>https://terreno.mercadolibre.com.mx/MLM-4169951774-terreno-en-venta-por-las-torres-toluca-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=29&amp;type=item&amp;tracking_id=ee737872-1b04-44c7-b466-ef90db8b4927&amp;price_drop=not_apply</t>
+          <t>https://terreno.mercadolibre.com.mx/MLM-2584697469-oportunidad-de-inversion-terreno-de-9993-m-cerca-de-parque-toluca-2000-ideal-para-naves-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=29&amp;type=item&amp;tracking_id=0b5ffd07-b636-4489-bf5a-81c4a52af9df&amp;price_drop=not_apply</t>
         </is>
       </c>
     </row>
@@ -1997,7 +1997,7 @@
         </is>
       </c>
       <c r="B79" t="n">
-        <v>12024000</v>
+        <v>24520000</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -2006,7 +2006,7 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>https://terreno.mercadolibre.com.mx/MLM-2323192153-terreno-en-venta-8016-m2-en-san-felipe-tlalmimilolpan-toluca-mexico-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=30&amp;type=item&amp;tracking_id=ee737872-1b04-44c7-b466-ef90db8b4927&amp;price_drop=not_apply</t>
+          <t>https://terreno.mercadolibre.com.mx/MLM-4169951774-terreno-en-venta-por-las-torres-toluca-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=30&amp;type=item&amp;tracking_id=0b5ffd07-b636-4489-bf5a-81c4a52af9df&amp;price_drop=not_apply</t>
         </is>
       </c>
     </row>
@@ -2017,7 +2017,7 @@
         </is>
       </c>
       <c r="B80" t="n">
-        <v>13650000</v>
+        <v>12024000</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -2026,7 +2026,7 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>https://terreno.mercadolibre.com.mx/MLM-2487732477-terreno-en-venta-por-las-torres-toluca-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=31&amp;type=item&amp;tracking_id=ee737872-1b04-44c7-b466-ef90db8b4927&amp;price_drop=not_apply</t>
+          <t>https://terreno.mercadolibre.com.mx/MLM-2323192153-terreno-en-venta-8016-m2-en-san-felipe-tlalmimilolpan-toluca-mexico-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=31&amp;type=item&amp;tracking_id=0b5ffd07-b636-4489-bf5a-81c4a52af9df&amp;price_drop=not_apply</t>
         </is>
       </c>
     </row>
@@ -2037,7 +2037,7 @@
         </is>
       </c>
       <c r="B81" t="n">
-        <v>4725000</v>
+        <v>13650000</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -2046,7 +2046,7 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>https://terreno.mercadolibre.com.mx/MLM-2318168399-terreno-en-venta-en-cacalomacan-a-2-cuadras-de-jinetes-cerca-de-calz-pacifico-y-colegio-paideia-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=32&amp;type=item&amp;tracking_id=ee737872-1b04-44c7-b466-ef90db8b4927&amp;price_drop=not_apply</t>
+          <t>https://terreno.mercadolibre.com.mx/MLM-2487732477-terreno-en-venta-por-las-torres-toluca-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=32&amp;type=item&amp;tracking_id=0b5ffd07-b636-4489-bf5a-81c4a52af9df&amp;price_drop=not_apply</t>
         </is>
       </c>
     </row>
@@ -2057,7 +2057,7 @@
         </is>
       </c>
       <c r="B82" t="n">
-        <v>11500000</v>
+        <v>4725000</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -2066,7 +2066,7 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>https://terreno.mercadolibre.com.mx/MLM-4080259510-terreno-en-venta-en-san-martin-toltepec-toluca-mexico-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=33&amp;type=item&amp;tracking_id=ee737872-1b04-44c7-b466-ef90db8b4927&amp;price_drop=not_apply</t>
+          <t>https://terreno.mercadolibre.com.mx/MLM-2318168399-terreno-en-venta-en-cacalomacan-a-2-cuadras-de-jinetes-cerca-de-calz-pacifico-y-colegio-paideia-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=33&amp;type=item&amp;tracking_id=0b5ffd07-b636-4489-bf5a-81c4a52af9df&amp;price_drop=not_apply</t>
         </is>
       </c>
     </row>
@@ -2077,7 +2077,7 @@
         </is>
       </c>
       <c r="B83" t="n">
-        <v>1840590</v>
+        <v>11500000</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -2086,7 +2086,7 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>https://terreno.mercadolibre.com.mx/MLM-4080239968-terreno-en-venta-toluca-cerca-del-aeropuerto-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=34&amp;type=item&amp;tracking_id=ee737872-1b04-44c7-b466-ef90db8b4927&amp;price_drop=not_apply</t>
+          <t>https://terreno.mercadolibre.com.mx/MLM-4080259510-terreno-en-venta-en-san-martin-toltepec-toluca-mexico-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=34&amp;type=item&amp;tracking_id=0b5ffd07-b636-4489-bf5a-81c4a52af9df&amp;price_drop=not_apply</t>
         </is>
       </c>
     </row>
@@ -2097,7 +2097,7 @@
         </is>
       </c>
       <c r="B84" t="n">
-        <v>8500000</v>
+        <v>1840590</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -2106,7 +2106,7 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>https://terreno.mercadolibre.com.mx/MLM-2343423083-terreno-en-san-pedro-totoltepec-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=35&amp;type=item&amp;tracking_id=ee737872-1b04-44c7-b466-ef90db8b4927&amp;price_drop=not_apply</t>
+          <t>https://terreno.mercadolibre.com.mx/MLM-4080239968-terreno-en-venta-toluca-cerca-del-aeropuerto-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=35&amp;type=item&amp;tracking_id=0b5ffd07-b636-4489-bf5a-81c4a52af9df&amp;price_drop=not_apply</t>
         </is>
       </c>
     </row>
@@ -2117,7 +2117,7 @@
         </is>
       </c>
       <c r="B85" t="n">
-        <v>35000000</v>
+        <v>8500000</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -2126,7 +2126,7 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>https://terreno.mercadolibre.com.mx/MLM-2370231281-terreno-en-venta-en-toluca-reforma-y-ferr-nac-independencia-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=36&amp;type=item&amp;tracking_id=ee737872-1b04-44c7-b466-ef90db8b4927&amp;price_drop=not_apply</t>
+          <t>https://terreno.mercadolibre.com.mx/MLM-2343423083-terreno-en-san-pedro-totoltepec-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=36&amp;type=item&amp;tracking_id=0b5ffd07-b636-4489-bf5a-81c4a52af9df&amp;price_drop=not_apply</t>
         </is>
       </c>
     </row>
@@ -2137,7 +2137,7 @@
         </is>
       </c>
       <c r="B86" t="n">
-        <v>2450000</v>
+        <v>35000000</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -2146,7 +2146,7 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>https://terreno.mercadolibre.com.mx/MLM-2343569515-terreno-en-santa-maria-totoltepec-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=37&amp;type=item&amp;tracking_id=ee737872-1b04-44c7-b466-ef90db8b4927&amp;price_drop=not_apply</t>
+          <t>https://terreno.mercadolibre.com.mx/MLM-2370231281-terreno-en-venta-en-toluca-reforma-y-ferr-nac-independencia-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=37&amp;type=item&amp;tracking_id=0b5ffd07-b636-4489-bf5a-81c4a52af9df&amp;price_drop=not_apply</t>
         </is>
       </c>
     </row>
@@ -2157,7 +2157,7 @@
         </is>
       </c>
       <c r="B87" t="n">
-        <v>50000000</v>
+        <v>2450000</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -2166,7 +2166,7 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>https://terreno.mercadolibre.com.mx/MLM-4558160588-terreno-en-venta-en-cipres-toluca-estado-de-mexico-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=38&amp;type=item&amp;tracking_id=ee737872-1b04-44c7-b466-ef90db8b4927&amp;price_drop=not_apply</t>
+          <t>https://terreno.mercadolibre.com.mx/MLM-2343569515-terreno-en-santa-maria-totoltepec-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=38&amp;type=item&amp;tracking_id=0b5ffd07-b636-4489-bf5a-81c4a52af9df&amp;price_drop=not_apply</t>
         </is>
       </c>
     </row>
@@ -2177,7 +2177,7 @@
         </is>
       </c>
       <c r="B88" t="n">
-        <v>203547204</v>
+        <v>50000000</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -2186,7 +2186,7 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>https://terreno.mercadolibre.com.mx/MLM-4261794654-terreno-en-venta-en-industrial-en-toluca-estado-de-mexico-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=39&amp;type=item&amp;tracking_id=ee737872-1b04-44c7-b466-ef90db8b4927&amp;price_drop=not_apply</t>
+          <t>https://terreno.mercadolibre.com.mx/MLM-4558160588-terreno-en-venta-en-cipres-toluca-estado-de-mexico-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=39&amp;type=item&amp;tracking_id=0b5ffd07-b636-4489-bf5a-81c4a52af9df&amp;price_drop=not_apply</t>
         </is>
       </c>
     </row>
@@ -2197,7 +2197,7 @@
         </is>
       </c>
       <c r="B89" t="n">
-        <v>14571000</v>
+        <v>203547204</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -2206,7 +2206,7 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>https://terreno.mercadolibre.com.mx/MLM-4261807760-se-vende-terreno-carretera-mexico-toluca-lerma-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=40&amp;type=item&amp;tracking_id=ee737872-1b04-44c7-b466-ef90db8b4927&amp;price_drop=not_apply</t>
+          <t>https://terreno.mercadolibre.com.mx/MLM-4261794654-terreno-en-venta-en-industrial-en-toluca-estado-de-mexico-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=40&amp;type=item&amp;tracking_id=0b5ffd07-b636-4489-bf5a-81c4a52af9df&amp;price_drop=not_apply</t>
         </is>
       </c>
     </row>
@@ -2217,7 +2217,7 @@
         </is>
       </c>
       <c r="B90" t="n">
-        <v>222618909</v>
+        <v>14571000</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -2226,7 +2226,7 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>https://terreno.mercadolibre.com.mx/MLM-4261859654-terreno-en-venta-industrial-en-toluca-estado-de-mexico-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=41&amp;type=item&amp;tracking_id=ee737872-1b04-44c7-b466-ef90db8b4927&amp;price_drop=not_apply</t>
+          <t>https://terreno.mercadolibre.com.mx/MLM-4261807760-se-vende-terreno-carretera-mexico-toluca-lerma-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=41&amp;type=item&amp;tracking_id=0b5ffd07-b636-4489-bf5a-81c4a52af9df&amp;price_drop=not_apply</t>
         </is>
       </c>
     </row>
@@ -2237,7 +2237,7 @@
         </is>
       </c>
       <c r="B91" t="n">
-        <v>1870000</v>
+        <v>222618909</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -2246,7 +2246,7 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>https://terreno.mercadolibre.com.mx/MLM-2811993671-terreno-en-venta-en-residencial-hacienda-san-jose-en-toluca-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=42&amp;type=item&amp;float_highlight=recent_publication&amp;tracking_id=ee737872-1b04-44c7-b466-ef90db8b4927&amp;price_drop=not_apply</t>
+          <t>https://terreno.mercadolibre.com.mx/MLM-4261859654-terreno-en-venta-industrial-en-toluca-estado-de-mexico-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=42&amp;type=item&amp;tracking_id=0b5ffd07-b636-4489-bf5a-81c4a52af9df&amp;price_drop=not_apply</t>
         </is>
       </c>
     </row>
@@ -2257,7 +2257,7 @@
         </is>
       </c>
       <c r="B92" t="n">
-        <v>700000</v>
+        <v>1870000</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -2266,7 +2266,7 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>https://terreno.mercadolibre.com.mx/MLM-5058024988-terreno-en-venta-en-san-lorenzo-tepaltitlan-toluca-estado-de-mexico-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=43&amp;type=item&amp;float_highlight=recent_publication&amp;tracking_id=ee737872-1b04-44c7-b466-ef90db8b4927&amp;price_drop=not_apply</t>
+          <t>https://terreno.mercadolibre.com.mx/MLM-2811993671-terreno-en-venta-en-residencial-hacienda-san-jose-en-toluca-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=43&amp;type=item&amp;float_highlight=recent_publication&amp;tracking_id=0b5ffd07-b636-4489-bf5a-81c4a52af9df&amp;price_drop=not_apply</t>
         </is>
       </c>
     </row>
@@ -2277,7 +2277,7 @@
         </is>
       </c>
       <c r="B93" t="n">
-        <v>3240000</v>
+        <v>132000000</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -2286,7 +2286,7 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>https://terreno.mercadolibre.com.mx/MLM-5058177406-terreno-en-venta-en-san-francisco-totoltepec-toluca-estado-de-mexico-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=44&amp;type=item&amp;float_highlight=recent_publication&amp;tracking_id=ee737872-1b04-44c7-b466-ef90db8b4927&amp;price_drop=not_apply</t>
+          <t>https://terreno.mercadolibre.com.mx/MLM-5064030156-terreno-en-venta-en-parque-industrial-el-coecillo-toluca-estado-de-mexico-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=44&amp;type=item&amp;float_highlight=recent_publication&amp;tracking_id=0b5ffd07-b636-4489-bf5a-81c4a52af9df&amp;price_drop=not_apply</t>
         </is>
       </c>
     </row>
@@ -2297,7 +2297,7 @@
         </is>
       </c>
       <c r="B94" t="n">
-        <v>132000000</v>
+        <v>279450</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -2306,7 +2306,7 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>https://terreno.mercadolibre.com.mx/MLM-5064030156-terreno-en-venta-en-parque-industrial-el-coecillo-toluca-estado-de-mexico-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=45&amp;type=item&amp;float_highlight=recent_publication&amp;tracking_id=ee737872-1b04-44c7-b466-ef90db8b4927&amp;price_drop=not_apply</t>
+          <t>https://terreno.mercadolibre.com.mx/MLM-5060346586-ultimos-2-lotes-en-venta-en-san-cayetano-muy-cerca-de-la-unsa-en-toluca-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=45&amp;type=item&amp;float_highlight=recent_publication&amp;tracking_id=0b5ffd07-b636-4489-bf5a-81c4a52af9df&amp;price_drop=not_apply</t>
         </is>
       </c>
     </row>
@@ -2317,7 +2317,7 @@
         </is>
       </c>
       <c r="B95" t="n">
-        <v>279450</v>
+        <v>23500000</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -2326,7 +2326,7 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>https://terreno.mercadolibre.com.mx/MLM-5060346586-ultimos-2-lotes-en-venta-en-san-cayetano-muy-cerca-de-la-unsa-en-toluca-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=46&amp;type=item&amp;float_highlight=recent_publication&amp;tracking_id=ee737872-1b04-44c7-b466-ef90db8b4927&amp;price_drop=not_apply</t>
+          <t>https://terreno.mercadolibre.com.mx/MLM-4950598656-terreno-comercial-en-venta-en-san-bernardino-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=46&amp;type=item&amp;tracking_id=0b5ffd07-b636-4489-bf5a-81c4a52af9df&amp;price_drop=not_apply</t>
         </is>
       </c>
     </row>
@@ -2337,7 +2337,7 @@
         </is>
       </c>
       <c r="B96" t="n">
-        <v>9215400</v>
+        <v>8760000</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -2346,7 +2346,7 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>https://terreno.mercadolibre.com.mx/MLM-5047581202-terreno-comercial-en-venta-en-santa-cruz-otzacatipan-toluca-mexico-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=47&amp;type=item&amp;float_highlight=recent_publication&amp;tracking_id=ee737872-1b04-44c7-b466-ef90db8b4927&amp;price_drop=not_apply</t>
+          <t>https://terreno.mercadolibre.com.mx/MLM-4761562052-terreno-comercial-en-venta-en-santa-maria-totoltepec-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=47&amp;type=item&amp;tracking_id=0b5ffd07-b636-4489-bf5a-81c4a52af9df&amp;price_drop=not_apply</t>
         </is>
       </c>
     </row>
@@ -2357,7 +2357,7 @@
         </is>
       </c>
       <c r="B97" t="n">
-        <v>8502990</v>
+        <v>26320000</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -2366,7 +2366,7 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>https://terreno.mercadolibre.com.mx/MLM-5047581198-terreno-comercial-en-venta-en-santa-cruz-otzacatipan-toluca-mexico-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=48&amp;type=item&amp;float_highlight=recent_publication&amp;tracking_id=ee737872-1b04-44c7-b466-ef90db8b4927&amp;price_drop=not_apply</t>
+          <t>https://terreno.mercadolibre.com.mx/MLM-4790443980-terreno-residencial-en-venta-en-la-venta-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=48&amp;type=item&amp;tracking_id=0b5ffd07-b636-4489-bf5a-81c4a52af9df&amp;price_drop=not_apply</t>
         </is>
       </c>
     </row>
@@ -2386,7 +2386,7 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>https://terreno.mercadolibre.com.mx/MLM-3835159420-lotes-de-terreno-desde-104-m2-en-venta-cerca-del-aeropuerto-de-toluca-en-la-constitucion-toltepec-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=1&amp;type=item&amp;tracking_id=83833016-059e-4410-b009-268e9b9166c7&amp;price_drop=not_apply</t>
+          <t>https://terreno.mercadolibre.com.mx/MLM-3835159420-lotes-de-terreno-desde-104-m2-en-venta-cerca-del-aeropuerto-de-toluca-en-la-constitucion-toltepec-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=1&amp;type=item&amp;tracking_id=3fb6d42b-4d65-4353-9cbe-760b5a922e09&amp;price_drop=not_apply</t>
         </is>
       </c>
     </row>
@@ -2406,7 +2406,7 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>https://terreno.mercadolibre.com.mx/MLM-2810992285-construye-tu-residencia-en-la-zona-de-mayor-proyeccion-de-toluca-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=2&amp;type=item&amp;float_highlight=recent_publication&amp;tracking_id=83833016-059e-4410-b009-268e9b9166c7&amp;price_drop=not_apply</t>
+          <t>https://terreno.mercadolibre.com.mx/MLM-2810992285-construye-tu-residencia-en-la-zona-de-mayor-proyeccion-de-toluca-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=2&amp;type=item&amp;float_highlight=recent_publication&amp;tracking_id=3fb6d42b-4d65-4353-9cbe-760b5a922e09&amp;price_drop=not_apply</t>
         </is>
       </c>
     </row>
@@ -2426,7 +2426,7 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>https://terreno.mercadolibre.com.mx/MLM-3847495816-el-mejor-terreno-del-condominio-puede-ser-tuyo-a-un-precio-de-oportunidad-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=3&amp;type=item&amp;tracking_id=83833016-059e-4410-b009-268e9b9166c7&amp;price_drop=not_apply</t>
+          <t>https://terreno.mercadolibre.com.mx/MLM-3847495816-el-mejor-terreno-del-condominio-puede-ser-tuyo-a-un-precio-de-oportunidad-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=3&amp;type=item&amp;tracking_id=3fb6d42b-4d65-4353-9cbe-760b5a922e09&amp;price_drop=not_apply</t>
         </is>
       </c>
     </row>
@@ -2437,7 +2437,7 @@
         </is>
       </c>
       <c r="B101" t="n">
-        <v>7600000</v>
+        <v>649000</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
@@ -2446,7 +2446,7 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>https://terreno.mercadolibre.com.mx/MLM-2231593183-terreno-en-venta-en-san-mateo-oxtotitlan-toluca-mexico-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=4&amp;type=item&amp;tracking_id=83833016-059e-4410-b009-268e9b9166c7&amp;price_drop=not_apply</t>
+          <t>https://terreno.mercadolibre.com.mx/MLM-2753915589-terreno-bardeado-en-cacalomacan-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=4&amp;type=item&amp;tracking_id=3fb6d42b-4d65-4353-9cbe-760b5a922e09&amp;price_drop=false</t>
         </is>
       </c>
     </row>
@@ -2457,7 +2457,7 @@
         </is>
       </c>
       <c r="B102" t="n">
-        <v>649000</v>
+        <v>7600000</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -2466,7 +2466,7 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>https://terreno.mercadolibre.com.mx/MLM-2753915589-terreno-bardeado-en-cacalomacan-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=5&amp;type=item&amp;tracking_id=83833016-059e-4410-b009-268e9b9166c7&amp;price_drop=false</t>
+          <t>https://terreno.mercadolibre.com.mx/MLM-2231593183-terreno-en-venta-en-san-mateo-oxtotitlan-toluca-mexico-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=5&amp;type=item&amp;tracking_id=3fb6d42b-4d65-4353-9cbe-760b5a922e09&amp;price_drop=not_apply</t>
         </is>
       </c>
     </row>
@@ -2486,7 +2486,7 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>https://terreno.mercadolibre.com.mx/MLM-2716356593-terreno-en-venta-en-colonia-nueva-santa-maria-de-las-rosas-toluca-estado-de-mexico-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=6&amp;type=item&amp;tracking_id=83833016-059e-4410-b009-268e9b9166c7&amp;price_drop=not_apply</t>
+          <t>https://terreno.mercadolibre.com.mx/MLM-2716356593-terreno-en-venta-en-colonia-nueva-santa-maria-de-las-rosas-toluca-estado-de-mexico-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=6&amp;type=item&amp;tracking_id=3fb6d42b-4d65-4353-9cbe-760b5a922e09&amp;price_drop=not_apply</t>
         </is>
       </c>
     </row>
@@ -2506,7 +2506,7 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>https://terreno.mercadolibre.com.mx/MLM-4660497978-terreno-en-venta-en-toluca-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=7&amp;type=item&amp;tracking_id=83833016-059e-4410-b009-268e9b9166c7&amp;price_drop=not_apply</t>
+          <t>https://terreno.mercadolibre.com.mx/MLM-4660497978-terreno-en-venta-en-toluca-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=7&amp;type=item&amp;tracking_id=3fb6d42b-4d65-4353-9cbe-760b5a922e09&amp;price_drop=not_apply</t>
         </is>
       </c>
     </row>
@@ -2526,7 +2526,7 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>https://terreno.mercadolibre.com.mx/MLM-4388186170-terreno-industrial-en-venta-en-toluca-san-cayetano-a-un-lado-de-la-caseta-el-dorado-cerca-puerta-mexico-recinto-aduanal-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=8&amp;type=item&amp;tracking_id=83833016-059e-4410-b009-268e9b9166c7&amp;price_drop=not_apply</t>
+          <t>https://terreno.mercadolibre.com.mx/MLM-4388186170-terreno-industrial-en-venta-en-toluca-san-cayetano-a-un-lado-de-la-caseta-el-dorado-cerca-puerta-mexico-recinto-aduanal-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=8&amp;type=item&amp;tracking_id=3fb6d42b-4d65-4353-9cbe-760b5a922e09&amp;price_drop=not_apply</t>
         </is>
       </c>
     </row>
@@ -2546,7 +2546,7 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>https://terreno.mercadolibre.com.mx/MLM-2716629645-terreno-industrial-en-venta-en-palmillas-son-13-hectareas-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=9&amp;type=item&amp;tracking_id=83833016-059e-4410-b009-268e9b9166c7&amp;price_drop=not_apply</t>
+          <t>https://terreno.mercadolibre.com.mx/MLM-2716629645-terreno-industrial-en-venta-en-palmillas-son-13-hectareas-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=9&amp;type=item&amp;tracking_id=3fb6d42b-4d65-4353-9cbe-760b5a922e09&amp;price_drop=not_apply</t>
         </is>
       </c>
     </row>
@@ -2566,7 +2566,7 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>https://terreno.mercadolibre.com.mx/MLM-2748643873-terreno-en-venta-a-pie-de-carretera-toluca-atlacomulco-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=10&amp;type=item&amp;tracking_id=83833016-059e-4410-b009-268e9b9166c7&amp;price_drop=not_apply</t>
+          <t>https://terreno.mercadolibre.com.mx/MLM-2748643873-terreno-en-venta-a-pie-de-carretera-toluca-atlacomulco-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=10&amp;type=item&amp;tracking_id=3fb6d42b-4d65-4353-9cbe-760b5a922e09&amp;price_drop=not_apply</t>
         </is>
       </c>
     </row>
@@ -2586,7 +2586,7 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>https://terreno.mercadolibre.com.mx/MLM-4790479866-terreno-regular-con-infraestructura-lista-base-solida-para-tu-proyecto-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=11&amp;type=item&amp;tracking_id=83833016-059e-4410-b009-268e9b9166c7&amp;price_drop=not_apply</t>
+          <t>https://terreno.mercadolibre.com.mx/MLM-4790479866-terreno-regular-con-infraestructura-lista-base-solida-para-tu-proyecto-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=11&amp;type=item&amp;tracking_id=3fb6d42b-4d65-4353-9cbe-760b5a922e09&amp;price_drop=not_apply</t>
         </is>
       </c>
     </row>
@@ -2606,7 +2606,7 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>https://terreno.mercadolibre.com.mx/MLM-5015164202-venta-terreno-lotes-palmillas-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=12&amp;type=item&amp;tracking_id=83833016-059e-4410-b009-268e9b9166c7&amp;price_drop=not_apply</t>
+          <t>https://terreno.mercadolibre.com.mx/MLM-5015164202-venta-terreno-lotes-palmillas-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=12&amp;type=item&amp;tracking_id=3fb6d42b-4d65-4353-9cbe-760b5a922e09&amp;price_drop=not_apply</t>
         </is>
       </c>
     </row>
@@ -2626,7 +2626,7 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>https://terreno.mercadolibre.com.mx/MLM-4416680104-terreno-en-venta-sobre-calzada-del-pacifico-cacalomacan-por-ocho-cedros-toluca-cas-23000-m2-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=13&amp;type=item&amp;tracking_id=83833016-059e-4410-b009-268e9b9166c7&amp;price_drop=not_apply</t>
+          <t>https://terreno.mercadolibre.com.mx/MLM-4416680104-terreno-en-venta-sobre-calzada-del-pacifico-cacalomacan-por-ocho-cedros-toluca-cas-23000-m2-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=13&amp;type=item&amp;tracking_id=3fb6d42b-4d65-4353-9cbe-760b5a922e09&amp;price_drop=not_apply</t>
         </is>
       </c>
     </row>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>https://terreno.mercadolibre.com.mx/MLM-2736455271-terreno-de-2-hectareas-en-zona-urbana-santa-maria-totoltepec-estado-de-mexico-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=14&amp;type=item&amp;tracking_id=83833016-059e-4410-b009-268e9b9166c7&amp;price_drop=not_apply</t>
+          <t>https://terreno.mercadolibre.com.mx/MLM-2736455271-terreno-de-2-hectareas-en-zona-urbana-santa-maria-totoltepec-estado-de-mexico-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=14&amp;type=item&amp;tracking_id=3fb6d42b-4d65-4353-9cbe-760b5a922e09&amp;price_drop=not_apply</t>
         </is>
       </c>
     </row>
@@ -2657,7 +2657,7 @@
         </is>
       </c>
       <c r="B112" t="n">
-        <v>1831680</v>
+        <v>299999</v>
       </c>
       <c r="C112" t="inlineStr">
         <is>
@@ -2666,7 +2666,7 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>https://terreno.mercadolibre.com.mx/MLM-2804712255-venta-terreno-paraje-san-rafael-en-toluca-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=15&amp;type=item&amp;float_highlight=recent_publication&amp;tracking_id=83833016-059e-4410-b009-268e9b9166c7&amp;price_drop=not_apply</t>
+          <t>https://terreno.mercadolibre.com.mx/MLM-5082958514-lotes-a-10-min-de-paideia-propiedad-desde-230-m-en-adelante-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=15&amp;type=item&amp;float_highlight=recent_publication&amp;tracking_id=3fb6d42b-4d65-4353-9cbe-760b5a922e09&amp;price_drop=not_apply</t>
         </is>
       </c>
     </row>
@@ -2677,7 +2677,7 @@
         </is>
       </c>
       <c r="B113" t="n">
-        <v>1485000</v>
+        <v>1831680</v>
       </c>
       <c r="C113" t="inlineStr">
         <is>
@@ -2686,7 +2686,7 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>https://terreno.mercadolibre.com.mx/MLM-2187928841-venta-terreno-cerrillo-vista-hermosa-toluca-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=16&amp;type=item&amp;tracking_id=83833016-059e-4410-b009-268e9b9166c7&amp;price_drop=not_apply</t>
+          <t>https://terreno.mercadolibre.com.mx/MLM-2804712255-venta-terreno-paraje-san-rafael-en-toluca-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=16&amp;type=item&amp;float_highlight=recent_publication&amp;tracking_id=3fb6d42b-4d65-4353-9cbe-760b5a922e09&amp;price_drop=not_apply</t>
         </is>
       </c>
     </row>
@@ -2697,7 +2697,7 @@
         </is>
       </c>
       <c r="B114" t="n">
-        <v>4805040</v>
+        <v>1485000</v>
       </c>
       <c r="C114" t="inlineStr">
         <is>
@@ -2706,7 +2706,7 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>https://terreno.mercadolibre.com.mx/MLM-3705026808-venta-de-terreno-en-cacalomacan-a-20-min-centro-toluca-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=17&amp;type=item&amp;tracking_id=83833016-059e-4410-b009-268e9b9166c7&amp;price_drop=not_apply</t>
+          <t>https://terreno.mercadolibre.com.mx/MLM-2187928841-venta-terreno-cerrillo-vista-hermosa-toluca-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=17&amp;type=item&amp;tracking_id=3fb6d42b-4d65-4353-9cbe-760b5a922e09&amp;price_drop=not_apply</t>
         </is>
       </c>
     </row>
@@ -2717,7 +2717,7 @@
         </is>
       </c>
       <c r="B115" t="n">
-        <v>1920000</v>
+        <v>4805040</v>
       </c>
       <c r="C115" t="inlineStr">
         <is>
@@ -2726,7 +2726,7 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>https://terreno.mercadolibre.com.mx/MLM-4119789692-terreno-en-venta-residencial-ex-hacienda-san-jose-toluca-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=18&amp;type=item&amp;tracking_id=83833016-059e-4410-b009-268e9b9166c7&amp;price_drop=not_apply</t>
+          <t>https://terreno.mercadolibre.com.mx/MLM-3705026808-venta-de-terreno-en-cacalomacan-a-20-min-centro-toluca-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=18&amp;type=item&amp;tracking_id=3fb6d42b-4d65-4353-9cbe-760b5a922e09&amp;price_drop=not_apply</t>
         </is>
       </c>
     </row>
@@ -2737,7 +2737,7 @@
         </is>
       </c>
       <c r="B116" t="n">
-        <v>1244380</v>
+        <v>1920000</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
@@ -2746,7 +2746,7 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>https://terreno.mercadolibre.com.mx/MLM-4826508826-venta-de-lote-de-terreno-residencial-cerca-de-galerias-metepec-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=19&amp;type=item&amp;tracking_id=83833016-059e-4410-b009-268e9b9166c7&amp;price_drop=not_apply</t>
+          <t>https://terreno.mercadolibre.com.mx/MLM-4119789692-terreno-en-venta-residencial-ex-hacienda-san-jose-toluca-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=19&amp;type=item&amp;tracking_id=3fb6d42b-4d65-4353-9cbe-760b5a922e09&amp;price_drop=not_apply</t>
         </is>
       </c>
     </row>
@@ -2757,7 +2757,7 @@
         </is>
       </c>
       <c r="B117" t="n">
-        <v>8565858</v>
+        <v>1244380</v>
       </c>
       <c r="C117" t="inlineStr">
         <is>
@@ -2766,7 +2766,7 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>https://terreno.mercadolibre.com.mx/MLM-4080298834-terreno-en-venta-en-san-miguel-zacango-toluca-mexico-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=20&amp;type=item&amp;tracking_id=83833016-059e-4410-b009-268e9b9166c7&amp;price_drop=not_apply</t>
+          <t>https://terreno.mercadolibre.com.mx/MLM-4826508826-venta-de-lote-de-terreno-residencial-cerca-de-galerias-metepec-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=20&amp;type=item&amp;tracking_id=3fb6d42b-4d65-4353-9cbe-760b5a922e09&amp;price_drop=not_apply</t>
         </is>
       </c>
     </row>
@@ -2777,7 +2777,7 @@
         </is>
       </c>
       <c r="B118" t="n">
-        <v>8500000</v>
+        <v>8565858</v>
       </c>
       <c r="C118" t="inlineStr">
         <is>
@@ -2786,7 +2786,7 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>https://terreno.mercadolibre.com.mx/MLM-2310439697-se-vende-terreno-en-toluca-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=21&amp;type=item&amp;tracking_id=83833016-059e-4410-b009-268e9b9166c7&amp;price_drop=not_apply</t>
+          <t>https://terreno.mercadolibre.com.mx/MLM-4080298834-terreno-en-venta-en-san-miguel-zacango-toluca-mexico-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=21&amp;type=item&amp;tracking_id=3fb6d42b-4d65-4353-9cbe-760b5a922e09&amp;price_drop=not_apply</t>
         </is>
       </c>
     </row>
@@ -2797,7 +2797,7 @@
         </is>
       </c>
       <c r="B119" t="n">
-        <v>1300000</v>
+        <v>8500000</v>
       </c>
       <c r="C119" t="inlineStr">
         <is>
@@ -2806,7 +2806,7 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>https://terreno.mercadolibre.com.mx/MLM-4495237624-lote-disponible-en-conjunto-ambar-toluca-edo-mex-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=22&amp;type=item&amp;tracking_id=83833016-059e-4410-b009-268e9b9166c7&amp;price_drop=not_apply</t>
+          <t>https://terreno.mercadolibre.com.mx/MLM-2310439697-se-vende-terreno-en-toluca-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=22&amp;type=item&amp;tracking_id=3fb6d42b-4d65-4353-9cbe-760b5a922e09&amp;price_drop=not_apply</t>
         </is>
       </c>
     </row>
@@ -2817,7 +2817,7 @@
         </is>
       </c>
       <c r="B120" t="n">
-        <v>1200000</v>
+        <v>1300000</v>
       </c>
       <c r="C120" t="inlineStr">
         <is>
@@ -2826,7 +2826,7 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>https://terreno.mercadolibre.com.mx/MLM-2485559517-terreno-en-venta-en-toluca-san-andres-cuexcontitlan-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=23&amp;type=item&amp;tracking_id=83833016-059e-4410-b009-268e9b9166c7&amp;price_drop=not_apply</t>
+          <t>https://terreno.mercadolibre.com.mx/MLM-4495237624-lote-disponible-en-conjunto-ambar-toluca-edo-mex-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=23&amp;type=item&amp;tracking_id=3fb6d42b-4d65-4353-9cbe-760b5a922e09&amp;price_drop=not_apply</t>
         </is>
       </c>
     </row>
@@ -2837,7 +2837,7 @@
         </is>
       </c>
       <c r="B121" t="n">
-        <v>38634000</v>
+        <v>1200000</v>
       </c>
       <c r="C121" t="inlineStr">
         <is>
@@ -2846,7 +2846,7 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>https://terreno.mercadolibre.com.mx/MLM-2431684449-terreno-en-toluca-25756-m2-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=24&amp;type=item&amp;tracking_id=83833016-059e-4410-b009-268e9b9166c7&amp;price_drop=not_apply</t>
+          <t>https://terreno.mercadolibre.com.mx/MLM-2485559517-terreno-en-venta-en-toluca-san-andres-cuexcontitlan-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=24&amp;type=item&amp;tracking_id=3fb6d42b-4d65-4353-9cbe-760b5a922e09&amp;price_drop=not_apply</t>
         </is>
       </c>
     </row>
@@ -2857,7 +2857,7 @@
         </is>
       </c>
       <c r="B122" t="n">
-        <v>5625000</v>
+        <v>38634000</v>
       </c>
       <c r="C122" t="inlineStr">
         <is>
@@ -2866,7 +2866,7 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>https://terreno.mercadolibre.com.mx/MLM-2323267483-terreno-en-venta-2250m2-en-san-felipe-tlalmimilolpan-toluca-mexico-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=25&amp;type=item&amp;tracking_id=83833016-059e-4410-b009-268e9b9166c7&amp;price_drop=not_apply</t>
+          <t>https://terreno.mercadolibre.com.mx/MLM-2431684449-terreno-en-toluca-25756-m2-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=25&amp;type=item&amp;tracking_id=3fb6d42b-4d65-4353-9cbe-760b5a922e09&amp;price_drop=not_apply</t>
         </is>
       </c>
     </row>
@@ -2877,7 +2877,7 @@
         </is>
       </c>
       <c r="B123" t="n">
-        <v>25650000</v>
+        <v>5625000</v>
       </c>
       <c r="C123" t="inlineStr">
         <is>
@@ -2886,7 +2886,7 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>https://terreno.mercadolibre.com.mx/MLM-4169951646-terreno-en-venta-por-las-torres-toluca-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=26&amp;type=item&amp;tracking_id=83833016-059e-4410-b009-268e9b9166c7&amp;price_drop=not_apply</t>
+          <t>https://terreno.mercadolibre.com.mx/MLM-2323267483-terreno-en-venta-2250m2-en-san-felipe-tlalmimilolpan-toluca-mexico-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=26&amp;type=item&amp;tracking_id=3fb6d42b-4d65-4353-9cbe-760b5a922e09&amp;price_drop=not_apply</t>
         </is>
       </c>
     </row>
@@ -2897,7 +2897,7 @@
         </is>
       </c>
       <c r="B124" t="n">
-        <v>4800000</v>
+        <v>25650000</v>
       </c>
       <c r="C124" t="inlineStr">
         <is>
@@ -2906,7 +2906,7 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>https://terreno.mercadolibre.com.mx/MLM-4416373342-terreno-en-venta-en-san-lorenzo-tepaltitlan-centro-toluca-mexico-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=27&amp;type=item&amp;tracking_id=83833016-059e-4410-b009-268e9b9166c7&amp;price_drop=not_apply</t>
+          <t>https://terreno.mercadolibre.com.mx/MLM-4169951646-terreno-en-venta-por-las-torres-toluca-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=27&amp;type=item&amp;tracking_id=3fb6d42b-4d65-4353-9cbe-760b5a922e09&amp;price_drop=not_apply</t>
         </is>
       </c>
     </row>
@@ -2917,7 +2917,7 @@
         </is>
       </c>
       <c r="B125" t="n">
-        <v>14490000</v>
+        <v>4800000</v>
       </c>
       <c r="C125" t="inlineStr">
         <is>
@@ -2926,7 +2926,7 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>https://terreno.mercadolibre.com.mx/MLM-2584697469-oportunidad-de-inversion-terreno-de-9993-m-cerca-de-parque-toluca-2000-ideal-para-naves-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=28&amp;type=item&amp;tracking_id=83833016-059e-4410-b009-268e9b9166c7&amp;price_drop=not_apply</t>
+          <t>https://terreno.mercadolibre.com.mx/MLM-4416373342-terreno-en-venta-en-san-lorenzo-tepaltitlan-centro-toluca-mexico-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=28&amp;type=item&amp;tracking_id=3fb6d42b-4d65-4353-9cbe-760b5a922e09&amp;price_drop=not_apply</t>
         </is>
       </c>
     </row>
@@ -2937,7 +2937,7 @@
         </is>
       </c>
       <c r="B126" t="n">
-        <v>24520000</v>
+        <v>14490000</v>
       </c>
       <c r="C126" t="inlineStr">
         <is>
@@ -2946,7 +2946,7 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>https://terreno.mercadolibre.com.mx/MLM-4169951774-terreno-en-venta-por-las-torres-toluca-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=29&amp;type=item&amp;tracking_id=83833016-059e-4410-b009-268e9b9166c7&amp;price_drop=not_apply</t>
+          <t>https://terreno.mercadolibre.com.mx/MLM-2584697469-oportunidad-de-inversion-terreno-de-9993-m-cerca-de-parque-toluca-2000-ideal-para-naves-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=29&amp;type=item&amp;tracking_id=3fb6d42b-4d65-4353-9cbe-760b5a922e09&amp;price_drop=not_apply</t>
         </is>
       </c>
     </row>
@@ -2957,7 +2957,7 @@
         </is>
       </c>
       <c r="B127" t="n">
-        <v>12024000</v>
+        <v>24520000</v>
       </c>
       <c r="C127" t="inlineStr">
         <is>
@@ -2966,7 +2966,7 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>https://terreno.mercadolibre.com.mx/MLM-2323192153-terreno-en-venta-8016-m2-en-san-felipe-tlalmimilolpan-toluca-mexico-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=30&amp;type=item&amp;tracking_id=83833016-059e-4410-b009-268e9b9166c7&amp;price_drop=not_apply</t>
+          <t>https://terreno.mercadolibre.com.mx/MLM-4169951774-terreno-en-venta-por-las-torres-toluca-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=30&amp;type=item&amp;tracking_id=3fb6d42b-4d65-4353-9cbe-760b5a922e09&amp;price_drop=not_apply</t>
         </is>
       </c>
     </row>
@@ -2977,7 +2977,7 @@
         </is>
       </c>
       <c r="B128" t="n">
-        <v>13650000</v>
+        <v>12024000</v>
       </c>
       <c r="C128" t="inlineStr">
         <is>
@@ -2986,7 +2986,7 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>https://terreno.mercadolibre.com.mx/MLM-2487732477-terreno-en-venta-por-las-torres-toluca-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=31&amp;type=item&amp;tracking_id=83833016-059e-4410-b009-268e9b9166c7&amp;price_drop=not_apply</t>
+          <t>https://terreno.mercadolibre.com.mx/MLM-2323192153-terreno-en-venta-8016-m2-en-san-felipe-tlalmimilolpan-toluca-mexico-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=31&amp;type=item&amp;tracking_id=3fb6d42b-4d65-4353-9cbe-760b5a922e09&amp;price_drop=not_apply</t>
         </is>
       </c>
     </row>
@@ -2997,7 +2997,7 @@
         </is>
       </c>
       <c r="B129" t="n">
-        <v>4725000</v>
+        <v>13650000</v>
       </c>
       <c r="C129" t="inlineStr">
         <is>
@@ -3006,7 +3006,7 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>https://terreno.mercadolibre.com.mx/MLM-2318168399-terreno-en-venta-en-cacalomacan-a-2-cuadras-de-jinetes-cerca-de-calz-pacifico-y-colegio-paideia-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=32&amp;type=item&amp;tracking_id=83833016-059e-4410-b009-268e9b9166c7&amp;price_drop=not_apply</t>
+          <t>https://terreno.mercadolibre.com.mx/MLM-2487732477-terreno-en-venta-por-las-torres-toluca-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=32&amp;type=item&amp;tracking_id=3fb6d42b-4d65-4353-9cbe-760b5a922e09&amp;price_drop=not_apply</t>
         </is>
       </c>
     </row>
@@ -3017,7 +3017,7 @@
         </is>
       </c>
       <c r="B130" t="n">
-        <v>11500000</v>
+        <v>4725000</v>
       </c>
       <c r="C130" t="inlineStr">
         <is>
@@ -3026,7 +3026,7 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>https://terreno.mercadolibre.com.mx/MLM-4080259510-terreno-en-venta-en-san-martin-toltepec-toluca-mexico-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=33&amp;type=item&amp;tracking_id=83833016-059e-4410-b009-268e9b9166c7&amp;price_drop=not_apply</t>
+          <t>https://terreno.mercadolibre.com.mx/MLM-2318168399-terreno-en-venta-en-cacalomacan-a-2-cuadras-de-jinetes-cerca-de-calz-pacifico-y-colegio-paideia-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=33&amp;type=item&amp;tracking_id=3fb6d42b-4d65-4353-9cbe-760b5a922e09&amp;price_drop=not_apply</t>
         </is>
       </c>
     </row>
@@ -3037,7 +3037,7 @@
         </is>
       </c>
       <c r="B131" t="n">
-        <v>1840590</v>
+        <v>11500000</v>
       </c>
       <c r="C131" t="inlineStr">
         <is>
@@ -3046,7 +3046,7 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>https://terreno.mercadolibre.com.mx/MLM-4080239968-terreno-en-venta-toluca-cerca-del-aeropuerto-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=34&amp;type=item&amp;tracking_id=83833016-059e-4410-b009-268e9b9166c7&amp;price_drop=not_apply</t>
+          <t>https://terreno.mercadolibre.com.mx/MLM-4080259510-terreno-en-venta-en-san-martin-toltepec-toluca-mexico-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=34&amp;type=item&amp;tracking_id=3fb6d42b-4d65-4353-9cbe-760b5a922e09&amp;price_drop=not_apply</t>
         </is>
       </c>
     </row>
@@ -3057,7 +3057,7 @@
         </is>
       </c>
       <c r="B132" t="n">
-        <v>8500000</v>
+        <v>1840590</v>
       </c>
       <c r="C132" t="inlineStr">
         <is>
@@ -3066,7 +3066,7 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>https://terreno.mercadolibre.com.mx/MLM-2343423083-terreno-en-san-pedro-totoltepec-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=35&amp;type=item&amp;tracking_id=83833016-059e-4410-b009-268e9b9166c7&amp;price_drop=not_apply</t>
+          <t>https://terreno.mercadolibre.com.mx/MLM-4080239968-terreno-en-venta-toluca-cerca-del-aeropuerto-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=35&amp;type=item&amp;tracking_id=3fb6d42b-4d65-4353-9cbe-760b5a922e09&amp;price_drop=not_apply</t>
         </is>
       </c>
     </row>
@@ -3077,7 +3077,7 @@
         </is>
       </c>
       <c r="B133" t="n">
-        <v>35000000</v>
+        <v>8500000</v>
       </c>
       <c r="C133" t="inlineStr">
         <is>
@@ -3086,7 +3086,7 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>https://terreno.mercadolibre.com.mx/MLM-2370231281-terreno-en-venta-en-toluca-reforma-y-ferr-nac-independencia-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=36&amp;type=item&amp;tracking_id=83833016-059e-4410-b009-268e9b9166c7&amp;price_drop=not_apply</t>
+          <t>https://terreno.mercadolibre.com.mx/MLM-2343423083-terreno-en-san-pedro-totoltepec-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=36&amp;type=item&amp;tracking_id=3fb6d42b-4d65-4353-9cbe-760b5a922e09&amp;price_drop=not_apply</t>
         </is>
       </c>
     </row>
@@ -3097,7 +3097,7 @@
         </is>
       </c>
       <c r="B134" t="n">
-        <v>2450000</v>
+        <v>35000000</v>
       </c>
       <c r="C134" t="inlineStr">
         <is>
@@ -3106,7 +3106,7 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>https://terreno.mercadolibre.com.mx/MLM-2343569515-terreno-en-santa-maria-totoltepec-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=37&amp;type=item&amp;tracking_id=83833016-059e-4410-b009-268e9b9166c7&amp;price_drop=not_apply</t>
+          <t>https://terreno.mercadolibre.com.mx/MLM-2370231281-terreno-en-venta-en-toluca-reforma-y-ferr-nac-independencia-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=37&amp;type=item&amp;tracking_id=3fb6d42b-4d65-4353-9cbe-760b5a922e09&amp;price_drop=not_apply</t>
         </is>
       </c>
     </row>
@@ -3117,7 +3117,7 @@
         </is>
       </c>
       <c r="B135" t="n">
-        <v>50000000</v>
+        <v>2450000</v>
       </c>
       <c r="C135" t="inlineStr">
         <is>
@@ -3126,7 +3126,7 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>https://terreno.mercadolibre.com.mx/MLM-4558160588-terreno-en-venta-en-cipres-toluca-estado-de-mexico-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=38&amp;type=item&amp;tracking_id=83833016-059e-4410-b009-268e9b9166c7&amp;price_drop=not_apply</t>
+          <t>https://terreno.mercadolibre.com.mx/MLM-2343569515-terreno-en-santa-maria-totoltepec-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=38&amp;type=item&amp;tracking_id=3fb6d42b-4d65-4353-9cbe-760b5a922e09&amp;price_drop=not_apply</t>
         </is>
       </c>
     </row>
@@ -3137,7 +3137,7 @@
         </is>
       </c>
       <c r="B136" t="n">
-        <v>203547204</v>
+        <v>50000000</v>
       </c>
       <c r="C136" t="inlineStr">
         <is>
@@ -3146,7 +3146,7 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>https://terreno.mercadolibre.com.mx/MLM-4261794654-terreno-en-venta-en-industrial-en-toluca-estado-de-mexico-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=39&amp;type=item&amp;tracking_id=83833016-059e-4410-b009-268e9b9166c7&amp;price_drop=not_apply</t>
+          <t>https://terreno.mercadolibre.com.mx/MLM-4558160588-terreno-en-venta-en-cipres-toluca-estado-de-mexico-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=39&amp;type=item&amp;tracking_id=3fb6d42b-4d65-4353-9cbe-760b5a922e09&amp;price_drop=not_apply</t>
         </is>
       </c>
     </row>
@@ -3157,7 +3157,7 @@
         </is>
       </c>
       <c r="B137" t="n">
-        <v>14571000</v>
+        <v>203547204</v>
       </c>
       <c r="C137" t="inlineStr">
         <is>
@@ -3166,7 +3166,7 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>https://terreno.mercadolibre.com.mx/MLM-4261807760-se-vende-terreno-carretera-mexico-toluca-lerma-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=40&amp;type=item&amp;tracking_id=83833016-059e-4410-b009-268e9b9166c7&amp;price_drop=not_apply</t>
+          <t>https://terreno.mercadolibre.com.mx/MLM-4261794654-terreno-en-venta-en-industrial-en-toluca-estado-de-mexico-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=40&amp;type=item&amp;tracking_id=3fb6d42b-4d65-4353-9cbe-760b5a922e09&amp;price_drop=not_apply</t>
         </is>
       </c>
     </row>
@@ -3177,7 +3177,7 @@
         </is>
       </c>
       <c r="B138" t="n">
-        <v>222618909</v>
+        <v>14571000</v>
       </c>
       <c r="C138" t="inlineStr">
         <is>
@@ -3186,7 +3186,7 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>https://terreno.mercadolibre.com.mx/MLM-4261859654-terreno-en-venta-industrial-en-toluca-estado-de-mexico-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=41&amp;type=item&amp;tracking_id=83833016-059e-4410-b009-268e9b9166c7&amp;price_drop=not_apply</t>
+          <t>https://terreno.mercadolibre.com.mx/MLM-4261807760-se-vende-terreno-carretera-mexico-toluca-lerma-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=41&amp;type=item&amp;tracking_id=3fb6d42b-4d65-4353-9cbe-760b5a922e09&amp;price_drop=not_apply</t>
         </is>
       </c>
     </row>
@@ -3197,7 +3197,7 @@
         </is>
       </c>
       <c r="B139" t="n">
-        <v>1870000</v>
+        <v>222618909</v>
       </c>
       <c r="C139" t="inlineStr">
         <is>
@@ -3206,7 +3206,7 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>https://terreno.mercadolibre.com.mx/MLM-2811993671-terreno-en-venta-en-residencial-hacienda-san-jose-en-toluca-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=42&amp;type=item&amp;float_highlight=recent_publication&amp;tracking_id=83833016-059e-4410-b009-268e9b9166c7&amp;price_drop=not_apply</t>
+          <t>https://terreno.mercadolibre.com.mx/MLM-4261859654-terreno-en-venta-industrial-en-toluca-estado-de-mexico-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=42&amp;type=item&amp;tracking_id=3fb6d42b-4d65-4353-9cbe-760b5a922e09&amp;price_drop=not_apply</t>
         </is>
       </c>
     </row>
@@ -3217,7 +3217,7 @@
         </is>
       </c>
       <c r="B140" t="n">
-        <v>700000</v>
+        <v>1870000</v>
       </c>
       <c r="C140" t="inlineStr">
         <is>
@@ -3226,7 +3226,7 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>https://terreno.mercadolibre.com.mx/MLM-5058024988-terreno-en-venta-en-san-lorenzo-tepaltitlan-toluca-estado-de-mexico-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=43&amp;type=item&amp;float_highlight=recent_publication&amp;tracking_id=83833016-059e-4410-b009-268e9b9166c7&amp;price_drop=not_apply</t>
+          <t>https://terreno.mercadolibre.com.mx/MLM-2811993671-terreno-en-venta-en-residencial-hacienda-san-jose-en-toluca-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=43&amp;type=item&amp;float_highlight=recent_publication&amp;tracking_id=3fb6d42b-4d65-4353-9cbe-760b5a922e09&amp;price_drop=not_apply</t>
         </is>
       </c>
     </row>
@@ -3237,7 +3237,7 @@
         </is>
       </c>
       <c r="B141" t="n">
-        <v>3240000</v>
+        <v>132000000</v>
       </c>
       <c r="C141" t="inlineStr">
         <is>
@@ -3246,7 +3246,7 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>https://terreno.mercadolibre.com.mx/MLM-5058177406-terreno-en-venta-en-san-francisco-totoltepec-toluca-estado-de-mexico-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=44&amp;type=item&amp;float_highlight=recent_publication&amp;tracking_id=83833016-059e-4410-b009-268e9b9166c7&amp;price_drop=not_apply</t>
+          <t>https://terreno.mercadolibre.com.mx/MLM-5064030156-terreno-en-venta-en-parque-industrial-el-coecillo-toluca-estado-de-mexico-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=44&amp;type=item&amp;float_highlight=recent_publication&amp;tracking_id=3fb6d42b-4d65-4353-9cbe-760b5a922e09&amp;price_drop=not_apply</t>
         </is>
       </c>
     </row>
@@ -3257,7 +3257,7 @@
         </is>
       </c>
       <c r="B142" t="n">
-        <v>132000000</v>
+        <v>279450</v>
       </c>
       <c r="C142" t="inlineStr">
         <is>
@@ -3266,7 +3266,7 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>https://terreno.mercadolibre.com.mx/MLM-5064030156-terreno-en-venta-en-parque-industrial-el-coecillo-toluca-estado-de-mexico-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=45&amp;type=item&amp;float_highlight=recent_publication&amp;tracking_id=83833016-059e-4410-b009-268e9b9166c7&amp;price_drop=not_apply</t>
+          <t>https://terreno.mercadolibre.com.mx/MLM-5060346586-ultimos-2-lotes-en-venta-en-san-cayetano-muy-cerca-de-la-unsa-en-toluca-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=45&amp;type=item&amp;float_highlight=recent_publication&amp;tracking_id=3fb6d42b-4d65-4353-9cbe-760b5a922e09&amp;price_drop=not_apply</t>
         </is>
       </c>
     </row>
@@ -3277,7 +3277,7 @@
         </is>
       </c>
       <c r="B143" t="n">
-        <v>279450</v>
+        <v>23500000</v>
       </c>
       <c r="C143" t="inlineStr">
         <is>
@@ -3286,7 +3286,7 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>https://terreno.mercadolibre.com.mx/MLM-5060346586-ultimos-2-lotes-en-venta-en-san-cayetano-muy-cerca-de-la-unsa-en-toluca-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=46&amp;type=item&amp;float_highlight=recent_publication&amp;tracking_id=83833016-059e-4410-b009-268e9b9166c7&amp;price_drop=not_apply</t>
+          <t>https://terreno.mercadolibre.com.mx/MLM-4950598656-terreno-comercial-en-venta-en-san-bernardino-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=46&amp;type=item&amp;tracking_id=3fb6d42b-4d65-4353-9cbe-760b5a922e09&amp;price_drop=not_apply</t>
         </is>
       </c>
     </row>
@@ -3297,7 +3297,7 @@
         </is>
       </c>
       <c r="B144" t="n">
-        <v>9215400</v>
+        <v>8760000</v>
       </c>
       <c r="C144" t="inlineStr">
         <is>
@@ -3306,7 +3306,7 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>https://terreno.mercadolibre.com.mx/MLM-5047581202-terreno-comercial-en-venta-en-santa-cruz-otzacatipan-toluca-mexico-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=47&amp;type=item&amp;float_highlight=recent_publication&amp;tracking_id=83833016-059e-4410-b009-268e9b9166c7&amp;price_drop=not_apply</t>
+          <t>https://terreno.mercadolibre.com.mx/MLM-4761562052-terreno-comercial-en-venta-en-santa-maria-totoltepec-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=47&amp;type=item&amp;tracking_id=3fb6d42b-4d65-4353-9cbe-760b5a922e09&amp;price_drop=not_apply</t>
         </is>
       </c>
     </row>
@@ -3317,7 +3317,7 @@
         </is>
       </c>
       <c r="B145" t="n">
-        <v>8502990</v>
+        <v>26320000</v>
       </c>
       <c r="C145" t="inlineStr">
         <is>
@@ -3326,7 +3326,7 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>https://terreno.mercadolibre.com.mx/MLM-5047581198-terreno-comercial-en-venta-en-santa-cruz-otzacatipan-toluca-mexico-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=48&amp;type=item&amp;float_highlight=recent_publication&amp;tracking_id=83833016-059e-4410-b009-268e9b9166c7&amp;price_drop=not_apply</t>
+          <t>https://terreno.mercadolibre.com.mx/MLM-4790443980-terreno-residencial-en-venta-en-la-venta-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=48&amp;type=item&amp;tracking_id=3fb6d42b-4d65-4353-9cbe-760b5a922e09&amp;price_drop=not_apply</t>
         </is>
       </c>
     </row>
@@ -3346,7 +3346,7 @@
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>https://terreno.mercadolibre.com.mx/MLM-3835159420-lotes-de-terreno-desde-104-m2-en-venta-cerca-del-aeropuerto-de-toluca-en-la-constitucion-toltepec-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=1&amp;type=item&amp;tracking_id=a57d6faf-17b2-476c-987c-3783bc1e01f3&amp;price_drop=not_apply</t>
+          <t>https://terreno.mercadolibre.com.mx/MLM-3835159420-lotes-de-terreno-desde-104-m2-en-venta-cerca-del-aeropuerto-de-toluca-en-la-constitucion-toltepec-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=1&amp;type=item&amp;tracking_id=c4dc49ac-dc63-4f0f-b01f-121745225170&amp;price_drop=not_apply</t>
         </is>
       </c>
     </row>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>https://terreno.mercadolibre.com.mx/MLM-2810992285-construye-tu-residencia-en-la-zona-de-mayor-proyeccion-de-toluca-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=2&amp;type=item&amp;float_highlight=recent_publication&amp;tracking_id=a57d6faf-17b2-476c-987c-3783bc1e01f3&amp;price_drop=not_apply</t>
+          <t>https://terreno.mercadolibre.com.mx/MLM-2810992285-construye-tu-residencia-en-la-zona-de-mayor-proyeccion-de-toluca-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=2&amp;type=item&amp;float_highlight=recent_publication&amp;tracking_id=c4dc49ac-dc63-4f0f-b01f-121745225170&amp;price_drop=not_apply</t>
         </is>
       </c>
     </row>
@@ -3386,7 +3386,7 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>https://terreno.mercadolibre.com.mx/MLM-3847495816-el-mejor-terreno-del-condominio-puede-ser-tuyo-a-un-precio-de-oportunidad-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=3&amp;type=item&amp;tracking_id=a57d6faf-17b2-476c-987c-3783bc1e01f3&amp;price_drop=not_apply</t>
+          <t>https://terreno.mercadolibre.com.mx/MLM-3847495816-el-mejor-terreno-del-condominio-puede-ser-tuyo-a-un-precio-de-oportunidad-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=3&amp;type=item&amp;tracking_id=c4dc49ac-dc63-4f0f-b01f-121745225170&amp;price_drop=not_apply</t>
         </is>
       </c>
     </row>
@@ -3397,7 +3397,7 @@
         </is>
       </c>
       <c r="B149" t="n">
-        <v>7600000</v>
+        <v>649000</v>
       </c>
       <c r="C149" t="inlineStr">
         <is>
@@ -3406,7 +3406,7 @@
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>https://terreno.mercadolibre.com.mx/MLM-2231593183-terreno-en-venta-en-san-mateo-oxtotitlan-toluca-mexico-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=4&amp;type=item&amp;tracking_id=a57d6faf-17b2-476c-987c-3783bc1e01f3&amp;price_drop=not_apply</t>
+          <t>https://terreno.mercadolibre.com.mx/MLM-2753915589-terreno-bardeado-en-cacalomacan-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=4&amp;type=item&amp;tracking_id=c4dc49ac-dc63-4f0f-b01f-121745225170&amp;price_drop=false</t>
         </is>
       </c>
     </row>
@@ -3417,7 +3417,7 @@
         </is>
       </c>
       <c r="B150" t="n">
-        <v>649000</v>
+        <v>7600000</v>
       </c>
       <c r="C150" t="inlineStr">
         <is>
@@ -3426,7 +3426,7 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>https://terreno.mercadolibre.com.mx/MLM-2753915589-terreno-bardeado-en-cacalomacan-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=5&amp;type=item&amp;tracking_id=a57d6faf-17b2-476c-987c-3783bc1e01f3&amp;price_drop=false</t>
+          <t>https://terreno.mercadolibre.com.mx/MLM-2231593183-terreno-en-venta-en-san-mateo-oxtotitlan-toluca-mexico-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=5&amp;type=item&amp;tracking_id=c4dc49ac-dc63-4f0f-b01f-121745225170&amp;price_drop=not_apply</t>
         </is>
       </c>
     </row>
@@ -3446,7 +3446,7 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>https://terreno.mercadolibre.com.mx/MLM-2716356593-terreno-en-venta-en-colonia-nueva-santa-maria-de-las-rosas-toluca-estado-de-mexico-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=6&amp;type=item&amp;tracking_id=a57d6faf-17b2-476c-987c-3783bc1e01f3&amp;price_drop=not_apply</t>
+          <t>https://terreno.mercadolibre.com.mx/MLM-2716356593-terreno-en-venta-en-colonia-nueva-santa-maria-de-las-rosas-toluca-estado-de-mexico-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=6&amp;type=item&amp;tracking_id=c4dc49ac-dc63-4f0f-b01f-121745225170&amp;price_drop=not_apply</t>
         </is>
       </c>
     </row>
@@ -3466,7 +3466,7 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>https://terreno.mercadolibre.com.mx/MLM-4660497978-terreno-en-venta-en-toluca-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=7&amp;type=item&amp;tracking_id=a57d6faf-17b2-476c-987c-3783bc1e01f3&amp;price_drop=not_apply</t>
+          <t>https://terreno.mercadolibre.com.mx/MLM-4660497978-terreno-en-venta-en-toluca-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=7&amp;type=item&amp;tracking_id=c4dc49ac-dc63-4f0f-b01f-121745225170&amp;price_drop=not_apply</t>
         </is>
       </c>
     </row>
@@ -3486,7 +3486,7 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>https://terreno.mercadolibre.com.mx/MLM-4388186170-terreno-industrial-en-venta-en-toluca-san-cayetano-a-un-lado-de-la-caseta-el-dorado-cerca-puerta-mexico-recinto-aduanal-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=8&amp;type=item&amp;tracking_id=a57d6faf-17b2-476c-987c-3783bc1e01f3&amp;price_drop=not_apply</t>
+          <t>https://terreno.mercadolibre.com.mx/MLM-4388186170-terreno-industrial-en-venta-en-toluca-san-cayetano-a-un-lado-de-la-caseta-el-dorado-cerca-puerta-mexico-recinto-aduanal-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=8&amp;type=item&amp;tracking_id=c4dc49ac-dc63-4f0f-b01f-121745225170&amp;price_drop=not_apply</t>
         </is>
       </c>
     </row>
@@ -3506,7 +3506,7 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>https://terreno.mercadolibre.com.mx/MLM-2716629645-terreno-industrial-en-venta-en-palmillas-son-13-hectareas-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=9&amp;type=item&amp;tracking_id=a57d6faf-17b2-476c-987c-3783bc1e01f3&amp;price_drop=not_apply</t>
+          <t>https://terreno.mercadolibre.com.mx/MLM-2716629645-terreno-industrial-en-venta-en-palmillas-son-13-hectareas-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=9&amp;type=item&amp;tracking_id=c4dc49ac-dc63-4f0f-b01f-121745225170&amp;price_drop=not_apply</t>
         </is>
       </c>
     </row>
@@ -3526,7 +3526,7 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>https://terreno.mercadolibre.com.mx/MLM-2748643873-terreno-en-venta-a-pie-de-carretera-toluca-atlacomulco-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=10&amp;type=item&amp;tracking_id=a57d6faf-17b2-476c-987c-3783bc1e01f3&amp;price_drop=not_apply</t>
+          <t>https://terreno.mercadolibre.com.mx/MLM-2748643873-terreno-en-venta-a-pie-de-carretera-toluca-atlacomulco-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=10&amp;type=item&amp;tracking_id=c4dc49ac-dc63-4f0f-b01f-121745225170&amp;price_drop=not_apply</t>
         </is>
       </c>
     </row>
@@ -3546,7 +3546,7 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>https://terreno.mercadolibre.com.mx/MLM-4790479866-terreno-regular-con-infraestructura-lista-base-solida-para-tu-proyecto-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=11&amp;type=item&amp;tracking_id=a57d6faf-17b2-476c-987c-3783bc1e01f3&amp;price_drop=not_apply</t>
+          <t>https://terreno.mercadolibre.com.mx/MLM-4790479866-terreno-regular-con-infraestructura-lista-base-solida-para-tu-proyecto-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=11&amp;type=item&amp;tracking_id=c4dc49ac-dc63-4f0f-b01f-121745225170&amp;price_drop=not_apply</t>
         </is>
       </c>
     </row>
@@ -3566,7 +3566,7 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>https://terreno.mercadolibre.com.mx/MLM-5015164202-venta-terreno-lotes-palmillas-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=12&amp;type=item&amp;tracking_id=a57d6faf-17b2-476c-987c-3783bc1e01f3&amp;price_drop=not_apply</t>
+          <t>https://terreno.mercadolibre.com.mx/MLM-5015164202-venta-terreno-lotes-palmillas-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=12&amp;type=item&amp;tracking_id=c4dc49ac-dc63-4f0f-b01f-121745225170&amp;price_drop=not_apply</t>
         </is>
       </c>
     </row>
@@ -3586,7 +3586,7 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>https://terreno.mercadolibre.com.mx/MLM-4416680104-terreno-en-venta-sobre-calzada-del-pacifico-cacalomacan-por-ocho-cedros-toluca-cas-23000-m2-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=13&amp;type=item&amp;tracking_id=a57d6faf-17b2-476c-987c-3783bc1e01f3&amp;price_drop=not_apply</t>
+          <t>https://terreno.mercadolibre.com.mx/MLM-4416680104-terreno-en-venta-sobre-calzada-del-pacifico-cacalomacan-por-ocho-cedros-toluca-cas-23000-m2-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=13&amp;type=item&amp;tracking_id=c4dc49ac-dc63-4f0f-b01f-121745225170&amp;price_drop=not_apply</t>
         </is>
       </c>
     </row>
@@ -3606,7 +3606,7 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>https://terreno.mercadolibre.com.mx/MLM-2736455271-terreno-de-2-hectareas-en-zona-urbana-santa-maria-totoltepec-estado-de-mexico-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=14&amp;type=item&amp;tracking_id=a57d6faf-17b2-476c-987c-3783bc1e01f3&amp;price_drop=not_apply</t>
+          <t>https://terreno.mercadolibre.com.mx/MLM-2736455271-terreno-de-2-hectareas-en-zona-urbana-santa-maria-totoltepec-estado-de-mexico-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=14&amp;type=item&amp;tracking_id=c4dc49ac-dc63-4f0f-b01f-121745225170&amp;price_drop=not_apply</t>
         </is>
       </c>
     </row>
@@ -3617,7 +3617,7 @@
         </is>
       </c>
       <c r="B160" t="n">
-        <v>1831680</v>
+        <v>299999</v>
       </c>
       <c r="C160" t="inlineStr">
         <is>
@@ -3626,7 +3626,7 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>https://terreno.mercadolibre.com.mx/MLM-2804712255-venta-terreno-paraje-san-rafael-en-toluca-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=15&amp;type=item&amp;float_highlight=recent_publication&amp;tracking_id=a57d6faf-17b2-476c-987c-3783bc1e01f3&amp;price_drop=not_apply</t>
+          <t>https://terreno.mercadolibre.com.mx/MLM-5082958514-lotes-a-10-min-de-paideia-propiedad-desde-230-m-en-adelante-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=15&amp;type=item&amp;float_highlight=recent_publication&amp;tracking_id=c4dc49ac-dc63-4f0f-b01f-121745225170&amp;price_drop=not_apply</t>
         </is>
       </c>
     </row>
@@ -3637,7 +3637,7 @@
         </is>
       </c>
       <c r="B161" t="n">
-        <v>1485000</v>
+        <v>1831680</v>
       </c>
       <c r="C161" t="inlineStr">
         <is>
@@ -3646,7 +3646,7 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>https://terreno.mercadolibre.com.mx/MLM-2187928841-venta-terreno-cerrillo-vista-hermosa-toluca-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=16&amp;type=item&amp;tracking_id=a57d6faf-17b2-476c-987c-3783bc1e01f3&amp;price_drop=not_apply</t>
+          <t>https://terreno.mercadolibre.com.mx/MLM-2804712255-venta-terreno-paraje-san-rafael-en-toluca-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=16&amp;type=item&amp;float_highlight=recent_publication&amp;tracking_id=c4dc49ac-dc63-4f0f-b01f-121745225170&amp;price_drop=not_apply</t>
         </is>
       </c>
     </row>
@@ -3657,7 +3657,7 @@
         </is>
       </c>
       <c r="B162" t="n">
-        <v>4805040</v>
+        <v>1485000</v>
       </c>
       <c r="C162" t="inlineStr">
         <is>
@@ -3666,7 +3666,7 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>https://terreno.mercadolibre.com.mx/MLM-3705026808-venta-de-terreno-en-cacalomacan-a-20-min-centro-toluca-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=17&amp;type=item&amp;tracking_id=a57d6faf-17b2-476c-987c-3783bc1e01f3&amp;price_drop=not_apply</t>
+          <t>https://terreno.mercadolibre.com.mx/MLM-2187928841-venta-terreno-cerrillo-vista-hermosa-toluca-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=17&amp;type=item&amp;tracking_id=c4dc49ac-dc63-4f0f-b01f-121745225170&amp;price_drop=not_apply</t>
         </is>
       </c>
     </row>
@@ -3677,7 +3677,7 @@
         </is>
       </c>
       <c r="B163" t="n">
-        <v>1920000</v>
+        <v>4805040</v>
       </c>
       <c r="C163" t="inlineStr">
         <is>
@@ -3686,7 +3686,7 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>https://terreno.mercadolibre.com.mx/MLM-4119789692-terreno-en-venta-residencial-ex-hacienda-san-jose-toluca-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=18&amp;type=item&amp;tracking_id=a57d6faf-17b2-476c-987c-3783bc1e01f3&amp;price_drop=not_apply</t>
+          <t>https://terreno.mercadolibre.com.mx/MLM-3705026808-venta-de-terreno-en-cacalomacan-a-20-min-centro-toluca-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=18&amp;type=item&amp;tracking_id=c4dc49ac-dc63-4f0f-b01f-121745225170&amp;price_drop=not_apply</t>
         </is>
       </c>
     </row>
@@ -3697,7 +3697,7 @@
         </is>
       </c>
       <c r="B164" t="n">
-        <v>1244380</v>
+        <v>1920000</v>
       </c>
       <c r="C164" t="inlineStr">
         <is>
@@ -3706,7 +3706,7 @@
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>https://terreno.mercadolibre.com.mx/MLM-4826508826-venta-de-lote-de-terreno-residencial-cerca-de-galerias-metepec-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=19&amp;type=item&amp;tracking_id=a57d6faf-17b2-476c-987c-3783bc1e01f3&amp;price_drop=not_apply</t>
+          <t>https://terreno.mercadolibre.com.mx/MLM-4119789692-terreno-en-venta-residencial-ex-hacienda-san-jose-toluca-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=19&amp;type=item&amp;tracking_id=c4dc49ac-dc63-4f0f-b01f-121745225170&amp;price_drop=not_apply</t>
         </is>
       </c>
     </row>
@@ -3717,7 +3717,7 @@
         </is>
       </c>
       <c r="B165" t="n">
-        <v>8565858</v>
+        <v>1244380</v>
       </c>
       <c r="C165" t="inlineStr">
         <is>
@@ -3726,7 +3726,7 @@
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>https://terreno.mercadolibre.com.mx/MLM-4080298834-terreno-en-venta-en-san-miguel-zacango-toluca-mexico-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=20&amp;type=item&amp;tracking_id=a57d6faf-17b2-476c-987c-3783bc1e01f3&amp;price_drop=not_apply</t>
+          <t>https://terreno.mercadolibre.com.mx/MLM-4826508826-venta-de-lote-de-terreno-residencial-cerca-de-galerias-metepec-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=20&amp;type=item&amp;tracking_id=c4dc49ac-dc63-4f0f-b01f-121745225170&amp;price_drop=not_apply</t>
         </is>
       </c>
     </row>
@@ -3737,7 +3737,7 @@
         </is>
       </c>
       <c r="B166" t="n">
-        <v>8500000</v>
+        <v>8565858</v>
       </c>
       <c r="C166" t="inlineStr">
         <is>
@@ -3746,7 +3746,7 @@
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>https://terreno.mercadolibre.com.mx/MLM-2310439697-se-vende-terreno-en-toluca-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=21&amp;type=item&amp;tracking_id=a57d6faf-17b2-476c-987c-3783bc1e01f3&amp;price_drop=not_apply</t>
+          <t>https://terreno.mercadolibre.com.mx/MLM-4080298834-terreno-en-venta-en-san-miguel-zacango-toluca-mexico-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=21&amp;type=item&amp;tracking_id=c4dc49ac-dc63-4f0f-b01f-121745225170&amp;price_drop=not_apply</t>
         </is>
       </c>
     </row>
@@ -3757,7 +3757,7 @@
         </is>
       </c>
       <c r="B167" t="n">
-        <v>1300000</v>
+        <v>8500000</v>
       </c>
       <c r="C167" t="inlineStr">
         <is>
@@ -3766,7 +3766,7 @@
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>https://terreno.mercadolibre.com.mx/MLM-4495237624-lote-disponible-en-conjunto-ambar-toluca-edo-mex-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=22&amp;type=item&amp;tracking_id=a57d6faf-17b2-476c-987c-3783bc1e01f3&amp;price_drop=not_apply</t>
+          <t>https://terreno.mercadolibre.com.mx/MLM-2310439697-se-vende-terreno-en-toluca-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=22&amp;type=item&amp;tracking_id=c4dc49ac-dc63-4f0f-b01f-121745225170&amp;price_drop=not_apply</t>
         </is>
       </c>
     </row>
@@ -3777,7 +3777,7 @@
         </is>
       </c>
       <c r="B168" t="n">
-        <v>1200000</v>
+        <v>1300000</v>
       </c>
       <c r="C168" t="inlineStr">
         <is>
@@ -3786,7 +3786,7 @@
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>https://terreno.mercadolibre.com.mx/MLM-2485559517-terreno-en-venta-en-toluca-san-andres-cuexcontitlan-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=23&amp;type=item&amp;tracking_id=a57d6faf-17b2-476c-987c-3783bc1e01f3&amp;price_drop=not_apply</t>
+          <t>https://terreno.mercadolibre.com.mx/MLM-4495237624-lote-disponible-en-conjunto-ambar-toluca-edo-mex-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=23&amp;type=item&amp;tracking_id=c4dc49ac-dc63-4f0f-b01f-121745225170&amp;price_drop=not_apply</t>
         </is>
       </c>
     </row>
@@ -3797,7 +3797,7 @@
         </is>
       </c>
       <c r="B169" t="n">
-        <v>38634000</v>
+        <v>1200000</v>
       </c>
       <c r="C169" t="inlineStr">
         <is>
@@ -3806,7 +3806,7 @@
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>https://terreno.mercadolibre.com.mx/MLM-2431684449-terreno-en-toluca-25756-m2-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=24&amp;type=item&amp;tracking_id=a57d6faf-17b2-476c-987c-3783bc1e01f3&amp;price_drop=not_apply</t>
+          <t>https://terreno.mercadolibre.com.mx/MLM-2485559517-terreno-en-venta-en-toluca-san-andres-cuexcontitlan-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=24&amp;type=item&amp;tracking_id=c4dc49ac-dc63-4f0f-b01f-121745225170&amp;price_drop=not_apply</t>
         </is>
       </c>
     </row>
@@ -3817,7 +3817,7 @@
         </is>
       </c>
       <c r="B170" t="n">
-        <v>5625000</v>
+        <v>38634000</v>
       </c>
       <c r="C170" t="inlineStr">
         <is>
@@ -3826,7 +3826,7 @@
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>https://terreno.mercadolibre.com.mx/MLM-2323267483-terreno-en-venta-2250m2-en-san-felipe-tlalmimilolpan-toluca-mexico-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=25&amp;type=item&amp;tracking_id=a57d6faf-17b2-476c-987c-3783bc1e01f3&amp;price_drop=not_apply</t>
+          <t>https://terreno.mercadolibre.com.mx/MLM-2431684449-terreno-en-toluca-25756-m2-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=25&amp;type=item&amp;tracking_id=c4dc49ac-dc63-4f0f-b01f-121745225170&amp;price_drop=not_apply</t>
         </is>
       </c>
     </row>
@@ -3837,7 +3837,7 @@
         </is>
       </c>
       <c r="B171" t="n">
-        <v>25650000</v>
+        <v>5625000</v>
       </c>
       <c r="C171" t="inlineStr">
         <is>
@@ -3846,7 +3846,7 @@
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>https://terreno.mercadolibre.com.mx/MLM-4169951646-terreno-en-venta-por-las-torres-toluca-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=26&amp;type=item&amp;tracking_id=a57d6faf-17b2-476c-987c-3783bc1e01f3&amp;price_drop=not_apply</t>
+          <t>https://terreno.mercadolibre.com.mx/MLM-2323267483-terreno-en-venta-2250m2-en-san-felipe-tlalmimilolpan-toluca-mexico-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=26&amp;type=item&amp;tracking_id=c4dc49ac-dc63-4f0f-b01f-121745225170&amp;price_drop=not_apply</t>
         </is>
       </c>
     </row>
@@ -3857,7 +3857,7 @@
         </is>
       </c>
       <c r="B172" t="n">
-        <v>4800000</v>
+        <v>25650000</v>
       </c>
       <c r="C172" t="inlineStr">
         <is>
@@ -3866,7 +3866,7 @@
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>https://terreno.mercadolibre.com.mx/MLM-4416373342-terreno-en-venta-en-san-lorenzo-tepaltitlan-centro-toluca-mexico-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=27&amp;type=item&amp;tracking_id=a57d6faf-17b2-476c-987c-3783bc1e01f3&amp;price_drop=not_apply</t>
+          <t>https://terreno.mercadolibre.com.mx/MLM-4169951646-terreno-en-venta-por-las-torres-toluca-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=27&amp;type=item&amp;tracking_id=c4dc49ac-dc63-4f0f-b01f-121745225170&amp;price_drop=not_apply</t>
         </is>
       </c>
     </row>
@@ -3877,7 +3877,7 @@
         </is>
       </c>
       <c r="B173" t="n">
-        <v>14490000</v>
+        <v>4800000</v>
       </c>
       <c r="C173" t="inlineStr">
         <is>
@@ -3886,7 +3886,7 @@
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>https://terreno.mercadolibre.com.mx/MLM-2584697469-oportunidad-de-inversion-terreno-de-9993-m-cerca-de-parque-toluca-2000-ideal-para-naves-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=28&amp;type=item&amp;tracking_id=a57d6faf-17b2-476c-987c-3783bc1e01f3&amp;price_drop=not_apply</t>
+          <t>https://terreno.mercadolibre.com.mx/MLM-4416373342-terreno-en-venta-en-san-lorenzo-tepaltitlan-centro-toluca-mexico-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=28&amp;type=item&amp;tracking_id=c4dc49ac-dc63-4f0f-b01f-121745225170&amp;price_drop=not_apply</t>
         </is>
       </c>
     </row>
@@ -3897,7 +3897,7 @@
         </is>
       </c>
       <c r="B174" t="n">
-        <v>24520000</v>
+        <v>14490000</v>
       </c>
       <c r="C174" t="inlineStr">
         <is>
@@ -3906,7 +3906,7 @@
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>https://terreno.mercadolibre.com.mx/MLM-4169951774-terreno-en-venta-por-las-torres-toluca-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=29&amp;type=item&amp;tracking_id=a57d6faf-17b2-476c-987c-3783bc1e01f3&amp;price_drop=not_apply</t>
+          <t>https://terreno.mercadolibre.com.mx/MLM-2584697469-oportunidad-de-inversion-terreno-de-9993-m-cerca-de-parque-toluca-2000-ideal-para-naves-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=29&amp;type=item&amp;tracking_id=c4dc49ac-dc63-4f0f-b01f-121745225170&amp;price_drop=not_apply</t>
         </is>
       </c>
     </row>
@@ -3917,7 +3917,7 @@
         </is>
       </c>
       <c r="B175" t="n">
-        <v>12024000</v>
+        <v>24520000</v>
       </c>
       <c r="C175" t="inlineStr">
         <is>
@@ -3926,7 +3926,7 @@
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>https://terreno.mercadolibre.com.mx/MLM-2323192153-terreno-en-venta-8016-m2-en-san-felipe-tlalmimilolpan-toluca-mexico-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=30&amp;type=item&amp;tracking_id=a57d6faf-17b2-476c-987c-3783bc1e01f3&amp;price_drop=not_apply</t>
+          <t>https://terreno.mercadolibre.com.mx/MLM-4169951774-terreno-en-venta-por-las-torres-toluca-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=30&amp;type=item&amp;tracking_id=c4dc49ac-dc63-4f0f-b01f-121745225170&amp;price_drop=not_apply</t>
         </is>
       </c>
     </row>
@@ -3937,7 +3937,7 @@
         </is>
       </c>
       <c r="B176" t="n">
-        <v>13650000</v>
+        <v>12024000</v>
       </c>
       <c r="C176" t="inlineStr">
         <is>
@@ -3946,7 +3946,7 @@
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>https://terreno.mercadolibre.com.mx/MLM-2487732477-terreno-en-venta-por-las-torres-toluca-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=31&amp;type=item&amp;tracking_id=a57d6faf-17b2-476c-987c-3783bc1e01f3&amp;price_drop=not_apply</t>
+          <t>https://terreno.mercadolibre.com.mx/MLM-2323192153-terreno-en-venta-8016-m2-en-san-felipe-tlalmimilolpan-toluca-mexico-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=31&amp;type=item&amp;tracking_id=c4dc49ac-dc63-4f0f-b01f-121745225170&amp;price_drop=not_apply</t>
         </is>
       </c>
     </row>
@@ -3957,7 +3957,7 @@
         </is>
       </c>
       <c r="B177" t="n">
-        <v>4725000</v>
+        <v>13650000</v>
       </c>
       <c r="C177" t="inlineStr">
         <is>
@@ -3966,7 +3966,7 @@
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>https://terreno.mercadolibre.com.mx/MLM-2318168399-terreno-en-venta-en-cacalomacan-a-2-cuadras-de-jinetes-cerca-de-calz-pacifico-y-colegio-paideia-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=32&amp;type=item&amp;tracking_id=a57d6faf-17b2-476c-987c-3783bc1e01f3&amp;price_drop=not_apply</t>
+          <t>https://terreno.mercadolibre.com.mx/MLM-2487732477-terreno-en-venta-por-las-torres-toluca-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=32&amp;type=item&amp;tracking_id=c4dc49ac-dc63-4f0f-b01f-121745225170&amp;price_drop=not_apply</t>
         </is>
       </c>
     </row>
@@ -3977,7 +3977,7 @@
         </is>
       </c>
       <c r="B178" t="n">
-        <v>11500000</v>
+        <v>4725000</v>
       </c>
       <c r="C178" t="inlineStr">
         <is>
@@ -3986,7 +3986,7 @@
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>https://terreno.mercadolibre.com.mx/MLM-4080259510-terreno-en-venta-en-san-martin-toltepec-toluca-mexico-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=33&amp;type=item&amp;tracking_id=a57d6faf-17b2-476c-987c-3783bc1e01f3&amp;price_drop=not_apply</t>
+          <t>https://terreno.mercadolibre.com.mx/MLM-2318168399-terreno-en-venta-en-cacalomacan-a-2-cuadras-de-jinetes-cerca-de-calz-pacifico-y-colegio-paideia-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=33&amp;type=item&amp;tracking_id=c4dc49ac-dc63-4f0f-b01f-121745225170&amp;price_drop=not_apply</t>
         </is>
       </c>
     </row>
@@ -3997,7 +3997,7 @@
         </is>
       </c>
       <c r="B179" t="n">
-        <v>1840590</v>
+        <v>11500000</v>
       </c>
       <c r="C179" t="inlineStr">
         <is>
@@ -4006,7 +4006,7 @@
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>https://terreno.mercadolibre.com.mx/MLM-4080239968-terreno-en-venta-toluca-cerca-del-aeropuerto-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=34&amp;type=item&amp;tracking_id=a57d6faf-17b2-476c-987c-3783bc1e01f3&amp;price_drop=not_apply</t>
+          <t>https://terreno.mercadolibre.com.mx/MLM-4080259510-terreno-en-venta-en-san-martin-toltepec-toluca-mexico-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=34&amp;type=item&amp;tracking_id=c4dc49ac-dc63-4f0f-b01f-121745225170&amp;price_drop=not_apply</t>
         </is>
       </c>
     </row>
@@ -4017,7 +4017,7 @@
         </is>
       </c>
       <c r="B180" t="n">
-        <v>8500000</v>
+        <v>1840590</v>
       </c>
       <c r="C180" t="inlineStr">
         <is>
@@ -4026,7 +4026,7 @@
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>https://terreno.mercadolibre.com.mx/MLM-2343423083-terreno-en-san-pedro-totoltepec-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=35&amp;type=item&amp;tracking_id=a57d6faf-17b2-476c-987c-3783bc1e01f3&amp;price_drop=not_apply</t>
+          <t>https://terreno.mercadolibre.com.mx/MLM-4080239968-terreno-en-venta-toluca-cerca-del-aeropuerto-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=35&amp;type=item&amp;tracking_id=c4dc49ac-dc63-4f0f-b01f-121745225170&amp;price_drop=not_apply</t>
         </is>
       </c>
     </row>
@@ -4037,7 +4037,7 @@
         </is>
       </c>
       <c r="B181" t="n">
-        <v>35000000</v>
+        <v>8500000</v>
       </c>
       <c r="C181" t="inlineStr">
         <is>
@@ -4046,7 +4046,7 @@
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>https://terreno.mercadolibre.com.mx/MLM-2370231281-terreno-en-venta-en-toluca-reforma-y-ferr-nac-independencia-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=36&amp;type=item&amp;tracking_id=a57d6faf-17b2-476c-987c-3783bc1e01f3&amp;price_drop=not_apply</t>
+          <t>https://terreno.mercadolibre.com.mx/MLM-2343423083-terreno-en-san-pedro-totoltepec-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=36&amp;type=item&amp;tracking_id=c4dc49ac-dc63-4f0f-b01f-121745225170&amp;price_drop=not_apply</t>
         </is>
       </c>
     </row>
@@ -4057,7 +4057,7 @@
         </is>
       </c>
       <c r="B182" t="n">
-        <v>2450000</v>
+        <v>35000000</v>
       </c>
       <c r="C182" t="inlineStr">
         <is>
@@ -4066,7 +4066,7 @@
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>https://terreno.mercadolibre.com.mx/MLM-2343569515-terreno-en-santa-maria-totoltepec-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=37&amp;type=item&amp;tracking_id=a57d6faf-17b2-476c-987c-3783bc1e01f3&amp;price_drop=not_apply</t>
+          <t>https://terreno.mercadolibre.com.mx/MLM-2370231281-terreno-en-venta-en-toluca-reforma-y-ferr-nac-independencia-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=37&amp;type=item&amp;tracking_id=c4dc49ac-dc63-4f0f-b01f-121745225170&amp;price_drop=not_apply</t>
         </is>
       </c>
     </row>
@@ -4077,7 +4077,7 @@
         </is>
       </c>
       <c r="B183" t="n">
-        <v>50000000</v>
+        <v>2450000</v>
       </c>
       <c r="C183" t="inlineStr">
         <is>
@@ -4086,7 +4086,7 @@
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>https://terreno.mercadolibre.com.mx/MLM-4558160588-terreno-en-venta-en-cipres-toluca-estado-de-mexico-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=38&amp;type=item&amp;tracking_id=a57d6faf-17b2-476c-987c-3783bc1e01f3&amp;price_drop=not_apply</t>
+          <t>https://terreno.mercadolibre.com.mx/MLM-2343569515-terreno-en-santa-maria-totoltepec-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=38&amp;type=item&amp;tracking_id=c4dc49ac-dc63-4f0f-b01f-121745225170&amp;price_drop=not_apply</t>
         </is>
       </c>
     </row>
@@ -4097,7 +4097,7 @@
         </is>
       </c>
       <c r="B184" t="n">
-        <v>203547204</v>
+        <v>50000000</v>
       </c>
       <c r="C184" t="inlineStr">
         <is>
@@ -4106,7 +4106,7 @@
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>https://terreno.mercadolibre.com.mx/MLM-4261794654-terreno-en-venta-en-industrial-en-toluca-estado-de-mexico-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=39&amp;type=item&amp;tracking_id=a57d6faf-17b2-476c-987c-3783bc1e01f3&amp;price_drop=not_apply</t>
+          <t>https://terreno.mercadolibre.com.mx/MLM-4558160588-terreno-en-venta-en-cipres-toluca-estado-de-mexico-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=39&amp;type=item&amp;tracking_id=c4dc49ac-dc63-4f0f-b01f-121745225170&amp;price_drop=not_apply</t>
         </is>
       </c>
     </row>
@@ -4117,7 +4117,7 @@
         </is>
       </c>
       <c r="B185" t="n">
-        <v>14571000</v>
+        <v>203547204</v>
       </c>
       <c r="C185" t="inlineStr">
         <is>
@@ -4126,7 +4126,7 @@
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>https://terreno.mercadolibre.com.mx/MLM-4261807760-se-vende-terreno-carretera-mexico-toluca-lerma-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=40&amp;type=item&amp;tracking_id=a57d6faf-17b2-476c-987c-3783bc1e01f3&amp;price_drop=not_apply</t>
+          <t>https://terreno.mercadolibre.com.mx/MLM-4261794654-terreno-en-venta-en-industrial-en-toluca-estado-de-mexico-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=40&amp;type=item&amp;tracking_id=c4dc49ac-dc63-4f0f-b01f-121745225170&amp;price_drop=not_apply</t>
         </is>
       </c>
     </row>
@@ -4137,7 +4137,7 @@
         </is>
       </c>
       <c r="B186" t="n">
-        <v>222618909</v>
+        <v>14571000</v>
       </c>
       <c r="C186" t="inlineStr">
         <is>
@@ -4146,7 +4146,7 @@
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>https://terreno.mercadolibre.com.mx/MLM-4261859654-terreno-en-venta-industrial-en-toluca-estado-de-mexico-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=41&amp;type=item&amp;tracking_id=a57d6faf-17b2-476c-987c-3783bc1e01f3&amp;price_drop=not_apply</t>
+          <t>https://terreno.mercadolibre.com.mx/MLM-4261807760-se-vende-terreno-carretera-mexico-toluca-lerma-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=41&amp;type=item&amp;tracking_id=c4dc49ac-dc63-4f0f-b01f-121745225170&amp;price_drop=not_apply</t>
         </is>
       </c>
     </row>
@@ -4157,7 +4157,7 @@
         </is>
       </c>
       <c r="B187" t="n">
-        <v>1870000</v>
+        <v>222618909</v>
       </c>
       <c r="C187" t="inlineStr">
         <is>
@@ -4166,7 +4166,7 @@
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>https://terreno.mercadolibre.com.mx/MLM-2811993671-terreno-en-venta-en-residencial-hacienda-san-jose-en-toluca-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=42&amp;type=item&amp;float_highlight=recent_publication&amp;tracking_id=a57d6faf-17b2-476c-987c-3783bc1e01f3&amp;price_drop=not_apply</t>
+          <t>https://terreno.mercadolibre.com.mx/MLM-4261859654-terreno-en-venta-industrial-en-toluca-estado-de-mexico-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=42&amp;type=item&amp;tracking_id=c4dc49ac-dc63-4f0f-b01f-121745225170&amp;price_drop=not_apply</t>
         </is>
       </c>
     </row>
@@ -4177,7 +4177,7 @@
         </is>
       </c>
       <c r="B188" t="n">
-        <v>700000</v>
+        <v>1870000</v>
       </c>
       <c r="C188" t="inlineStr">
         <is>
@@ -4186,7 +4186,7 @@
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>https://terreno.mercadolibre.com.mx/MLM-5058024988-terreno-en-venta-en-san-lorenzo-tepaltitlan-toluca-estado-de-mexico-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=43&amp;type=item&amp;float_highlight=recent_publication&amp;tracking_id=a57d6faf-17b2-476c-987c-3783bc1e01f3&amp;price_drop=not_apply</t>
+          <t>https://terreno.mercadolibre.com.mx/MLM-2811993671-terreno-en-venta-en-residencial-hacienda-san-jose-en-toluca-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=43&amp;type=item&amp;float_highlight=recent_publication&amp;tracking_id=c4dc49ac-dc63-4f0f-b01f-121745225170&amp;price_drop=not_apply</t>
         </is>
       </c>
     </row>
@@ -4197,7 +4197,7 @@
         </is>
       </c>
       <c r="B189" t="n">
-        <v>3240000</v>
+        <v>132000000</v>
       </c>
       <c r="C189" t="inlineStr">
         <is>
@@ -4206,7 +4206,7 @@
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>https://terreno.mercadolibre.com.mx/MLM-5058177406-terreno-en-venta-en-san-francisco-totoltepec-toluca-estado-de-mexico-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=44&amp;type=item&amp;float_highlight=recent_publication&amp;tracking_id=a57d6faf-17b2-476c-987c-3783bc1e01f3&amp;price_drop=not_apply</t>
+          <t>https://terreno.mercadolibre.com.mx/MLM-5064030156-terreno-en-venta-en-parque-industrial-el-coecillo-toluca-estado-de-mexico-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=44&amp;type=item&amp;float_highlight=recent_publication&amp;tracking_id=c4dc49ac-dc63-4f0f-b01f-121745225170&amp;price_drop=not_apply</t>
         </is>
       </c>
     </row>
@@ -4217,7 +4217,7 @@
         </is>
       </c>
       <c r="B190" t="n">
-        <v>132000000</v>
+        <v>279450</v>
       </c>
       <c r="C190" t="inlineStr">
         <is>
@@ -4226,7 +4226,7 @@
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>https://terreno.mercadolibre.com.mx/MLM-5064030156-terreno-en-venta-en-parque-industrial-el-coecillo-toluca-estado-de-mexico-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=45&amp;type=item&amp;float_highlight=recent_publication&amp;tracking_id=a57d6faf-17b2-476c-987c-3783bc1e01f3&amp;price_drop=not_apply</t>
+          <t>https://terreno.mercadolibre.com.mx/MLM-5060346586-ultimos-2-lotes-en-venta-en-san-cayetano-muy-cerca-de-la-unsa-en-toluca-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=45&amp;type=item&amp;float_highlight=recent_publication&amp;tracking_id=c4dc49ac-dc63-4f0f-b01f-121745225170&amp;price_drop=not_apply</t>
         </is>
       </c>
     </row>
@@ -4237,7 +4237,7 @@
         </is>
       </c>
       <c r="B191" t="n">
-        <v>279450</v>
+        <v>23500000</v>
       </c>
       <c r="C191" t="inlineStr">
         <is>
@@ -4246,7 +4246,7 @@
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>https://terreno.mercadolibre.com.mx/MLM-5060346586-ultimos-2-lotes-en-venta-en-san-cayetano-muy-cerca-de-la-unsa-en-toluca-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=46&amp;type=item&amp;float_highlight=recent_publication&amp;tracking_id=a57d6faf-17b2-476c-987c-3783bc1e01f3&amp;price_drop=not_apply</t>
+          <t>https://terreno.mercadolibre.com.mx/MLM-4950598656-terreno-comercial-en-venta-en-san-bernardino-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=46&amp;type=item&amp;tracking_id=c4dc49ac-dc63-4f0f-b01f-121745225170&amp;price_drop=not_apply</t>
         </is>
       </c>
     </row>
@@ -4257,7 +4257,7 @@
         </is>
       </c>
       <c r="B192" t="n">
-        <v>9215400</v>
+        <v>8760000</v>
       </c>
       <c r="C192" t="inlineStr">
         <is>
@@ -4266,7 +4266,7 @@
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>https://terreno.mercadolibre.com.mx/MLM-5047581202-terreno-comercial-en-venta-en-santa-cruz-otzacatipan-toluca-mexico-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=47&amp;type=item&amp;float_highlight=recent_publication&amp;tracking_id=a57d6faf-17b2-476c-987c-3783bc1e01f3&amp;price_drop=not_apply</t>
+          <t>https://terreno.mercadolibre.com.mx/MLM-4761562052-terreno-comercial-en-venta-en-santa-maria-totoltepec-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=47&amp;type=item&amp;tracking_id=c4dc49ac-dc63-4f0f-b01f-121745225170&amp;price_drop=not_apply</t>
         </is>
       </c>
     </row>
@@ -4277,7 +4277,7 @@
         </is>
       </c>
       <c r="B193" t="n">
-        <v>8502990</v>
+        <v>26320000</v>
       </c>
       <c r="C193" t="inlineStr">
         <is>
@@ -4286,7 +4286,7 @@
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>https://terreno.mercadolibre.com.mx/MLM-5047581198-terreno-comercial-en-venta-en-santa-cruz-otzacatipan-toluca-mexico-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=48&amp;type=item&amp;float_highlight=recent_publication&amp;tracking_id=a57d6faf-17b2-476c-987c-3783bc1e01f3&amp;price_drop=not_apply</t>
+          <t>https://terreno.mercadolibre.com.mx/MLM-4790443980-terreno-residencial-en-venta-en-la-venta-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=48&amp;type=item&amp;tracking_id=c4dc49ac-dc63-4f0f-b01f-121745225170&amp;price_drop=not_apply</t>
         </is>
       </c>
     </row>
@@ -4306,7 +4306,7 @@
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>https://terreno.mercadolibre.com.mx/MLM-3835159420-lotes-de-terreno-desde-104-m2-en-venta-cerca-del-aeropuerto-de-toluca-en-la-constitucion-toltepec-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=1&amp;type=item&amp;tracking_id=ff6bedc1-9bb0-4a87-b0ff-198407b4640e&amp;price_drop=not_apply</t>
+          <t>https://terreno.mercadolibre.com.mx/MLM-3835159420-lotes-de-terreno-desde-104-m2-en-venta-cerca-del-aeropuerto-de-toluca-en-la-constitucion-toltepec-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=1&amp;type=item&amp;tracking_id=64db4c17-d904-410a-9333-7d5af75aa233&amp;price_drop=not_apply</t>
         </is>
       </c>
     </row>
@@ -4326,7 +4326,7 @@
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>https://terreno.mercadolibre.com.mx/MLM-2810992285-construye-tu-residencia-en-la-zona-de-mayor-proyeccion-de-toluca-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=2&amp;type=item&amp;float_highlight=recent_publication&amp;tracking_id=ff6bedc1-9bb0-4a87-b0ff-198407b4640e&amp;price_drop=not_apply</t>
+          <t>https://terreno.mercadolibre.com.mx/MLM-2810992285-construye-tu-residencia-en-la-zona-de-mayor-proyeccion-de-toluca-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=2&amp;type=item&amp;float_highlight=recent_publication&amp;tracking_id=64db4c17-d904-410a-9333-7d5af75aa233&amp;price_drop=not_apply</t>
         </is>
       </c>
     </row>
@@ -4346,7 +4346,7 @@
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>https://terreno.mercadolibre.com.mx/MLM-3847495816-el-mejor-terreno-del-condominio-puede-ser-tuyo-a-un-precio-de-oportunidad-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=3&amp;type=item&amp;tracking_id=ff6bedc1-9bb0-4a87-b0ff-198407b4640e&amp;price_drop=not_apply</t>
+          <t>https://terreno.mercadolibre.com.mx/MLM-3847495816-el-mejor-terreno-del-condominio-puede-ser-tuyo-a-un-precio-de-oportunidad-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=3&amp;type=item&amp;tracking_id=64db4c17-d904-410a-9333-7d5af75aa233&amp;price_drop=not_apply</t>
         </is>
       </c>
     </row>
@@ -4357,7 +4357,7 @@
         </is>
       </c>
       <c r="B197" t="n">
-        <v>7600000</v>
+        <v>649000</v>
       </c>
       <c r="C197" t="inlineStr">
         <is>
@@ -4366,7 +4366,7 @@
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>https://terreno.mercadolibre.com.mx/MLM-2231593183-terreno-en-venta-en-san-mateo-oxtotitlan-toluca-mexico-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=4&amp;type=item&amp;tracking_id=ff6bedc1-9bb0-4a87-b0ff-198407b4640e&amp;price_drop=not_apply</t>
+          <t>https://terreno.mercadolibre.com.mx/MLM-2753915589-terreno-bardeado-en-cacalomacan-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=4&amp;type=item&amp;tracking_id=64db4c17-d904-410a-9333-7d5af75aa233&amp;price_drop=false</t>
         </is>
       </c>
     </row>
@@ -4377,7 +4377,7 @@
         </is>
       </c>
       <c r="B198" t="n">
-        <v>649000</v>
+        <v>7600000</v>
       </c>
       <c r="C198" t="inlineStr">
         <is>
@@ -4386,7 +4386,7 @@
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>https://terreno.mercadolibre.com.mx/MLM-2753915589-terreno-bardeado-en-cacalomacan-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=5&amp;type=item&amp;tracking_id=ff6bedc1-9bb0-4a87-b0ff-198407b4640e&amp;price_drop=false</t>
+          <t>https://terreno.mercadolibre.com.mx/MLM-2231593183-terreno-en-venta-en-san-mateo-oxtotitlan-toluca-mexico-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=5&amp;type=item&amp;tracking_id=64db4c17-d904-410a-9333-7d5af75aa233&amp;price_drop=not_apply</t>
         </is>
       </c>
     </row>
@@ -4406,7 +4406,7 @@
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>https://terreno.mercadolibre.com.mx/MLM-2716356593-terreno-en-venta-en-colonia-nueva-santa-maria-de-las-rosas-toluca-estado-de-mexico-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=6&amp;type=item&amp;tracking_id=ff6bedc1-9bb0-4a87-b0ff-198407b4640e&amp;price_drop=not_apply</t>
+          <t>https://terreno.mercadolibre.com.mx/MLM-2716356593-terreno-en-venta-en-colonia-nueva-santa-maria-de-las-rosas-toluca-estado-de-mexico-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=6&amp;type=item&amp;tracking_id=64db4c17-d904-410a-9333-7d5af75aa233&amp;price_drop=not_apply</t>
         </is>
       </c>
     </row>
@@ -4426,7 +4426,7 @@
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>https://terreno.mercadolibre.com.mx/MLM-4660497978-terreno-en-venta-en-toluca-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=7&amp;type=item&amp;tracking_id=ff6bedc1-9bb0-4a87-b0ff-198407b4640e&amp;price_drop=not_apply</t>
+          <t>https://terreno.mercadolibre.com.mx/MLM-4660497978-terreno-en-venta-en-toluca-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=7&amp;type=item&amp;tracking_id=64db4c17-d904-410a-9333-7d5af75aa233&amp;price_drop=not_apply</t>
         </is>
       </c>
     </row>
@@ -4446,7 +4446,7 @@
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>https://terreno.mercadolibre.com.mx/MLM-4388186170-terreno-industrial-en-venta-en-toluca-san-cayetano-a-un-lado-de-la-caseta-el-dorado-cerca-puerta-mexico-recinto-aduanal-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=8&amp;type=item&amp;tracking_id=ff6bedc1-9bb0-4a87-b0ff-198407b4640e&amp;price_drop=not_apply</t>
+          <t>https://terreno.mercadolibre.com.mx/MLM-4388186170-terreno-industrial-en-venta-en-toluca-san-cayetano-a-un-lado-de-la-caseta-el-dorado-cerca-puerta-mexico-recinto-aduanal-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=8&amp;type=item&amp;tracking_id=64db4c17-d904-410a-9333-7d5af75aa233&amp;price_drop=not_apply</t>
         </is>
       </c>
     </row>
@@ -4466,7 +4466,7 @@
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>https://terreno.mercadolibre.com.mx/MLM-2716629645-terreno-industrial-en-venta-en-palmillas-son-13-hectareas-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=9&amp;type=item&amp;tracking_id=ff6bedc1-9bb0-4a87-b0ff-198407b4640e&amp;price_drop=not_apply</t>
+          <t>https://terreno.mercadolibre.com.mx/MLM-2716629645-terreno-industrial-en-venta-en-palmillas-son-13-hectareas-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=9&amp;type=item&amp;tracking_id=64db4c17-d904-410a-9333-7d5af75aa233&amp;price_drop=not_apply</t>
         </is>
       </c>
     </row>
@@ -4486,7 +4486,7 @@
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>https://terreno.mercadolibre.com.mx/MLM-2748643873-terreno-en-venta-a-pie-de-carretera-toluca-atlacomulco-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=10&amp;type=item&amp;tracking_id=ff6bedc1-9bb0-4a87-b0ff-198407b4640e&amp;price_drop=not_apply</t>
+          <t>https://terreno.mercadolibre.com.mx/MLM-2748643873-terreno-en-venta-a-pie-de-carretera-toluca-atlacomulco-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=10&amp;type=item&amp;tracking_id=64db4c17-d904-410a-9333-7d5af75aa233&amp;price_drop=not_apply</t>
         </is>
       </c>
     </row>
@@ -4506,7 +4506,7 @@
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>https://terreno.mercadolibre.com.mx/MLM-4790479866-terreno-regular-con-infraestructura-lista-base-solida-para-tu-proyecto-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=11&amp;type=item&amp;tracking_id=ff6bedc1-9bb0-4a87-b0ff-198407b4640e&amp;price_drop=not_apply</t>
+          <t>https://terreno.mercadolibre.com.mx/MLM-4790479866-terreno-regular-con-infraestructura-lista-base-solida-para-tu-proyecto-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=11&amp;type=item&amp;tracking_id=64db4c17-d904-410a-9333-7d5af75aa233&amp;price_drop=not_apply</t>
         </is>
       </c>
     </row>
@@ -4526,7 +4526,7 @@
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>https://terreno.mercadolibre.com.mx/MLM-5015164202-venta-terreno-lotes-palmillas-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=12&amp;type=item&amp;tracking_id=ff6bedc1-9bb0-4a87-b0ff-198407b4640e&amp;price_drop=not_apply</t>
+          <t>https://terreno.mercadolibre.com.mx/MLM-5015164202-venta-terreno-lotes-palmillas-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=12&amp;type=item&amp;tracking_id=64db4c17-d904-410a-9333-7d5af75aa233&amp;price_drop=not_apply</t>
         </is>
       </c>
     </row>
@@ -4546,7 +4546,7 @@
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>https://terreno.mercadolibre.com.mx/MLM-4416680104-terreno-en-venta-sobre-calzada-del-pacifico-cacalomacan-por-ocho-cedros-toluca-cas-23000-m2-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=13&amp;type=item&amp;tracking_id=ff6bedc1-9bb0-4a87-b0ff-198407b4640e&amp;price_drop=not_apply</t>
+          <t>https://terreno.mercadolibre.com.mx/MLM-4416680104-terreno-en-venta-sobre-calzada-del-pacifico-cacalomacan-por-ocho-cedros-toluca-cas-23000-m2-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=13&amp;type=item&amp;tracking_id=64db4c17-d904-410a-9333-7d5af75aa233&amp;price_drop=not_apply</t>
         </is>
       </c>
     </row>
@@ -4566,7 +4566,7 @@
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>https://terreno.mercadolibre.com.mx/MLM-2736455271-terreno-de-2-hectareas-en-zona-urbana-santa-maria-totoltepec-estado-de-mexico-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=14&amp;type=item&amp;tracking_id=ff6bedc1-9bb0-4a87-b0ff-198407b4640e&amp;price_drop=not_apply</t>
+          <t>https://terreno.mercadolibre.com.mx/MLM-2736455271-terreno-de-2-hectareas-en-zona-urbana-santa-maria-totoltepec-estado-de-mexico-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=14&amp;type=item&amp;tracking_id=64db4c17-d904-410a-9333-7d5af75aa233&amp;price_drop=not_apply</t>
         </is>
       </c>
     </row>
@@ -4577,7 +4577,7 @@
         </is>
       </c>
       <c r="B208" t="n">
-        <v>1831680</v>
+        <v>299999</v>
       </c>
       <c r="C208" t="inlineStr">
         <is>
@@ -4586,7 +4586,7 @@
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>https://terreno.mercadolibre.com.mx/MLM-2804712255-venta-terreno-paraje-san-rafael-en-toluca-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=15&amp;type=item&amp;float_highlight=recent_publication&amp;tracking_id=ff6bedc1-9bb0-4a87-b0ff-198407b4640e&amp;price_drop=not_apply</t>
+          <t>https://terreno.mercadolibre.com.mx/MLM-5082958514-lotes-a-10-min-de-paideia-propiedad-desde-230-m-en-adelante-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=15&amp;type=item&amp;float_highlight=recent_publication&amp;tracking_id=64db4c17-d904-410a-9333-7d5af75aa233&amp;price_drop=not_apply</t>
         </is>
       </c>
     </row>
@@ -4597,7 +4597,7 @@
         </is>
       </c>
       <c r="B209" t="n">
-        <v>1485000</v>
+        <v>1831680</v>
       </c>
       <c r="C209" t="inlineStr">
         <is>
@@ -4606,7 +4606,7 @@
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>https://terreno.mercadolibre.com.mx/MLM-2187928841-venta-terreno-cerrillo-vista-hermosa-toluca-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=16&amp;type=item&amp;tracking_id=ff6bedc1-9bb0-4a87-b0ff-198407b4640e&amp;price_drop=not_apply</t>
+          <t>https://terreno.mercadolibre.com.mx/MLM-2804712255-venta-terreno-paraje-san-rafael-en-toluca-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=16&amp;type=item&amp;float_highlight=recent_publication&amp;tracking_id=64db4c17-d904-410a-9333-7d5af75aa233&amp;price_drop=not_apply</t>
         </is>
       </c>
     </row>
@@ -4617,7 +4617,7 @@
         </is>
       </c>
       <c r="B210" t="n">
-        <v>4805040</v>
+        <v>1485000</v>
       </c>
       <c r="C210" t="inlineStr">
         <is>
@@ -4626,7 +4626,7 @@
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>https://terreno.mercadolibre.com.mx/MLM-3705026808-venta-de-terreno-en-cacalomacan-a-20-min-centro-toluca-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=17&amp;type=item&amp;tracking_id=ff6bedc1-9bb0-4a87-b0ff-198407b4640e&amp;price_drop=not_apply</t>
+          <t>https://terreno.mercadolibre.com.mx/MLM-2187928841-venta-terreno-cerrillo-vista-hermosa-toluca-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=17&amp;type=item&amp;tracking_id=64db4c17-d904-410a-9333-7d5af75aa233&amp;price_drop=not_apply</t>
         </is>
       </c>
     </row>
@@ -4637,7 +4637,7 @@
         </is>
       </c>
       <c r="B211" t="n">
-        <v>1920000</v>
+        <v>4805040</v>
       </c>
       <c r="C211" t="inlineStr">
         <is>
@@ -4646,7 +4646,7 @@
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>https://terreno.mercadolibre.com.mx/MLM-4119789692-terreno-en-venta-residencial-ex-hacienda-san-jose-toluca-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=18&amp;type=item&amp;tracking_id=ff6bedc1-9bb0-4a87-b0ff-198407b4640e&amp;price_drop=not_apply</t>
+          <t>https://terreno.mercadolibre.com.mx/MLM-3705026808-venta-de-terreno-en-cacalomacan-a-20-min-centro-toluca-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=18&amp;type=item&amp;tracking_id=64db4c17-d904-410a-9333-7d5af75aa233&amp;price_drop=not_apply</t>
         </is>
       </c>
     </row>
@@ -4657,7 +4657,7 @@
         </is>
       </c>
       <c r="B212" t="n">
-        <v>1244380</v>
+        <v>1920000</v>
       </c>
       <c r="C212" t="inlineStr">
         <is>
@@ -4666,7 +4666,7 @@
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>https://terreno.mercadolibre.com.mx/MLM-4826508826-venta-de-lote-de-terreno-residencial-cerca-de-galerias-metepec-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=19&amp;type=item&amp;tracking_id=ff6bedc1-9bb0-4a87-b0ff-198407b4640e&amp;price_drop=not_apply</t>
+          <t>https://terreno.mercadolibre.com.mx/MLM-4119789692-terreno-en-venta-residencial-ex-hacienda-san-jose-toluca-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=19&amp;type=item&amp;tracking_id=64db4c17-d904-410a-9333-7d5af75aa233&amp;price_drop=not_apply</t>
         </is>
       </c>
     </row>
@@ -4677,7 +4677,7 @@
         </is>
       </c>
       <c r="B213" t="n">
-        <v>8565858</v>
+        <v>1244380</v>
       </c>
       <c r="C213" t="inlineStr">
         <is>
@@ -4686,7 +4686,7 @@
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>https://terreno.mercadolibre.com.mx/MLM-4080298834-terreno-en-venta-en-san-miguel-zacango-toluca-mexico-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=20&amp;type=item&amp;tracking_id=ff6bedc1-9bb0-4a87-b0ff-198407b4640e&amp;price_drop=not_apply</t>
+          <t>https://terreno.mercadolibre.com.mx/MLM-4826508826-venta-de-lote-de-terreno-residencial-cerca-de-galerias-metepec-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=20&amp;type=item&amp;tracking_id=64db4c17-d904-410a-9333-7d5af75aa233&amp;price_drop=not_apply</t>
         </is>
       </c>
     </row>
@@ -4697,7 +4697,7 @@
         </is>
       </c>
       <c r="B214" t="n">
-        <v>8500000</v>
+        <v>8565858</v>
       </c>
       <c r="C214" t="inlineStr">
         <is>
@@ -4706,7 +4706,7 @@
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>https://terreno.mercadolibre.com.mx/MLM-2310439697-se-vende-terreno-en-toluca-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=21&amp;type=item&amp;tracking_id=ff6bedc1-9bb0-4a87-b0ff-198407b4640e&amp;price_drop=not_apply</t>
+          <t>https://terreno.mercadolibre.com.mx/MLM-4080298834-terreno-en-venta-en-san-miguel-zacango-toluca-mexico-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=21&amp;type=item&amp;tracking_id=64db4c17-d904-410a-9333-7d5af75aa233&amp;price_drop=not_apply</t>
         </is>
       </c>
     </row>
@@ -4717,7 +4717,7 @@
         </is>
       </c>
       <c r="B215" t="n">
-        <v>1300000</v>
+        <v>8500000</v>
       </c>
       <c r="C215" t="inlineStr">
         <is>
@@ -4726,7 +4726,7 @@
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>https://terreno.mercadolibre.com.mx/MLM-4495237624-lote-disponible-en-conjunto-ambar-toluca-edo-mex-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=22&amp;type=item&amp;tracking_id=ff6bedc1-9bb0-4a87-b0ff-198407b4640e&amp;price_drop=not_apply</t>
+          <t>https://terreno.mercadolibre.com.mx/MLM-2310439697-se-vende-terreno-en-toluca-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=22&amp;type=item&amp;tracking_id=64db4c17-d904-410a-9333-7d5af75aa233&amp;price_drop=not_apply</t>
         </is>
       </c>
     </row>
@@ -4737,7 +4737,7 @@
         </is>
       </c>
       <c r="B216" t="n">
-        <v>1200000</v>
+        <v>1300000</v>
       </c>
       <c r="C216" t="inlineStr">
         <is>
@@ -4746,7 +4746,7 @@
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>https://terreno.mercadolibre.com.mx/MLM-2485559517-terreno-en-venta-en-toluca-san-andres-cuexcontitlan-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=23&amp;type=item&amp;tracking_id=ff6bedc1-9bb0-4a87-b0ff-198407b4640e&amp;price_drop=not_apply</t>
+          <t>https://terreno.mercadolibre.com.mx/MLM-4495237624-lote-disponible-en-conjunto-ambar-toluca-edo-mex-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=23&amp;type=item&amp;tracking_id=64db4c17-d904-410a-9333-7d5af75aa233&amp;price_drop=not_apply</t>
         </is>
       </c>
     </row>
@@ -4757,7 +4757,7 @@
         </is>
       </c>
       <c r="B217" t="n">
-        <v>38634000</v>
+        <v>1200000</v>
       </c>
       <c r="C217" t="inlineStr">
         <is>
@@ -4766,7 +4766,7 @@
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>https://terreno.mercadolibre.com.mx/MLM-2431684449-terreno-en-toluca-25756-m2-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=24&amp;type=item&amp;tracking_id=ff6bedc1-9bb0-4a87-b0ff-198407b4640e&amp;price_drop=not_apply</t>
+          <t>https://terreno.mercadolibre.com.mx/MLM-2485559517-terreno-en-venta-en-toluca-san-andres-cuexcontitlan-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=24&amp;type=item&amp;tracking_id=64db4c17-d904-410a-9333-7d5af75aa233&amp;price_drop=not_apply</t>
         </is>
       </c>
     </row>
@@ -4777,7 +4777,7 @@
         </is>
       </c>
       <c r="B218" t="n">
-        <v>5625000</v>
+        <v>38634000</v>
       </c>
       <c r="C218" t="inlineStr">
         <is>
@@ -4786,7 +4786,7 @@
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>https://terreno.mercadolibre.com.mx/MLM-2323267483-terreno-en-venta-2250m2-en-san-felipe-tlalmimilolpan-toluca-mexico-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=25&amp;type=item&amp;tracking_id=ff6bedc1-9bb0-4a87-b0ff-198407b4640e&amp;price_drop=not_apply</t>
+          <t>https://terreno.mercadolibre.com.mx/MLM-2431684449-terreno-en-toluca-25756-m2-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=25&amp;type=item&amp;tracking_id=64db4c17-d904-410a-9333-7d5af75aa233&amp;price_drop=not_apply</t>
         </is>
       </c>
     </row>
@@ -4797,7 +4797,7 @@
         </is>
       </c>
       <c r="B219" t="n">
-        <v>25650000</v>
+        <v>5625000</v>
       </c>
       <c r="C219" t="inlineStr">
         <is>
@@ -4806,7 +4806,7 @@
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>https://terreno.mercadolibre.com.mx/MLM-4169951646-terreno-en-venta-por-las-torres-toluca-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=26&amp;type=item&amp;tracking_id=ff6bedc1-9bb0-4a87-b0ff-198407b4640e&amp;price_drop=not_apply</t>
+          <t>https://terreno.mercadolibre.com.mx/MLM-2323267483-terreno-en-venta-2250m2-en-san-felipe-tlalmimilolpan-toluca-mexico-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=26&amp;type=item&amp;tracking_id=64db4c17-d904-410a-9333-7d5af75aa233&amp;price_drop=not_apply</t>
         </is>
       </c>
     </row>
@@ -4817,7 +4817,7 @@
         </is>
       </c>
       <c r="B220" t="n">
-        <v>4800000</v>
+        <v>25650000</v>
       </c>
       <c r="C220" t="inlineStr">
         <is>
@@ -4826,7 +4826,7 @@
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t>https://terreno.mercadolibre.com.mx/MLM-4416373342-terreno-en-venta-en-san-lorenzo-tepaltitlan-centro-toluca-mexico-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=27&amp;type=item&amp;tracking_id=ff6bedc1-9bb0-4a87-b0ff-198407b4640e&amp;price_drop=not_apply</t>
+          <t>https://terreno.mercadolibre.com.mx/MLM-4169951646-terreno-en-venta-por-las-torres-toluca-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=27&amp;type=item&amp;tracking_id=64db4c17-d904-410a-9333-7d5af75aa233&amp;price_drop=not_apply</t>
         </is>
       </c>
     </row>
@@ -4837,7 +4837,7 @@
         </is>
       </c>
       <c r="B221" t="n">
-        <v>14490000</v>
+        <v>4800000</v>
       </c>
       <c r="C221" t="inlineStr">
         <is>
@@ -4846,7 +4846,7 @@
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>https://terreno.mercadolibre.com.mx/MLM-2584697469-oportunidad-de-inversion-terreno-de-9993-m-cerca-de-parque-toluca-2000-ideal-para-naves-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=28&amp;type=item&amp;tracking_id=ff6bedc1-9bb0-4a87-b0ff-198407b4640e&amp;price_drop=not_apply</t>
+          <t>https://terreno.mercadolibre.com.mx/MLM-4416373342-terreno-en-venta-en-san-lorenzo-tepaltitlan-centro-toluca-mexico-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=28&amp;type=item&amp;tracking_id=64db4c17-d904-410a-9333-7d5af75aa233&amp;price_drop=not_apply</t>
         </is>
       </c>
     </row>
@@ -4857,7 +4857,7 @@
         </is>
       </c>
       <c r="B222" t="n">
-        <v>24520000</v>
+        <v>14490000</v>
       </c>
       <c r="C222" t="inlineStr">
         <is>
@@ -4866,7 +4866,7 @@
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>https://terreno.mercadolibre.com.mx/MLM-4169951774-terreno-en-venta-por-las-torres-toluca-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=29&amp;type=item&amp;tracking_id=ff6bedc1-9bb0-4a87-b0ff-198407b4640e&amp;price_drop=not_apply</t>
+          <t>https://terreno.mercadolibre.com.mx/MLM-2584697469-oportunidad-de-inversion-terreno-de-9993-m-cerca-de-parque-toluca-2000-ideal-para-naves-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=29&amp;type=item&amp;tracking_id=64db4c17-d904-410a-9333-7d5af75aa233&amp;price_drop=not_apply</t>
         </is>
       </c>
     </row>
@@ -4877,7 +4877,7 @@
         </is>
       </c>
       <c r="B223" t="n">
-        <v>12024000</v>
+        <v>24520000</v>
       </c>
       <c r="C223" t="inlineStr">
         <is>
@@ -4886,7 +4886,7 @@
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>https://terreno.mercadolibre.com.mx/MLM-2323192153-terreno-en-venta-8016-m2-en-san-felipe-tlalmimilolpan-toluca-mexico-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=30&amp;type=item&amp;tracking_id=ff6bedc1-9bb0-4a87-b0ff-198407b4640e&amp;price_drop=not_apply</t>
+          <t>https://terreno.mercadolibre.com.mx/MLM-4169951774-terreno-en-venta-por-las-torres-toluca-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=30&amp;type=item&amp;tracking_id=64db4c17-d904-410a-9333-7d5af75aa233&amp;price_drop=not_apply</t>
         </is>
       </c>
     </row>
@@ -4897,7 +4897,7 @@
         </is>
       </c>
       <c r="B224" t="n">
-        <v>13650000</v>
+        <v>12024000</v>
       </c>
       <c r="C224" t="inlineStr">
         <is>
@@ -4906,7 +4906,7 @@
       </c>
       <c r="D224" t="inlineStr">
         <is>
-          <t>https://terreno.mercadolibre.com.mx/MLM-2487732477-terreno-en-venta-por-las-torres-toluca-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=31&amp;type=item&amp;tracking_id=ff6bedc1-9bb0-4a87-b0ff-198407b4640e&amp;price_drop=not_apply</t>
+          <t>https://terreno.mercadolibre.com.mx/MLM-2323192153-terreno-en-venta-8016-m2-en-san-felipe-tlalmimilolpan-toluca-mexico-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=31&amp;type=item&amp;tracking_id=64db4c17-d904-410a-9333-7d5af75aa233&amp;price_drop=not_apply</t>
         </is>
       </c>
     </row>
@@ -4917,7 +4917,7 @@
         </is>
       </c>
       <c r="B225" t="n">
-        <v>4725000</v>
+        <v>13650000</v>
       </c>
       <c r="C225" t="inlineStr">
         <is>
@@ -4926,7 +4926,7 @@
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t>https://terreno.mercadolibre.com.mx/MLM-2318168399-terreno-en-venta-en-cacalomacan-a-2-cuadras-de-jinetes-cerca-de-calz-pacifico-y-colegio-paideia-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=32&amp;type=item&amp;tracking_id=ff6bedc1-9bb0-4a87-b0ff-198407b4640e&amp;price_drop=not_apply</t>
+          <t>https://terreno.mercadolibre.com.mx/MLM-2487732477-terreno-en-venta-por-las-torres-toluca-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=32&amp;type=item&amp;tracking_id=64db4c17-d904-410a-9333-7d5af75aa233&amp;price_drop=not_apply</t>
         </is>
       </c>
     </row>
@@ -4937,7 +4937,7 @@
         </is>
       </c>
       <c r="B226" t="n">
-        <v>11500000</v>
+        <v>4725000</v>
       </c>
       <c r="C226" t="inlineStr">
         <is>
@@ -4946,7 +4946,7 @@
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>https://terreno.mercadolibre.com.mx/MLM-4080259510-terreno-en-venta-en-san-martin-toltepec-toluca-mexico-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=33&amp;type=item&amp;tracking_id=ff6bedc1-9bb0-4a87-b0ff-198407b4640e&amp;price_drop=not_apply</t>
+          <t>https://terreno.mercadolibre.com.mx/MLM-2318168399-terreno-en-venta-en-cacalomacan-a-2-cuadras-de-jinetes-cerca-de-calz-pacifico-y-colegio-paideia-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=33&amp;type=item&amp;tracking_id=64db4c17-d904-410a-9333-7d5af75aa233&amp;price_drop=not_apply</t>
         </is>
       </c>
     </row>
@@ -4957,7 +4957,7 @@
         </is>
       </c>
       <c r="B227" t="n">
-        <v>1840590</v>
+        <v>11500000</v>
       </c>
       <c r="C227" t="inlineStr">
         <is>
@@ -4966,7 +4966,7 @@
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>https://terreno.mercadolibre.com.mx/MLM-4080239968-terreno-en-venta-toluca-cerca-del-aeropuerto-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=34&amp;type=item&amp;tracking_id=ff6bedc1-9bb0-4a87-b0ff-198407b4640e&amp;price_drop=not_apply</t>
+          <t>https://terreno.mercadolibre.com.mx/MLM-4080259510-terreno-en-venta-en-san-martin-toltepec-toluca-mexico-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=34&amp;type=item&amp;tracking_id=64db4c17-d904-410a-9333-7d5af75aa233&amp;price_drop=not_apply</t>
         </is>
       </c>
     </row>
@@ -4977,7 +4977,7 @@
         </is>
       </c>
       <c r="B228" t="n">
-        <v>8500000</v>
+        <v>1840590</v>
       </c>
       <c r="C228" t="inlineStr">
         <is>
@@ -4986,7 +4986,7 @@
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>https://terreno.mercadolibre.com.mx/MLM-2343423083-terreno-en-san-pedro-totoltepec-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=35&amp;type=item&amp;tracking_id=ff6bedc1-9bb0-4a87-b0ff-198407b4640e&amp;price_drop=not_apply</t>
+          <t>https://terreno.mercadolibre.com.mx/MLM-4080239968-terreno-en-venta-toluca-cerca-del-aeropuerto-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=35&amp;type=item&amp;tracking_id=64db4c17-d904-410a-9333-7d5af75aa233&amp;price_drop=not_apply</t>
         </is>
       </c>
     </row>
@@ -4997,7 +4997,7 @@
         </is>
       </c>
       <c r="B229" t="n">
-        <v>35000000</v>
+        <v>8500000</v>
       </c>
       <c r="C229" t="inlineStr">
         <is>
@@ -5006,7 +5006,7 @@
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>https://terreno.mercadolibre.com.mx/MLM-2370231281-terreno-en-venta-en-toluca-reforma-y-ferr-nac-independencia-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=36&amp;type=item&amp;tracking_id=ff6bedc1-9bb0-4a87-b0ff-198407b4640e&amp;price_drop=not_apply</t>
+          <t>https://terreno.mercadolibre.com.mx/MLM-2343423083-terreno-en-san-pedro-totoltepec-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=36&amp;type=item&amp;tracking_id=64db4c17-d904-410a-9333-7d5af75aa233&amp;price_drop=not_apply</t>
         </is>
       </c>
     </row>
@@ -5017,7 +5017,7 @@
         </is>
       </c>
       <c r="B230" t="n">
-        <v>2450000</v>
+        <v>35000000</v>
       </c>
       <c r="C230" t="inlineStr">
         <is>
@@ -5026,7 +5026,7 @@
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t>https://terreno.mercadolibre.com.mx/MLM-2343569515-terreno-en-santa-maria-totoltepec-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=37&amp;type=item&amp;tracking_id=ff6bedc1-9bb0-4a87-b0ff-198407b4640e&amp;price_drop=not_apply</t>
+          <t>https://terreno.mercadolibre.com.mx/MLM-2370231281-terreno-en-venta-en-toluca-reforma-y-ferr-nac-independencia-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=37&amp;type=item&amp;tracking_id=64db4c17-d904-410a-9333-7d5af75aa233&amp;price_drop=not_apply</t>
         </is>
       </c>
     </row>
@@ -5037,7 +5037,7 @@
         </is>
       </c>
       <c r="B231" t="n">
-        <v>50000000</v>
+        <v>2450000</v>
       </c>
       <c r="C231" t="inlineStr">
         <is>
@@ -5046,7 +5046,7 @@
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>https://terreno.mercadolibre.com.mx/MLM-4558160588-terreno-en-venta-en-cipres-toluca-estado-de-mexico-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=38&amp;type=item&amp;tracking_id=ff6bedc1-9bb0-4a87-b0ff-198407b4640e&amp;price_drop=not_apply</t>
+          <t>https://terreno.mercadolibre.com.mx/MLM-2343569515-terreno-en-santa-maria-totoltepec-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=38&amp;type=item&amp;tracking_id=64db4c17-d904-410a-9333-7d5af75aa233&amp;price_drop=not_apply</t>
         </is>
       </c>
     </row>
@@ -5057,7 +5057,7 @@
         </is>
       </c>
       <c r="B232" t="n">
-        <v>203547204</v>
+        <v>50000000</v>
       </c>
       <c r="C232" t="inlineStr">
         <is>
@@ -5066,7 +5066,7 @@
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>https://terreno.mercadolibre.com.mx/MLM-4261794654-terreno-en-venta-en-industrial-en-toluca-estado-de-mexico-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=39&amp;type=item&amp;tracking_id=ff6bedc1-9bb0-4a87-b0ff-198407b4640e&amp;price_drop=not_apply</t>
+          <t>https://terreno.mercadolibre.com.mx/MLM-4558160588-terreno-en-venta-en-cipres-toluca-estado-de-mexico-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=39&amp;type=item&amp;tracking_id=64db4c17-d904-410a-9333-7d5af75aa233&amp;price_drop=not_apply</t>
         </is>
       </c>
     </row>
@@ -5077,7 +5077,7 @@
         </is>
       </c>
       <c r="B233" t="n">
-        <v>14571000</v>
+        <v>203547204</v>
       </c>
       <c r="C233" t="inlineStr">
         <is>
@@ -5086,7 +5086,7 @@
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>https://terreno.mercadolibre.com.mx/MLM-4261807760-se-vende-terreno-carretera-mexico-toluca-lerma-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=40&amp;type=item&amp;tracking_id=ff6bedc1-9bb0-4a87-b0ff-198407b4640e&amp;price_drop=not_apply</t>
+          <t>https://terreno.mercadolibre.com.mx/MLM-4261794654-terreno-en-venta-en-industrial-en-toluca-estado-de-mexico-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=40&amp;type=item&amp;tracking_id=64db4c17-d904-410a-9333-7d5af75aa233&amp;price_drop=not_apply</t>
         </is>
       </c>
     </row>
@@ -5097,7 +5097,7 @@
         </is>
       </c>
       <c r="B234" t="n">
-        <v>222618909</v>
+        <v>14571000</v>
       </c>
       <c r="C234" t="inlineStr">
         <is>
@@ -5106,7 +5106,7 @@
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t>https://terreno.mercadolibre.com.mx/MLM-4261859654-terreno-en-venta-industrial-en-toluca-estado-de-mexico-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=41&amp;type=item&amp;tracking_id=ff6bedc1-9bb0-4a87-b0ff-198407b4640e&amp;price_drop=not_apply</t>
+          <t>https://terreno.mercadolibre.com.mx/MLM-4261807760-se-vende-terreno-carretera-mexico-toluca-lerma-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=41&amp;type=item&amp;tracking_id=64db4c17-d904-410a-9333-7d5af75aa233&amp;price_drop=not_apply</t>
         </is>
       </c>
     </row>
@@ -5117,7 +5117,7 @@
         </is>
       </c>
       <c r="B235" t="n">
-        <v>1870000</v>
+        <v>222618909</v>
       </c>
       <c r="C235" t="inlineStr">
         <is>
@@ -5126,7 +5126,7 @@
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t>https://terreno.mercadolibre.com.mx/MLM-2811993671-terreno-en-venta-en-residencial-hacienda-san-jose-en-toluca-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=42&amp;type=item&amp;float_highlight=recent_publication&amp;tracking_id=ff6bedc1-9bb0-4a87-b0ff-198407b4640e&amp;price_drop=not_apply</t>
+          <t>https://terreno.mercadolibre.com.mx/MLM-4261859654-terreno-en-venta-industrial-en-toluca-estado-de-mexico-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=42&amp;type=item&amp;tracking_id=64db4c17-d904-410a-9333-7d5af75aa233&amp;price_drop=not_apply</t>
         </is>
       </c>
     </row>
@@ -5137,7 +5137,7 @@
         </is>
       </c>
       <c r="B236" t="n">
-        <v>700000</v>
+        <v>1870000</v>
       </c>
       <c r="C236" t="inlineStr">
         <is>
@@ -5146,7 +5146,7 @@
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t>https://terreno.mercadolibre.com.mx/MLM-5058024988-terreno-en-venta-en-san-lorenzo-tepaltitlan-toluca-estado-de-mexico-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=43&amp;type=item&amp;float_highlight=recent_publication&amp;tracking_id=ff6bedc1-9bb0-4a87-b0ff-198407b4640e&amp;price_drop=not_apply</t>
+          <t>https://terreno.mercadolibre.com.mx/MLM-2811993671-terreno-en-venta-en-residencial-hacienda-san-jose-en-toluca-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=43&amp;type=item&amp;float_highlight=recent_publication&amp;tracking_id=64db4c17-d904-410a-9333-7d5af75aa233&amp;price_drop=not_apply</t>
         </is>
       </c>
     </row>
@@ -5157,7 +5157,7 @@
         </is>
       </c>
       <c r="B237" t="n">
-        <v>3240000</v>
+        <v>132000000</v>
       </c>
       <c r="C237" t="inlineStr">
         <is>
@@ -5166,7 +5166,7 @@
       </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t>https://terreno.mercadolibre.com.mx/MLM-5058177406-terreno-en-venta-en-san-francisco-totoltepec-toluca-estado-de-mexico-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=44&amp;type=item&amp;float_highlight=recent_publication&amp;tracking_id=ff6bedc1-9bb0-4a87-b0ff-198407b4640e&amp;price_drop=not_apply</t>
+          <t>https://terreno.mercadolibre.com.mx/MLM-5064030156-terreno-en-venta-en-parque-industrial-el-coecillo-toluca-estado-de-mexico-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=44&amp;type=item&amp;float_highlight=recent_publication&amp;tracking_id=64db4c17-d904-410a-9333-7d5af75aa233&amp;price_drop=not_apply</t>
         </is>
       </c>
     </row>
@@ -5177,7 +5177,7 @@
         </is>
       </c>
       <c r="B238" t="n">
-        <v>132000000</v>
+        <v>279450</v>
       </c>
       <c r="C238" t="inlineStr">
         <is>
@@ -5186,7 +5186,7 @@
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t>https://terreno.mercadolibre.com.mx/MLM-5064030156-terreno-en-venta-en-parque-industrial-el-coecillo-toluca-estado-de-mexico-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=45&amp;type=item&amp;float_highlight=recent_publication&amp;tracking_id=ff6bedc1-9bb0-4a87-b0ff-198407b4640e&amp;price_drop=not_apply</t>
+          <t>https://terreno.mercadolibre.com.mx/MLM-5060346586-ultimos-2-lotes-en-venta-en-san-cayetano-muy-cerca-de-la-unsa-en-toluca-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=45&amp;type=item&amp;float_highlight=recent_publication&amp;tracking_id=64db4c17-d904-410a-9333-7d5af75aa233&amp;price_drop=not_apply</t>
         </is>
       </c>
     </row>
@@ -5197,7 +5197,7 @@
         </is>
       </c>
       <c r="B239" t="n">
-        <v>279450</v>
+        <v>23500000</v>
       </c>
       <c r="C239" t="inlineStr">
         <is>
@@ -5206,7 +5206,7 @@
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>https://terreno.mercadolibre.com.mx/MLM-5060346586-ultimos-2-lotes-en-venta-en-san-cayetano-muy-cerca-de-la-unsa-en-toluca-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=46&amp;type=item&amp;float_highlight=recent_publication&amp;tracking_id=ff6bedc1-9bb0-4a87-b0ff-198407b4640e&amp;price_drop=not_apply</t>
+          <t>https://terreno.mercadolibre.com.mx/MLM-4950598656-terreno-comercial-en-venta-en-san-bernardino-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=46&amp;type=item&amp;tracking_id=64db4c17-d904-410a-9333-7d5af75aa233&amp;price_drop=not_apply</t>
         </is>
       </c>
     </row>
@@ -5217,7 +5217,7 @@
         </is>
       </c>
       <c r="B240" t="n">
-        <v>9215400</v>
+        <v>8760000</v>
       </c>
       <c r="C240" t="inlineStr">
         <is>
@@ -5226,7 +5226,7 @@
       </c>
       <c r="D240" t="inlineStr">
         <is>
-          <t>https://terreno.mercadolibre.com.mx/MLM-5047581202-terreno-comercial-en-venta-en-santa-cruz-otzacatipan-toluca-mexico-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=47&amp;type=item&amp;float_highlight=recent_publication&amp;tracking_id=ff6bedc1-9bb0-4a87-b0ff-198407b4640e&amp;price_drop=not_apply</t>
+          <t>https://terreno.mercadolibre.com.mx/MLM-4761562052-terreno-comercial-en-venta-en-santa-maria-totoltepec-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=47&amp;type=item&amp;tracking_id=64db4c17-d904-410a-9333-7d5af75aa233&amp;price_drop=not_apply</t>
         </is>
       </c>
     </row>
@@ -5237,7 +5237,7 @@
         </is>
       </c>
       <c r="B241" t="n">
-        <v>8502990</v>
+        <v>26320000</v>
       </c>
       <c r="C241" t="inlineStr">
         <is>
@@ -5246,7 +5246,7 @@
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t>https://terreno.mercadolibre.com.mx/MLM-5047581198-terreno-comercial-en-venta-en-santa-cruz-otzacatipan-toluca-mexico-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=48&amp;type=item&amp;float_highlight=recent_publication&amp;tracking_id=ff6bedc1-9bb0-4a87-b0ff-198407b4640e&amp;price_drop=not_apply</t>
+          <t>https://terreno.mercadolibre.com.mx/MLM-4790443980-terreno-residencial-en-venta-en-la-venta-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=48&amp;type=item&amp;tracking_id=64db4c17-d904-410a-9333-7d5af75aa233&amp;price_drop=not_apply</t>
         </is>
       </c>
     </row>
@@ -5266,7 +5266,7 @@
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t>https://terreno.mercadolibre.com.mx/MLM-3835159420-lotes-de-terreno-desde-104-m2-en-venta-cerca-del-aeropuerto-de-toluca-en-la-constitucion-toltepec-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=1&amp;type=item&amp;tracking_id=ff203ee2-37fa-4950-a44d-9937b0de4a54&amp;price_drop=not_apply</t>
+          <t>https://terreno.mercadolibre.com.mx/MLM-3835159420-lotes-de-terreno-desde-104-m2-en-venta-cerca-del-aeropuerto-de-toluca-en-la-constitucion-toltepec-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=1&amp;type=item&amp;tracking_id=f7bb9fa4-4cfc-4a58-add0-4b068a29e30a&amp;price_drop=not_apply</t>
         </is>
       </c>
     </row>
@@ -5286,7 +5286,7 @@
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>https://terreno.mercadolibre.com.mx/MLM-2810992285-construye-tu-residencia-en-la-zona-de-mayor-proyeccion-de-toluca-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=2&amp;type=item&amp;float_highlight=recent_publication&amp;tracking_id=ff203ee2-37fa-4950-a44d-9937b0de4a54&amp;price_drop=not_apply</t>
+          <t>https://terreno.mercadolibre.com.mx/MLM-2810992285-construye-tu-residencia-en-la-zona-de-mayor-proyeccion-de-toluca-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=2&amp;type=item&amp;float_highlight=recent_publication&amp;tracking_id=f7bb9fa4-4cfc-4a58-add0-4b068a29e30a&amp;price_drop=not_apply</t>
         </is>
       </c>
     </row>
@@ -5306,7 +5306,7 @@
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t>https://terreno.mercadolibre.com.mx/MLM-3847495816-el-mejor-terreno-del-condominio-puede-ser-tuyo-a-un-precio-de-oportunidad-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=3&amp;type=item&amp;tracking_id=ff203ee2-37fa-4950-a44d-9937b0de4a54&amp;price_drop=not_apply</t>
+          <t>https://terreno.mercadolibre.com.mx/MLM-3847495816-el-mejor-terreno-del-condominio-puede-ser-tuyo-a-un-precio-de-oportunidad-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=3&amp;type=item&amp;tracking_id=f7bb9fa4-4cfc-4a58-add0-4b068a29e30a&amp;price_drop=not_apply</t>
         </is>
       </c>
     </row>
@@ -5317,7 +5317,7 @@
         </is>
       </c>
       <c r="B245" t="n">
-        <v>7600000</v>
+        <v>649000</v>
       </c>
       <c r="C245" t="inlineStr">
         <is>
@@ -5326,7 +5326,7 @@
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t>https://terreno.mercadolibre.com.mx/MLM-2231593183-terreno-en-venta-en-san-mateo-oxtotitlan-toluca-mexico-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=4&amp;type=item&amp;tracking_id=ff203ee2-37fa-4950-a44d-9937b0de4a54&amp;price_drop=not_apply</t>
+          <t>https://terreno.mercadolibre.com.mx/MLM-2753915589-terreno-bardeado-en-cacalomacan-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=4&amp;type=item&amp;tracking_id=f7bb9fa4-4cfc-4a58-add0-4b068a29e30a&amp;price_drop=false</t>
         </is>
       </c>
     </row>
@@ -5337,7 +5337,7 @@
         </is>
       </c>
       <c r="B246" t="n">
-        <v>649000</v>
+        <v>7600000</v>
       </c>
       <c r="C246" t="inlineStr">
         <is>
@@ -5346,7 +5346,7 @@
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>https://terreno.mercadolibre.com.mx/MLM-2753915589-terreno-bardeado-en-cacalomacan-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=5&amp;type=item&amp;tracking_id=ff203ee2-37fa-4950-a44d-9937b0de4a54&amp;price_drop=false</t>
+          <t>https://terreno.mercadolibre.com.mx/MLM-2231593183-terreno-en-venta-en-san-mateo-oxtotitlan-toluca-mexico-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=5&amp;type=item&amp;tracking_id=f7bb9fa4-4cfc-4a58-add0-4b068a29e30a&amp;price_drop=not_apply</t>
         </is>
       </c>
     </row>
@@ -5366,7 +5366,7 @@
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t>https://terreno.mercadolibre.com.mx/MLM-2716356593-terreno-en-venta-en-colonia-nueva-santa-maria-de-las-rosas-toluca-estado-de-mexico-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=6&amp;type=item&amp;tracking_id=ff203ee2-37fa-4950-a44d-9937b0de4a54&amp;price_drop=not_apply</t>
+          <t>https://terreno.mercadolibre.com.mx/MLM-2716356593-terreno-en-venta-en-colonia-nueva-santa-maria-de-las-rosas-toluca-estado-de-mexico-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=6&amp;type=item&amp;tracking_id=f7bb9fa4-4cfc-4a58-add0-4b068a29e30a&amp;price_drop=not_apply</t>
         </is>
       </c>
     </row>
@@ -5386,7 +5386,7 @@
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t>https://terreno.mercadolibre.com.mx/MLM-4660497978-terreno-en-venta-en-toluca-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=7&amp;type=item&amp;tracking_id=ff203ee2-37fa-4950-a44d-9937b0de4a54&amp;price_drop=not_apply</t>
+          <t>https://terreno.mercadolibre.com.mx/MLM-4660497978-terreno-en-venta-en-toluca-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=7&amp;type=item&amp;tracking_id=f7bb9fa4-4cfc-4a58-add0-4b068a29e30a&amp;price_drop=not_apply</t>
         </is>
       </c>
     </row>
@@ -5406,7 +5406,7 @@
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t>https://terreno.mercadolibre.com.mx/MLM-4388186170-terreno-industrial-en-venta-en-toluca-san-cayetano-a-un-lado-de-la-caseta-el-dorado-cerca-puerta-mexico-recinto-aduanal-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=8&amp;type=item&amp;tracking_id=ff203ee2-37fa-4950-a44d-9937b0de4a54&amp;price_drop=not_apply</t>
+          <t>https://terreno.mercadolibre.com.mx/MLM-4388186170-terreno-industrial-en-venta-en-toluca-san-cayetano-a-un-lado-de-la-caseta-el-dorado-cerca-puerta-mexico-recinto-aduanal-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=8&amp;type=item&amp;tracking_id=f7bb9fa4-4cfc-4a58-add0-4b068a29e30a&amp;price_drop=not_apply</t>
         </is>
       </c>
     </row>
@@ -5426,7 +5426,7 @@
       </c>
       <c r="D250" t="inlineStr">
         <is>
-          <t>https://terreno.mercadolibre.com.mx/MLM-2716629645-terreno-industrial-en-venta-en-palmillas-son-13-hectareas-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=9&amp;type=item&amp;tracking_id=ff203ee2-37fa-4950-a44d-9937b0de4a54&amp;price_drop=not_apply</t>
+          <t>https://terreno.mercadolibre.com.mx/MLM-2716629645-terreno-industrial-en-venta-en-palmillas-son-13-hectareas-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=9&amp;type=item&amp;tracking_id=f7bb9fa4-4cfc-4a58-add0-4b068a29e30a&amp;price_drop=not_apply</t>
         </is>
       </c>
     </row>
@@ -5446,7 +5446,7 @@
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t>https://terreno.mercadolibre.com.mx/MLM-2748643873-terreno-en-venta-a-pie-de-carretera-toluca-atlacomulco-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=10&amp;type=item&amp;tracking_id=ff203ee2-37fa-4950-a44d-9937b0de4a54&amp;price_drop=not_apply</t>
+          <t>https://terreno.mercadolibre.com.mx/MLM-2748643873-terreno-en-venta-a-pie-de-carretera-toluca-atlacomulco-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=10&amp;type=item&amp;tracking_id=f7bb9fa4-4cfc-4a58-add0-4b068a29e30a&amp;price_drop=not_apply</t>
         </is>
       </c>
     </row>
@@ -5466,7 +5466,7 @@
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t>https://terreno.mercadolibre.com.mx/MLM-4790479866-terreno-regular-con-infraestructura-lista-base-solida-para-tu-proyecto-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=11&amp;type=item&amp;tracking_id=ff203ee2-37fa-4950-a44d-9937b0de4a54&amp;price_drop=not_apply</t>
+          <t>https://terreno.mercadolibre.com.mx/MLM-4790479866-terreno-regular-con-infraestructura-lista-base-solida-para-tu-proyecto-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=11&amp;type=item&amp;tracking_id=f7bb9fa4-4cfc-4a58-add0-4b068a29e30a&amp;price_drop=not_apply</t>
         </is>
       </c>
     </row>
@@ -5486,7 +5486,7 @@
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t>https://terreno.mercadolibre.com.mx/MLM-5015164202-venta-terreno-lotes-palmillas-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=12&amp;type=item&amp;tracking_id=ff203ee2-37fa-4950-a44d-9937b0de4a54&amp;price_drop=not_apply</t>
+          <t>https://terreno.mercadolibre.com.mx/MLM-5015164202-venta-terreno-lotes-palmillas-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=12&amp;type=item&amp;tracking_id=f7bb9fa4-4cfc-4a58-add0-4b068a29e30a&amp;price_drop=not_apply</t>
         </is>
       </c>
     </row>
@@ -5506,7 +5506,7 @@
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>https://terreno.mercadolibre.com.mx/MLM-4416680104-terreno-en-venta-sobre-calzada-del-pacifico-cacalomacan-por-ocho-cedros-toluca-cas-23000-m2-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=13&amp;type=item&amp;tracking_id=ff203ee2-37fa-4950-a44d-9937b0de4a54&amp;price_drop=not_apply</t>
+          <t>https://terreno.mercadolibre.com.mx/MLM-4416680104-terreno-en-venta-sobre-calzada-del-pacifico-cacalomacan-por-ocho-cedros-toluca-cas-23000-m2-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=13&amp;type=item&amp;tracking_id=f7bb9fa4-4cfc-4a58-add0-4b068a29e30a&amp;price_drop=not_apply</t>
         </is>
       </c>
     </row>
@@ -5526,7 +5526,7 @@
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>https://terreno.mercadolibre.com.mx/MLM-2736455271-terreno-de-2-hectareas-en-zona-urbana-santa-maria-totoltepec-estado-de-mexico-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=14&amp;type=item&amp;tracking_id=ff203ee2-37fa-4950-a44d-9937b0de4a54&amp;price_drop=not_apply</t>
+          <t>https://terreno.mercadolibre.com.mx/MLM-2736455271-terreno-de-2-hectareas-en-zona-urbana-santa-maria-totoltepec-estado-de-mexico-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=14&amp;type=item&amp;tracking_id=f7bb9fa4-4cfc-4a58-add0-4b068a29e30a&amp;price_drop=not_apply</t>
         </is>
       </c>
     </row>
@@ -5537,7 +5537,7 @@
         </is>
       </c>
       <c r="B256" t="n">
-        <v>1831680</v>
+        <v>299999</v>
       </c>
       <c r="C256" t="inlineStr">
         <is>
@@ -5546,7 +5546,7 @@
       </c>
       <c r="D256" t="inlineStr">
         <is>
-          <t>https://terreno.mercadolibre.com.mx/MLM-2804712255-venta-terreno-paraje-san-rafael-en-toluca-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=15&amp;type=item&amp;float_highlight=recent_publication&amp;tracking_id=ff203ee2-37fa-4950-a44d-9937b0de4a54&amp;price_drop=not_apply</t>
+          <t>https://terreno.mercadolibre.com.mx/MLM-5082958514-lotes-a-10-min-de-paideia-propiedad-desde-230-m-en-adelante-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=15&amp;type=item&amp;float_highlight=recent_publication&amp;tracking_id=f7bb9fa4-4cfc-4a58-add0-4b068a29e30a&amp;price_drop=not_apply</t>
         </is>
       </c>
     </row>
@@ -5557,7 +5557,7 @@
         </is>
       </c>
       <c r="B257" t="n">
-        <v>1485000</v>
+        <v>1831680</v>
       </c>
       <c r="C257" t="inlineStr">
         <is>
@@ -5566,7 +5566,7 @@
       </c>
       <c r="D257" t="inlineStr">
         <is>
-          <t>https://terreno.mercadolibre.com.mx/MLM-2187928841-venta-terreno-cerrillo-vista-hermosa-toluca-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=16&amp;type=item&amp;tracking_id=ff203ee2-37fa-4950-a44d-9937b0de4a54&amp;price_drop=not_apply</t>
+          <t>https://terreno.mercadolibre.com.mx/MLM-2804712255-venta-terreno-paraje-san-rafael-en-toluca-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=16&amp;type=item&amp;float_highlight=recent_publication&amp;tracking_id=f7bb9fa4-4cfc-4a58-add0-4b068a29e30a&amp;price_drop=not_apply</t>
         </is>
       </c>
     </row>
@@ -5577,7 +5577,7 @@
         </is>
       </c>
       <c r="B258" t="n">
-        <v>4805040</v>
+        <v>1485000</v>
       </c>
       <c r="C258" t="inlineStr">
         <is>
@@ -5586,7 +5586,7 @@
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t>https://terreno.mercadolibre.com.mx/MLM-3705026808-venta-de-terreno-en-cacalomacan-a-20-min-centro-toluca-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=17&amp;type=item&amp;tracking_id=ff203ee2-37fa-4950-a44d-9937b0de4a54&amp;price_drop=not_apply</t>
+          <t>https://terreno.mercadolibre.com.mx/MLM-2187928841-venta-terreno-cerrillo-vista-hermosa-toluca-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=17&amp;type=item&amp;tracking_id=f7bb9fa4-4cfc-4a58-add0-4b068a29e30a&amp;price_drop=not_apply</t>
         </is>
       </c>
     </row>
@@ -5597,7 +5597,7 @@
         </is>
       </c>
       <c r="B259" t="n">
-        <v>1920000</v>
+        <v>4805040</v>
       </c>
       <c r="C259" t="inlineStr">
         <is>
@@ -5606,7 +5606,7 @@
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t>https://terreno.mercadolibre.com.mx/MLM-4119789692-terreno-en-venta-residencial-ex-hacienda-san-jose-toluca-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=18&amp;type=item&amp;tracking_id=ff203ee2-37fa-4950-a44d-9937b0de4a54&amp;price_drop=not_apply</t>
+          <t>https://terreno.mercadolibre.com.mx/MLM-3705026808-venta-de-terreno-en-cacalomacan-a-20-min-centro-toluca-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=18&amp;type=item&amp;tracking_id=f7bb9fa4-4cfc-4a58-add0-4b068a29e30a&amp;price_drop=not_apply</t>
         </is>
       </c>
     </row>
@@ -5617,7 +5617,7 @@
         </is>
       </c>
       <c r="B260" t="n">
-        <v>1244380</v>
+        <v>1920000</v>
       </c>
       <c r="C260" t="inlineStr">
         <is>
@@ -5626,7 +5626,7 @@
       </c>
       <c r="D260" t="inlineStr">
         <is>
-          <t>https://terreno.mercadolibre.com.mx/MLM-4826508826-venta-de-lote-de-terreno-residencial-cerca-de-galerias-metepec-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=19&amp;type=item&amp;tracking_id=ff203ee2-37fa-4950-a44d-9937b0de4a54&amp;price_drop=not_apply</t>
+          <t>https://terreno.mercadolibre.com.mx/MLM-4119789692-terreno-en-venta-residencial-ex-hacienda-san-jose-toluca-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=19&amp;type=item&amp;tracking_id=f7bb9fa4-4cfc-4a58-add0-4b068a29e30a&amp;price_drop=not_apply</t>
         </is>
       </c>
     </row>
@@ -5637,7 +5637,7 @@
         </is>
       </c>
       <c r="B261" t="n">
-        <v>8565858</v>
+        <v>1244380</v>
       </c>
       <c r="C261" t="inlineStr">
         <is>
@@ -5646,7 +5646,7 @@
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t>https://terreno.mercadolibre.com.mx/MLM-4080298834-terreno-en-venta-en-san-miguel-zacango-toluca-mexico-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=20&amp;type=item&amp;tracking_id=ff203ee2-37fa-4950-a44d-9937b0de4a54&amp;price_drop=not_apply</t>
+          <t>https://terreno.mercadolibre.com.mx/MLM-4826508826-venta-de-lote-de-terreno-residencial-cerca-de-galerias-metepec-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=20&amp;type=item&amp;tracking_id=f7bb9fa4-4cfc-4a58-add0-4b068a29e30a&amp;price_drop=not_apply</t>
         </is>
       </c>
     </row>
@@ -5657,7 +5657,7 @@
         </is>
       </c>
       <c r="B262" t="n">
-        <v>8500000</v>
+        <v>8565858</v>
       </c>
       <c r="C262" t="inlineStr">
         <is>
@@ -5666,7 +5666,7 @@
       </c>
       <c r="D262" t="inlineStr">
         <is>
-          <t>https://terreno.mercadolibre.com.mx/MLM-2310439697-se-vende-terreno-en-toluca-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=21&amp;type=item&amp;tracking_id=ff203ee2-37fa-4950-a44d-9937b0de4a54&amp;price_drop=not_apply</t>
+          <t>https://terreno.mercadolibre.com.mx/MLM-4080298834-terreno-en-venta-en-san-miguel-zacango-toluca-mexico-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=21&amp;type=item&amp;tracking_id=f7bb9fa4-4cfc-4a58-add0-4b068a29e30a&amp;price_drop=not_apply</t>
         </is>
       </c>
     </row>
@@ -5677,7 +5677,7 @@
         </is>
       </c>
       <c r="B263" t="n">
-        <v>1300000</v>
+        <v>8500000</v>
       </c>
       <c r="C263" t="inlineStr">
         <is>
@@ -5686,7 +5686,7 @@
       </c>
       <c r="D263" t="inlineStr">
         <is>
-          <t>https://terreno.mercadolibre.com.mx/MLM-4495237624-lote-disponible-en-conjunto-ambar-toluca-edo-mex-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=22&amp;type=item&amp;tracking_id=ff203ee2-37fa-4950-a44d-9937b0de4a54&amp;price_drop=not_apply</t>
+          <t>https://terreno.mercadolibre.com.mx/MLM-2310439697-se-vende-terreno-en-toluca-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=22&amp;type=item&amp;tracking_id=f7bb9fa4-4cfc-4a58-add0-4b068a29e30a&amp;price_drop=not_apply</t>
         </is>
       </c>
     </row>
@@ -5697,7 +5697,7 @@
         </is>
       </c>
       <c r="B264" t="n">
-        <v>1200000</v>
+        <v>1300000</v>
       </c>
       <c r="C264" t="inlineStr">
         <is>
@@ -5706,7 +5706,7 @@
       </c>
       <c r="D264" t="inlineStr">
         <is>
-          <t>https://terreno.mercadolibre.com.mx/MLM-2485559517-terreno-en-venta-en-toluca-san-andres-cuexcontitlan-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=23&amp;type=item&amp;tracking_id=ff203ee2-37fa-4950-a44d-9937b0de4a54&amp;price_drop=not_apply</t>
+          <t>https://terreno.mercadolibre.com.mx/MLM-4495237624-lote-disponible-en-conjunto-ambar-toluca-edo-mex-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=23&amp;type=item&amp;tracking_id=f7bb9fa4-4cfc-4a58-add0-4b068a29e30a&amp;price_drop=not_apply</t>
         </is>
       </c>
     </row>
@@ -5717,7 +5717,7 @@
         </is>
       </c>
       <c r="B265" t="n">
-        <v>38634000</v>
+        <v>1200000</v>
       </c>
       <c r="C265" t="inlineStr">
         <is>
@@ -5726,7 +5726,7 @@
       </c>
       <c r="D265" t="inlineStr">
         <is>
-          <t>https://terreno.mercadolibre.com.mx/MLM-2431684449-terreno-en-toluca-25756-m2-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=24&amp;type=item&amp;tracking_id=ff203ee2-37fa-4950-a44d-9937b0de4a54&amp;price_drop=not_apply</t>
+          <t>https://terreno.mercadolibre.com.mx/MLM-2485559517-terreno-en-venta-en-toluca-san-andres-cuexcontitlan-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=24&amp;type=item&amp;tracking_id=f7bb9fa4-4cfc-4a58-add0-4b068a29e30a&amp;price_drop=not_apply</t>
         </is>
       </c>
     </row>
@@ -5737,7 +5737,7 @@
         </is>
       </c>
       <c r="B266" t="n">
-        <v>5625000</v>
+        <v>38634000</v>
       </c>
       <c r="C266" t="inlineStr">
         <is>
@@ -5746,7 +5746,7 @@
       </c>
       <c r="D266" t="inlineStr">
         <is>
-          <t>https://terreno.mercadolibre.com.mx/MLM-2323267483-terreno-en-venta-2250m2-en-san-felipe-tlalmimilolpan-toluca-mexico-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=25&amp;type=item&amp;tracking_id=ff203ee2-37fa-4950-a44d-9937b0de4a54&amp;price_drop=not_apply</t>
+          <t>https://terreno.mercadolibre.com.mx/MLM-2431684449-terreno-en-toluca-25756-m2-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=25&amp;type=item&amp;tracking_id=f7bb9fa4-4cfc-4a58-add0-4b068a29e30a&amp;price_drop=not_apply</t>
         </is>
       </c>
     </row>
@@ -5757,7 +5757,7 @@
         </is>
       </c>
       <c r="B267" t="n">
-        <v>25650000</v>
+        <v>5625000</v>
       </c>
       <c r="C267" t="inlineStr">
         <is>
@@ -5766,7 +5766,7 @@
       </c>
       <c r="D267" t="inlineStr">
         <is>
-          <t>https://terreno.mercadolibre.com.mx/MLM-4169951646-terreno-en-venta-por-las-torres-toluca-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=26&amp;type=item&amp;tracking_id=ff203ee2-37fa-4950-a44d-9937b0de4a54&amp;price_drop=not_apply</t>
+          <t>https://terreno.mercadolibre.com.mx/MLM-2323267483-terreno-en-venta-2250m2-en-san-felipe-tlalmimilolpan-toluca-mexico-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=26&amp;type=item&amp;tracking_id=f7bb9fa4-4cfc-4a58-add0-4b068a29e30a&amp;price_drop=not_apply</t>
         </is>
       </c>
     </row>
@@ -5777,7 +5777,7 @@
         </is>
       </c>
       <c r="B268" t="n">
-        <v>4800000</v>
+        <v>25650000</v>
       </c>
       <c r="C268" t="inlineStr">
         <is>
@@ -5786,7 +5786,7 @@
       </c>
       <c r="D268" t="inlineStr">
         <is>
-          <t>https://terreno.mercadolibre.com.mx/MLM-4416373342-terreno-en-venta-en-san-lorenzo-tepaltitlan-centro-toluca-mexico-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=27&amp;type=item&amp;tracking_id=ff203ee2-37fa-4950-a44d-9937b0de4a54&amp;price_drop=not_apply</t>
+          <t>https://terreno.mercadolibre.com.mx/MLM-4169951646-terreno-en-venta-por-las-torres-toluca-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=27&amp;type=item&amp;tracking_id=f7bb9fa4-4cfc-4a58-add0-4b068a29e30a&amp;price_drop=not_apply</t>
         </is>
       </c>
     </row>
@@ -5797,7 +5797,7 @@
         </is>
       </c>
       <c r="B269" t="n">
-        <v>14490000</v>
+        <v>4800000</v>
       </c>
       <c r="C269" t="inlineStr">
         <is>
@@ -5806,7 +5806,7 @@
       </c>
       <c r="D269" t="inlineStr">
         <is>
-          <t>https://terreno.mercadolibre.com.mx/MLM-2584697469-oportunidad-de-inversion-terreno-de-9993-m-cerca-de-parque-toluca-2000-ideal-para-naves-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=28&amp;type=item&amp;tracking_id=ff203ee2-37fa-4950-a44d-9937b0de4a54&amp;price_drop=not_apply</t>
+          <t>https://terreno.mercadolibre.com.mx/MLM-4416373342-terreno-en-venta-en-san-lorenzo-tepaltitlan-centro-toluca-mexico-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=28&amp;type=item&amp;tracking_id=f7bb9fa4-4cfc-4a58-add0-4b068a29e30a&amp;price_drop=not_apply</t>
         </is>
       </c>
     </row>
@@ -5817,7 +5817,7 @@
         </is>
       </c>
       <c r="B270" t="n">
-        <v>24520000</v>
+        <v>14490000</v>
       </c>
       <c r="C270" t="inlineStr">
         <is>
@@ -5826,7 +5826,7 @@
       </c>
       <c r="D270" t="inlineStr">
         <is>
-          <t>https://terreno.mercadolibre.com.mx/MLM-4169951774-terreno-en-venta-por-las-torres-toluca-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=29&amp;type=item&amp;tracking_id=ff203ee2-37fa-4950-a44d-9937b0de4a54&amp;price_drop=not_apply</t>
+          <t>https://terreno.mercadolibre.com.mx/MLM-2584697469-oportunidad-de-inversion-terreno-de-9993-m-cerca-de-parque-toluca-2000-ideal-para-naves-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=29&amp;type=item&amp;tracking_id=f7bb9fa4-4cfc-4a58-add0-4b068a29e30a&amp;price_drop=not_apply</t>
         </is>
       </c>
     </row>
@@ -5837,7 +5837,7 @@
         </is>
       </c>
       <c r="B271" t="n">
-        <v>12024000</v>
+        <v>24520000</v>
       </c>
       <c r="C271" t="inlineStr">
         <is>
@@ -5846,7 +5846,7 @@
       </c>
       <c r="D271" t="inlineStr">
         <is>
-          <t>https://terreno.mercadolibre.com.mx/MLM-2323192153-terreno-en-venta-8016-m2-en-san-felipe-tlalmimilolpan-toluca-mexico-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=30&amp;type=item&amp;tracking_id=ff203ee2-37fa-4950-a44d-9937b0de4a54&amp;price_drop=not_apply</t>
+          <t>https://terreno.mercadolibre.com.mx/MLM-4169951774-terreno-en-venta-por-las-torres-toluca-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=30&amp;type=item&amp;tracking_id=f7bb9fa4-4cfc-4a58-add0-4b068a29e30a&amp;price_drop=not_apply</t>
         </is>
       </c>
     </row>
@@ -5857,7 +5857,7 @@
         </is>
       </c>
       <c r="B272" t="n">
-        <v>13650000</v>
+        <v>12024000</v>
       </c>
       <c r="C272" t="inlineStr">
         <is>
@@ -5866,7 +5866,7 @@
       </c>
       <c r="D272" t="inlineStr">
         <is>
-          <t>https://terreno.mercadolibre.com.mx/MLM-2487732477-terreno-en-venta-por-las-torres-toluca-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=31&amp;type=item&amp;tracking_id=ff203ee2-37fa-4950-a44d-9937b0de4a54&amp;price_drop=not_apply</t>
+          <t>https://terreno.mercadolibre.com.mx/MLM-2323192153-terreno-en-venta-8016-m2-en-san-felipe-tlalmimilolpan-toluca-mexico-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=31&amp;type=item&amp;tracking_id=f7bb9fa4-4cfc-4a58-add0-4b068a29e30a&amp;price_drop=not_apply</t>
         </is>
       </c>
     </row>
@@ -5877,7 +5877,7 @@
         </is>
       </c>
       <c r="B273" t="n">
-        <v>4725000</v>
+        <v>13650000</v>
       </c>
       <c r="C273" t="inlineStr">
         <is>
@@ -5886,7 +5886,7 @@
       </c>
       <c r="D273" t="inlineStr">
         <is>
-          <t>https://terreno.mercadolibre.com.mx/MLM-2318168399-terreno-en-venta-en-cacalomacan-a-2-cuadras-de-jinetes-cerca-de-calz-pacifico-y-colegio-paideia-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=32&amp;type=item&amp;tracking_id=ff203ee2-37fa-4950-a44d-9937b0de4a54&amp;price_drop=not_apply</t>
+          <t>https://terreno.mercadolibre.com.mx/MLM-2487732477-terreno-en-venta-por-las-torres-toluca-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=32&amp;type=item&amp;tracking_id=f7bb9fa4-4cfc-4a58-add0-4b068a29e30a&amp;price_drop=not_apply</t>
         </is>
       </c>
     </row>
@@ -5897,7 +5897,7 @@
         </is>
       </c>
       <c r="B274" t="n">
-        <v>11500000</v>
+        <v>4725000</v>
       </c>
       <c r="C274" t="inlineStr">
         <is>
@@ -5906,7 +5906,7 @@
       </c>
       <c r="D274" t="inlineStr">
         <is>
-          <t>https://terreno.mercadolibre.com.mx/MLM-4080259510-terreno-en-venta-en-san-martin-toltepec-toluca-mexico-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=33&amp;type=item&amp;tracking_id=ff203ee2-37fa-4950-a44d-9937b0de4a54&amp;price_drop=not_apply</t>
+          <t>https://terreno.mercadolibre.com.mx/MLM-2318168399-terreno-en-venta-en-cacalomacan-a-2-cuadras-de-jinetes-cerca-de-calz-pacifico-y-colegio-paideia-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=33&amp;type=item&amp;tracking_id=f7bb9fa4-4cfc-4a58-add0-4b068a29e30a&amp;price_drop=not_apply</t>
         </is>
       </c>
     </row>
@@ -5917,7 +5917,7 @@
         </is>
       </c>
       <c r="B275" t="n">
-        <v>1840590</v>
+        <v>11500000</v>
       </c>
       <c r="C275" t="inlineStr">
         <is>
@@ -5926,7 +5926,7 @@
       </c>
       <c r="D275" t="inlineStr">
         <is>
-          <t>https://terreno.mercadolibre.com.mx/MLM-4080239968-terreno-en-venta-toluca-cerca-del-aeropuerto-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=34&amp;type=item&amp;tracking_id=ff203ee2-37fa-4950-a44d-9937b0de4a54&amp;price_drop=not_apply</t>
+          <t>https://terreno.mercadolibre.com.mx/MLM-4080259510-terreno-en-venta-en-san-martin-toltepec-toluca-mexico-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=34&amp;type=item&amp;tracking_id=f7bb9fa4-4cfc-4a58-add0-4b068a29e30a&amp;price_drop=not_apply</t>
         </is>
       </c>
     </row>
@@ -5937,7 +5937,7 @@
         </is>
       </c>
       <c r="B276" t="n">
-        <v>8500000</v>
+        <v>1840590</v>
       </c>
       <c r="C276" t="inlineStr">
         <is>
@@ -5946,7 +5946,7 @@
       </c>
       <c r="D276" t="inlineStr">
         <is>
-          <t>https://terreno.mercadolibre.com.mx/MLM-2343423083-terreno-en-san-pedro-totoltepec-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=35&amp;type=item&amp;tracking_id=ff203ee2-37fa-4950-a44d-9937b0de4a54&amp;price_drop=not_apply</t>
+          <t>https://terreno.mercadolibre.com.mx/MLM-4080239968-terreno-en-venta-toluca-cerca-del-aeropuerto-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=35&amp;type=item&amp;tracking_id=f7bb9fa4-4cfc-4a58-add0-4b068a29e30a&amp;price_drop=not_apply</t>
         </is>
       </c>
     </row>
@@ -5957,7 +5957,7 @@
         </is>
       </c>
       <c r="B277" t="n">
-        <v>35000000</v>
+        <v>8500000</v>
       </c>
       <c r="C277" t="inlineStr">
         <is>
@@ -5966,7 +5966,7 @@
       </c>
       <c r="D277" t="inlineStr">
         <is>
-          <t>https://terreno.mercadolibre.com.mx/MLM-2370231281-terreno-en-venta-en-toluca-reforma-y-ferr-nac-independencia-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=36&amp;type=item&amp;tracking_id=ff203ee2-37fa-4950-a44d-9937b0de4a54&amp;price_drop=not_apply</t>
+          <t>https://terreno.mercadolibre.com.mx/MLM-2343423083-terreno-en-san-pedro-totoltepec-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=36&amp;type=item&amp;tracking_id=f7bb9fa4-4cfc-4a58-add0-4b068a29e30a&amp;price_drop=not_apply</t>
         </is>
       </c>
     </row>
@@ -5977,7 +5977,7 @@
         </is>
       </c>
       <c r="B278" t="n">
-        <v>2450000</v>
+        <v>35000000</v>
       </c>
       <c r="C278" t="inlineStr">
         <is>
@@ -5986,7 +5986,7 @@
       </c>
       <c r="D278" t="inlineStr">
         <is>
-          <t>https://terreno.mercadolibre.com.mx/MLM-2343569515-terreno-en-santa-maria-totoltepec-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=37&amp;type=item&amp;tracking_id=ff203ee2-37fa-4950-a44d-9937b0de4a54&amp;price_drop=not_apply</t>
+          <t>https://terreno.mercadolibre.com.mx/MLM-2370231281-terreno-en-venta-en-toluca-reforma-y-ferr-nac-independencia-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=37&amp;type=item&amp;tracking_id=f7bb9fa4-4cfc-4a58-add0-4b068a29e30a&amp;price_drop=not_apply</t>
         </is>
       </c>
     </row>
@@ -5997,7 +5997,7 @@
         </is>
       </c>
       <c r="B279" t="n">
-        <v>50000000</v>
+        <v>2450000</v>
       </c>
       <c r="C279" t="inlineStr">
         <is>
@@ -6006,7 +6006,7 @@
       </c>
       <c r="D279" t="inlineStr">
         <is>
-          <t>https://terreno.mercadolibre.com.mx/MLM-4558160588-terreno-en-venta-en-cipres-toluca-estado-de-mexico-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=38&amp;type=item&amp;tracking_id=ff203ee2-37fa-4950-a44d-9937b0de4a54&amp;price_drop=not_apply</t>
+          <t>https://terreno.mercadolibre.com.mx/MLM-2343569515-terreno-en-santa-maria-totoltepec-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=38&amp;type=item&amp;tracking_id=f7bb9fa4-4cfc-4a58-add0-4b068a29e30a&amp;price_drop=not_apply</t>
         </is>
       </c>
     </row>
@@ -6017,7 +6017,7 @@
         </is>
       </c>
       <c r="B280" t="n">
-        <v>203547204</v>
+        <v>50000000</v>
       </c>
       <c r="C280" t="inlineStr">
         <is>
@@ -6026,7 +6026,7 @@
       </c>
       <c r="D280" t="inlineStr">
         <is>
-          <t>https://terreno.mercadolibre.com.mx/MLM-4261794654-terreno-en-venta-en-industrial-en-toluca-estado-de-mexico-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=39&amp;type=item&amp;tracking_id=ff203ee2-37fa-4950-a44d-9937b0de4a54&amp;price_drop=not_apply</t>
+          <t>https://terreno.mercadolibre.com.mx/MLM-4558160588-terreno-en-venta-en-cipres-toluca-estado-de-mexico-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=39&amp;type=item&amp;tracking_id=f7bb9fa4-4cfc-4a58-add0-4b068a29e30a&amp;price_drop=not_apply</t>
         </is>
       </c>
     </row>
@@ -6037,7 +6037,7 @@
         </is>
       </c>
       <c r="B281" t="n">
-        <v>14571000</v>
+        <v>203547204</v>
       </c>
       <c r="C281" t="inlineStr">
         <is>
@@ -6046,7 +6046,7 @@
       </c>
       <c r="D281" t="inlineStr">
         <is>
-          <t>https://terreno.mercadolibre.com.mx/MLM-4261807760-se-vende-terreno-carretera-mexico-toluca-lerma-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=40&amp;type=item&amp;tracking_id=ff203ee2-37fa-4950-a44d-9937b0de4a54&amp;price_drop=not_apply</t>
+          <t>https://terreno.mercadolibre.com.mx/MLM-4261794654-terreno-en-venta-en-industrial-en-toluca-estado-de-mexico-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=40&amp;type=item&amp;tracking_id=f7bb9fa4-4cfc-4a58-add0-4b068a29e30a&amp;price_drop=not_apply</t>
         </is>
       </c>
     </row>
@@ -6057,7 +6057,7 @@
         </is>
       </c>
       <c r="B282" t="n">
-        <v>222618909</v>
+        <v>14571000</v>
       </c>
       <c r="C282" t="inlineStr">
         <is>
@@ -6066,7 +6066,7 @@
       </c>
       <c r="D282" t="inlineStr">
         <is>
-          <t>https://terreno.mercadolibre.com.mx/MLM-4261859654-terreno-en-venta-industrial-en-toluca-estado-de-mexico-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=41&amp;type=item&amp;tracking_id=ff203ee2-37fa-4950-a44d-9937b0de4a54&amp;price_drop=not_apply</t>
+          <t>https://terreno.mercadolibre.com.mx/MLM-4261807760-se-vende-terreno-carretera-mexico-toluca-lerma-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=41&amp;type=item&amp;tracking_id=f7bb9fa4-4cfc-4a58-add0-4b068a29e30a&amp;price_drop=not_apply</t>
         </is>
       </c>
     </row>
@@ -6077,7 +6077,7 @@
         </is>
       </c>
       <c r="B283" t="n">
-        <v>1870000</v>
+        <v>222618909</v>
       </c>
       <c r="C283" t="inlineStr">
         <is>
@@ -6086,7 +6086,7 @@
       </c>
       <c r="D283" t="inlineStr">
         <is>
-          <t>https://terreno.mercadolibre.com.mx/MLM-2811993671-terreno-en-venta-en-residencial-hacienda-san-jose-en-toluca-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=42&amp;type=item&amp;float_highlight=recent_publication&amp;tracking_id=ff203ee2-37fa-4950-a44d-9937b0de4a54&amp;price_drop=not_apply</t>
+          <t>https://terreno.mercadolibre.com.mx/MLM-4261859654-terreno-en-venta-industrial-en-toluca-estado-de-mexico-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=42&amp;type=item&amp;tracking_id=f7bb9fa4-4cfc-4a58-add0-4b068a29e30a&amp;price_drop=not_apply</t>
         </is>
       </c>
     </row>
@@ -6097,7 +6097,7 @@
         </is>
       </c>
       <c r="B284" t="n">
-        <v>700000</v>
+        <v>1870000</v>
       </c>
       <c r="C284" t="inlineStr">
         <is>
@@ -6106,7 +6106,7 @@
       </c>
       <c r="D284" t="inlineStr">
         <is>
-          <t>https://terreno.mercadolibre.com.mx/MLM-5058024988-terreno-en-venta-en-san-lorenzo-tepaltitlan-toluca-estado-de-mexico-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=43&amp;type=item&amp;float_highlight=recent_publication&amp;tracking_id=ff203ee2-37fa-4950-a44d-9937b0de4a54&amp;price_drop=not_apply</t>
+          <t>https://terreno.mercadolibre.com.mx/MLM-2811993671-terreno-en-venta-en-residencial-hacienda-san-jose-en-toluca-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=43&amp;type=item&amp;float_highlight=recent_publication&amp;tracking_id=f7bb9fa4-4cfc-4a58-add0-4b068a29e30a&amp;price_drop=not_apply</t>
         </is>
       </c>
     </row>
@@ -6117,7 +6117,7 @@
         </is>
       </c>
       <c r="B285" t="n">
-        <v>3240000</v>
+        <v>132000000</v>
       </c>
       <c r="C285" t="inlineStr">
         <is>
@@ -6126,7 +6126,7 @@
       </c>
       <c r="D285" t="inlineStr">
         <is>
-          <t>https://terreno.mercadolibre.com.mx/MLM-5058177406-terreno-en-venta-en-san-francisco-totoltepec-toluca-estado-de-mexico-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=44&amp;type=item&amp;float_highlight=recent_publication&amp;tracking_id=ff203ee2-37fa-4950-a44d-9937b0de4a54&amp;price_drop=not_apply</t>
+          <t>https://terreno.mercadolibre.com.mx/MLM-5064030156-terreno-en-venta-en-parque-industrial-el-coecillo-toluca-estado-de-mexico-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=44&amp;type=item&amp;float_highlight=recent_publication&amp;tracking_id=f7bb9fa4-4cfc-4a58-add0-4b068a29e30a&amp;price_drop=not_apply</t>
         </is>
       </c>
     </row>
@@ -6137,7 +6137,7 @@
         </is>
       </c>
       <c r="B286" t="n">
-        <v>132000000</v>
+        <v>279450</v>
       </c>
       <c r="C286" t="inlineStr">
         <is>
@@ -6146,7 +6146,7 @@
       </c>
       <c r="D286" t="inlineStr">
         <is>
-          <t>https://terreno.mercadolibre.com.mx/MLM-5064030156-terreno-en-venta-en-parque-industrial-el-coecillo-toluca-estado-de-mexico-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=45&amp;type=item&amp;float_highlight=recent_publication&amp;tracking_id=ff203ee2-37fa-4950-a44d-9937b0de4a54&amp;price_drop=not_apply</t>
+          <t>https://terreno.mercadolibre.com.mx/MLM-5060346586-ultimos-2-lotes-en-venta-en-san-cayetano-muy-cerca-de-la-unsa-en-toluca-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=45&amp;type=item&amp;float_highlight=recent_publication&amp;tracking_id=f7bb9fa4-4cfc-4a58-add0-4b068a29e30a&amp;price_drop=not_apply</t>
         </is>
       </c>
     </row>
@@ -6157,7 +6157,7 @@
         </is>
       </c>
       <c r="B287" t="n">
-        <v>279450</v>
+        <v>23500000</v>
       </c>
       <c r="C287" t="inlineStr">
         <is>
@@ -6166,7 +6166,7 @@
       </c>
       <c r="D287" t="inlineStr">
         <is>
-          <t>https://terreno.mercadolibre.com.mx/MLM-5060346586-ultimos-2-lotes-en-venta-en-san-cayetano-muy-cerca-de-la-unsa-en-toluca-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=46&amp;type=item&amp;float_highlight=recent_publication&amp;tracking_id=ff203ee2-37fa-4950-a44d-9937b0de4a54&amp;price_drop=not_apply</t>
+          <t>https://terreno.mercadolibre.com.mx/MLM-4950598656-terreno-comercial-en-venta-en-san-bernardino-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=46&amp;type=item&amp;tracking_id=f7bb9fa4-4cfc-4a58-add0-4b068a29e30a&amp;price_drop=not_apply</t>
         </is>
       </c>
     </row>
@@ -6177,7 +6177,7 @@
         </is>
       </c>
       <c r="B288" t="n">
-        <v>9215400</v>
+        <v>8760000</v>
       </c>
       <c r="C288" t="inlineStr">
         <is>
@@ -6186,7 +6186,7 @@
       </c>
       <c r="D288" t="inlineStr">
         <is>
-          <t>https://terreno.mercadolibre.com.mx/MLM-5047581202-terreno-comercial-en-venta-en-santa-cruz-otzacatipan-toluca-mexico-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=47&amp;type=item&amp;float_highlight=recent_publication&amp;tracking_id=ff203ee2-37fa-4950-a44d-9937b0de4a54&amp;price_drop=not_apply</t>
+          <t>https://terreno.mercadolibre.com.mx/MLM-4761562052-terreno-comercial-en-venta-en-santa-maria-totoltepec-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=47&amp;type=item&amp;tracking_id=f7bb9fa4-4cfc-4a58-add0-4b068a29e30a&amp;price_drop=not_apply</t>
         </is>
       </c>
     </row>
@@ -6197,7 +6197,7 @@
         </is>
       </c>
       <c r="B289" t="n">
-        <v>8502990</v>
+        <v>26320000</v>
       </c>
       <c r="C289" t="inlineStr">
         <is>
@@ -6206,7 +6206,7 @@
       </c>
       <c r="D289" t="inlineStr">
         <is>
-          <t>https://terreno.mercadolibre.com.mx/MLM-5047581198-terreno-comercial-en-venta-en-santa-cruz-otzacatipan-toluca-mexico-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=48&amp;type=item&amp;float_highlight=recent_publication&amp;tracking_id=ff203ee2-37fa-4950-a44d-9937b0de4a54&amp;price_drop=not_apply</t>
+          <t>https://terreno.mercadolibre.com.mx/MLM-4790443980-terreno-residencial-en-venta-en-la-venta-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=48&amp;type=item&amp;tracking_id=f7bb9fa4-4cfc-4a58-add0-4b068a29e30a&amp;price_drop=not_apply</t>
         </is>
       </c>
     </row>
@@ -6226,7 +6226,7 @@
       </c>
       <c r="D290" t="inlineStr">
         <is>
-          <t>https://terreno.mercadolibre.com.mx/MLM-3835159420-lotes-de-terreno-desde-104-m2-en-venta-cerca-del-aeropuerto-de-toluca-en-la-constitucion-toltepec-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=1&amp;type=item&amp;tracking_id=e9f4bfe8-53e2-4bf3-90ec-22a1ec510b87&amp;price_drop=not_apply</t>
+          <t>https://terreno.mercadolibre.com.mx/MLM-3835159420-lotes-de-terreno-desde-104-m2-en-venta-cerca-del-aeropuerto-de-toluca-en-la-constitucion-toltepec-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=1&amp;type=item&amp;tracking_id=e2a21522-489e-4892-844a-18ff9381f16b&amp;price_drop=not_apply</t>
         </is>
       </c>
     </row>
@@ -6246,7 +6246,7 @@
       </c>
       <c r="D291" t="inlineStr">
         <is>
-          <t>https://terreno.mercadolibre.com.mx/MLM-2810992285-construye-tu-residencia-en-la-zona-de-mayor-proyeccion-de-toluca-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=2&amp;type=item&amp;float_highlight=recent_publication&amp;tracking_id=e9f4bfe8-53e2-4bf3-90ec-22a1ec510b87&amp;price_drop=not_apply</t>
+          <t>https://terreno.mercadolibre.com.mx/MLM-2810992285-construye-tu-residencia-en-la-zona-de-mayor-proyeccion-de-toluca-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=2&amp;type=item&amp;float_highlight=recent_publication&amp;tracking_id=e2a21522-489e-4892-844a-18ff9381f16b&amp;price_drop=not_apply</t>
         </is>
       </c>
     </row>
@@ -6266,7 +6266,7 @@
       </c>
       <c r="D292" t="inlineStr">
         <is>
-          <t>https://terreno.mercadolibre.com.mx/MLM-3847495816-el-mejor-terreno-del-condominio-puede-ser-tuyo-a-un-precio-de-oportunidad-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=3&amp;type=item&amp;tracking_id=e9f4bfe8-53e2-4bf3-90ec-22a1ec510b87&amp;price_drop=not_apply</t>
+          <t>https://terreno.mercadolibre.com.mx/MLM-3847495816-el-mejor-terreno-del-condominio-puede-ser-tuyo-a-un-precio-de-oportunidad-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=3&amp;type=item&amp;tracking_id=e2a21522-489e-4892-844a-18ff9381f16b&amp;price_drop=not_apply</t>
         </is>
       </c>
     </row>
@@ -6277,7 +6277,7 @@
         </is>
       </c>
       <c r="B293" t="n">
-        <v>7600000</v>
+        <v>649000</v>
       </c>
       <c r="C293" t="inlineStr">
         <is>
@@ -6286,7 +6286,7 @@
       </c>
       <c r="D293" t="inlineStr">
         <is>
-          <t>https://terreno.mercadolibre.com.mx/MLM-2231593183-terreno-en-venta-en-san-mateo-oxtotitlan-toluca-mexico-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=4&amp;type=item&amp;tracking_id=e9f4bfe8-53e2-4bf3-90ec-22a1ec510b87&amp;price_drop=not_apply</t>
+          <t>https://terreno.mercadolibre.com.mx/MLM-2753915589-terreno-bardeado-en-cacalomacan-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=4&amp;type=item&amp;tracking_id=e2a21522-489e-4892-844a-18ff9381f16b&amp;price_drop=false</t>
         </is>
       </c>
     </row>
@@ -6297,7 +6297,7 @@
         </is>
       </c>
       <c r="B294" t="n">
-        <v>649000</v>
+        <v>7600000</v>
       </c>
       <c r="C294" t="inlineStr">
         <is>
@@ -6306,7 +6306,7 @@
       </c>
       <c r="D294" t="inlineStr">
         <is>
-          <t>https://terreno.mercadolibre.com.mx/MLM-2753915589-terreno-bardeado-en-cacalomacan-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=5&amp;type=item&amp;tracking_id=e9f4bfe8-53e2-4bf3-90ec-22a1ec510b87&amp;price_drop=false</t>
+          <t>https://terreno.mercadolibre.com.mx/MLM-2231593183-terreno-en-venta-en-san-mateo-oxtotitlan-toluca-mexico-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=5&amp;type=item&amp;tracking_id=e2a21522-489e-4892-844a-18ff9381f16b&amp;price_drop=not_apply</t>
         </is>
       </c>
     </row>
@@ -6326,7 +6326,7 @@
       </c>
       <c r="D295" t="inlineStr">
         <is>
-          <t>https://terreno.mercadolibre.com.mx/MLM-2716356593-terreno-en-venta-en-colonia-nueva-santa-maria-de-las-rosas-toluca-estado-de-mexico-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=6&amp;type=item&amp;tracking_id=e9f4bfe8-53e2-4bf3-90ec-22a1ec510b87&amp;price_drop=not_apply</t>
+          <t>https://terreno.mercadolibre.com.mx/MLM-2716356593-terreno-en-venta-en-colonia-nueva-santa-maria-de-las-rosas-toluca-estado-de-mexico-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=6&amp;type=item&amp;tracking_id=e2a21522-489e-4892-844a-18ff9381f16b&amp;price_drop=not_apply</t>
         </is>
       </c>
     </row>
@@ -6346,7 +6346,7 @@
       </c>
       <c r="D296" t="inlineStr">
         <is>
-          <t>https://terreno.mercadolibre.com.mx/MLM-4660497978-terreno-en-venta-en-toluca-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=7&amp;type=item&amp;tracking_id=e9f4bfe8-53e2-4bf3-90ec-22a1ec510b87&amp;price_drop=not_apply</t>
+          <t>https://terreno.mercadolibre.com.mx/MLM-4660497978-terreno-en-venta-en-toluca-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=7&amp;type=item&amp;tracking_id=e2a21522-489e-4892-844a-18ff9381f16b&amp;price_drop=not_apply</t>
         </is>
       </c>
     </row>
@@ -6366,7 +6366,7 @@
       </c>
       <c r="D297" t="inlineStr">
         <is>
-          <t>https://terreno.mercadolibre.com.mx/MLM-4388186170-terreno-industrial-en-venta-en-toluca-san-cayetano-a-un-lado-de-la-caseta-el-dorado-cerca-puerta-mexico-recinto-aduanal-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=8&amp;type=item&amp;tracking_id=e9f4bfe8-53e2-4bf3-90ec-22a1ec510b87&amp;price_drop=not_apply</t>
+          <t>https://terreno.mercadolibre.com.mx/MLM-4388186170-terreno-industrial-en-venta-en-toluca-san-cayetano-a-un-lado-de-la-caseta-el-dorado-cerca-puerta-mexico-recinto-aduanal-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=8&amp;type=item&amp;tracking_id=e2a21522-489e-4892-844a-18ff9381f16b&amp;price_drop=not_apply</t>
         </is>
       </c>
     </row>
@@ -6386,7 +6386,7 @@
       </c>
       <c r="D298" t="inlineStr">
         <is>
-          <t>https://terreno.mercadolibre.com.mx/MLM-2716629645-terreno-industrial-en-venta-en-palmillas-son-13-hectareas-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=9&amp;type=item&amp;tracking_id=e9f4bfe8-53e2-4bf3-90ec-22a1ec510b87&amp;price_drop=not_apply</t>
+          <t>https://terreno.mercadolibre.com.mx/MLM-2716629645-terreno-industrial-en-venta-en-palmillas-son-13-hectareas-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=9&amp;type=item&amp;tracking_id=e2a21522-489e-4892-844a-18ff9381f16b&amp;price_drop=not_apply</t>
         </is>
       </c>
     </row>
@@ -6406,7 +6406,7 @@
       </c>
       <c r="D299" t="inlineStr">
         <is>
-          <t>https://terreno.mercadolibre.com.mx/MLM-2748643873-terreno-en-venta-a-pie-de-carretera-toluca-atlacomulco-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=10&amp;type=item&amp;tracking_id=e9f4bfe8-53e2-4bf3-90ec-22a1ec510b87&amp;price_drop=not_apply</t>
+          <t>https://terreno.mercadolibre.com.mx/MLM-2748643873-terreno-en-venta-a-pie-de-carretera-toluca-atlacomulco-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=10&amp;type=item&amp;tracking_id=e2a21522-489e-4892-844a-18ff9381f16b&amp;price_drop=not_apply</t>
         </is>
       </c>
     </row>
@@ -6426,7 +6426,7 @@
       </c>
       <c r="D300" t="inlineStr">
         <is>
-          <t>https://terreno.mercadolibre.com.mx/MLM-4790479866-terreno-regular-con-infraestructura-lista-base-solida-para-tu-proyecto-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=11&amp;type=item&amp;tracking_id=e9f4bfe8-53e2-4bf3-90ec-22a1ec510b87&amp;price_drop=not_apply</t>
+          <t>https://terreno.mercadolibre.com.mx/MLM-4790479866-terreno-regular-con-infraestructura-lista-base-solida-para-tu-proyecto-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=11&amp;type=item&amp;tracking_id=e2a21522-489e-4892-844a-18ff9381f16b&amp;price_drop=not_apply</t>
         </is>
       </c>
     </row>
@@ -6446,7 +6446,7 @@
       </c>
       <c r="D301" t="inlineStr">
         <is>
-          <t>https://terreno.mercadolibre.com.mx/MLM-5015164202-venta-terreno-lotes-palmillas-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=12&amp;type=item&amp;tracking_id=e9f4bfe8-53e2-4bf3-90ec-22a1ec510b87&amp;price_drop=not_apply</t>
+          <t>https://terreno.mercadolibre.com.mx/MLM-5015164202-venta-terreno-lotes-palmillas-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=12&amp;type=item&amp;tracking_id=e2a21522-489e-4892-844a-18ff9381f16b&amp;price_drop=not_apply</t>
         </is>
       </c>
     </row>
@@ -6466,7 +6466,7 @@
       </c>
       <c r="D302" t="inlineStr">
         <is>
-          <t>https://terreno.mercadolibre.com.mx/MLM-4416680104-terreno-en-venta-sobre-calzada-del-pacifico-cacalomacan-por-ocho-cedros-toluca-cas-23000-m2-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=13&amp;type=item&amp;tracking_id=e9f4bfe8-53e2-4bf3-90ec-22a1ec510b87&amp;price_drop=not_apply</t>
+          <t>https://terreno.mercadolibre.com.mx/MLM-4416680104-terreno-en-venta-sobre-calzada-del-pacifico-cacalomacan-por-ocho-cedros-toluca-cas-23000-m2-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=13&amp;type=item&amp;tracking_id=e2a21522-489e-4892-844a-18ff9381f16b&amp;price_drop=not_apply</t>
         </is>
       </c>
     </row>
@@ -6486,7 +6486,7 @@
       </c>
       <c r="D303" t="inlineStr">
         <is>
-          <t>https://terreno.mercadolibre.com.mx/MLM-2736455271-terreno-de-2-hectareas-en-zona-urbana-santa-maria-totoltepec-estado-de-mexico-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=14&amp;type=item&amp;tracking_id=e9f4bfe8-53e2-4bf3-90ec-22a1ec510b87&amp;price_drop=not_apply</t>
+          <t>https://terreno.mercadolibre.com.mx/MLM-2736455271-terreno-de-2-hectareas-en-zona-urbana-santa-maria-totoltepec-estado-de-mexico-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=14&amp;type=item&amp;tracking_id=e2a21522-489e-4892-844a-18ff9381f16b&amp;price_drop=not_apply</t>
         </is>
       </c>
     </row>
@@ -6497,7 +6497,7 @@
         </is>
       </c>
       <c r="B304" t="n">
-        <v>1831680</v>
+        <v>299999</v>
       </c>
       <c r="C304" t="inlineStr">
         <is>
@@ -6506,7 +6506,7 @@
       </c>
       <c r="D304" t="inlineStr">
         <is>
-          <t>https://terreno.mercadolibre.com.mx/MLM-2804712255-venta-terreno-paraje-san-rafael-en-toluca-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=15&amp;type=item&amp;float_highlight=recent_publication&amp;tracking_id=e9f4bfe8-53e2-4bf3-90ec-22a1ec510b87&amp;price_drop=not_apply</t>
+          <t>https://terreno.mercadolibre.com.mx/MLM-5082958514-lotes-a-10-min-de-paideia-propiedad-desde-230-m-en-adelante-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=15&amp;type=item&amp;float_highlight=recent_publication&amp;tracking_id=e2a21522-489e-4892-844a-18ff9381f16b&amp;price_drop=not_apply</t>
         </is>
       </c>
     </row>
@@ -6517,7 +6517,7 @@
         </is>
       </c>
       <c r="B305" t="n">
-        <v>1485000</v>
+        <v>1831680</v>
       </c>
       <c r="C305" t="inlineStr">
         <is>
@@ -6526,7 +6526,7 @@
       </c>
       <c r="D305" t="inlineStr">
         <is>
-          <t>https://terreno.mercadolibre.com.mx/MLM-2187928841-venta-terreno-cerrillo-vista-hermosa-toluca-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=16&amp;type=item&amp;tracking_id=e9f4bfe8-53e2-4bf3-90ec-22a1ec510b87&amp;price_drop=not_apply</t>
+          <t>https://terreno.mercadolibre.com.mx/MLM-2804712255-venta-terreno-paraje-san-rafael-en-toluca-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=16&amp;type=item&amp;float_highlight=recent_publication&amp;tracking_id=e2a21522-489e-4892-844a-18ff9381f16b&amp;price_drop=not_apply</t>
         </is>
       </c>
     </row>
@@ -6537,7 +6537,7 @@
         </is>
       </c>
       <c r="B306" t="n">
-        <v>4805040</v>
+        <v>1485000</v>
       </c>
       <c r="C306" t="inlineStr">
         <is>
@@ -6546,7 +6546,7 @@
       </c>
       <c r="D306" t="inlineStr">
         <is>
-          <t>https://terreno.mercadolibre.com.mx/MLM-3705026808-venta-de-terreno-en-cacalomacan-a-20-min-centro-toluca-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=17&amp;type=item&amp;tracking_id=e9f4bfe8-53e2-4bf3-90ec-22a1ec510b87&amp;price_drop=not_apply</t>
+          <t>https://terreno.mercadolibre.com.mx/MLM-2187928841-venta-terreno-cerrillo-vista-hermosa-toluca-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=17&amp;type=item&amp;tracking_id=e2a21522-489e-4892-844a-18ff9381f16b&amp;price_drop=not_apply</t>
         </is>
       </c>
     </row>
@@ -6557,7 +6557,7 @@
         </is>
       </c>
       <c r="B307" t="n">
-        <v>1920000</v>
+        <v>4805040</v>
       </c>
       <c r="C307" t="inlineStr">
         <is>
@@ -6566,7 +6566,7 @@
       </c>
       <c r="D307" t="inlineStr">
         <is>
-          <t>https://terreno.mercadolibre.com.mx/MLM-4119789692-terreno-en-venta-residencial-ex-hacienda-san-jose-toluca-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=18&amp;type=item&amp;tracking_id=e9f4bfe8-53e2-4bf3-90ec-22a1ec510b87&amp;price_drop=not_apply</t>
+          <t>https://terreno.mercadolibre.com.mx/MLM-3705026808-venta-de-terreno-en-cacalomacan-a-20-min-centro-toluca-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=18&amp;type=item&amp;tracking_id=e2a21522-489e-4892-844a-18ff9381f16b&amp;price_drop=not_apply</t>
         </is>
       </c>
     </row>
@@ -6577,7 +6577,7 @@
         </is>
       </c>
       <c r="B308" t="n">
-        <v>1244380</v>
+        <v>1920000</v>
       </c>
       <c r="C308" t="inlineStr">
         <is>
@@ -6586,7 +6586,7 @@
       </c>
       <c r="D308" t="inlineStr">
         <is>
-          <t>https://terreno.mercadolibre.com.mx/MLM-4826508826-venta-de-lote-de-terreno-residencial-cerca-de-galerias-metepec-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=19&amp;type=item&amp;tracking_id=e9f4bfe8-53e2-4bf3-90ec-22a1ec510b87&amp;price_drop=not_apply</t>
+          <t>https://terreno.mercadolibre.com.mx/MLM-4119789692-terreno-en-venta-residencial-ex-hacienda-san-jose-toluca-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=19&amp;type=item&amp;tracking_id=e2a21522-489e-4892-844a-18ff9381f16b&amp;price_drop=not_apply</t>
         </is>
       </c>
     </row>
@@ -6597,7 +6597,7 @@
         </is>
       </c>
       <c r="B309" t="n">
-        <v>8565858</v>
+        <v>1244380</v>
       </c>
       <c r="C309" t="inlineStr">
         <is>
@@ -6606,7 +6606,7 @@
       </c>
       <c r="D309" t="inlineStr">
         <is>
-          <t>https://terreno.mercadolibre.com.mx/MLM-4080298834-terreno-en-venta-en-san-miguel-zacango-toluca-mexico-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=20&amp;type=item&amp;tracking_id=e9f4bfe8-53e2-4bf3-90ec-22a1ec510b87&amp;price_drop=not_apply</t>
+          <t>https://terreno.mercadolibre.com.mx/MLM-4826508826-venta-de-lote-de-terreno-residencial-cerca-de-galerias-metepec-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=20&amp;type=item&amp;tracking_id=e2a21522-489e-4892-844a-18ff9381f16b&amp;price_drop=not_apply</t>
         </is>
       </c>
     </row>
@@ -6617,7 +6617,7 @@
         </is>
       </c>
       <c r="B310" t="n">
-        <v>8500000</v>
+        <v>8565858</v>
       </c>
       <c r="C310" t="inlineStr">
         <is>
@@ -6626,7 +6626,7 @@
       </c>
       <c r="D310" t="inlineStr">
         <is>
-          <t>https://terreno.mercadolibre.com.mx/MLM-2310439697-se-vende-terreno-en-toluca-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=21&amp;type=item&amp;tracking_id=e9f4bfe8-53e2-4bf3-90ec-22a1ec510b87&amp;price_drop=not_apply</t>
+          <t>https://terreno.mercadolibre.com.mx/MLM-4080298834-terreno-en-venta-en-san-miguel-zacango-toluca-mexico-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=21&amp;type=item&amp;tracking_id=e2a21522-489e-4892-844a-18ff9381f16b&amp;price_drop=not_apply</t>
         </is>
       </c>
     </row>
@@ -6637,7 +6637,7 @@
         </is>
       </c>
       <c r="B311" t="n">
-        <v>1300000</v>
+        <v>8500000</v>
       </c>
       <c r="C311" t="inlineStr">
         <is>
@@ -6646,7 +6646,7 @@
       </c>
       <c r="D311" t="inlineStr">
         <is>
-          <t>https://terreno.mercadolibre.com.mx/MLM-4495237624-lote-disponible-en-conjunto-ambar-toluca-edo-mex-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=22&amp;type=item&amp;tracking_id=e9f4bfe8-53e2-4bf3-90ec-22a1ec510b87&amp;price_drop=not_apply</t>
+          <t>https://terreno.mercadolibre.com.mx/MLM-2310439697-se-vende-terreno-en-toluca-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=22&amp;type=item&amp;tracking_id=e2a21522-489e-4892-844a-18ff9381f16b&amp;price_drop=not_apply</t>
         </is>
       </c>
     </row>
@@ -6657,7 +6657,7 @@
         </is>
       </c>
       <c r="B312" t="n">
-        <v>1200000</v>
+        <v>1300000</v>
       </c>
       <c r="C312" t="inlineStr">
         <is>
@@ -6666,7 +6666,7 @@
       </c>
       <c r="D312" t="inlineStr">
         <is>
-          <t>https://terreno.mercadolibre.com.mx/MLM-2485559517-terreno-en-venta-en-toluca-san-andres-cuexcontitlan-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=23&amp;type=item&amp;tracking_id=e9f4bfe8-53e2-4bf3-90ec-22a1ec510b87&amp;price_drop=not_apply</t>
+          <t>https://terreno.mercadolibre.com.mx/MLM-4495237624-lote-disponible-en-conjunto-ambar-toluca-edo-mex-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=23&amp;type=item&amp;tracking_id=e2a21522-489e-4892-844a-18ff9381f16b&amp;price_drop=not_apply</t>
         </is>
       </c>
     </row>
@@ -6677,7 +6677,7 @@
         </is>
       </c>
       <c r="B313" t="n">
-        <v>38634000</v>
+        <v>1200000</v>
       </c>
       <c r="C313" t="inlineStr">
         <is>
@@ -6686,7 +6686,7 @@
       </c>
       <c r="D313" t="inlineStr">
         <is>
-          <t>https://terreno.mercadolibre.com.mx/MLM-2431684449-terreno-en-toluca-25756-m2-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=24&amp;type=item&amp;tracking_id=e9f4bfe8-53e2-4bf3-90ec-22a1ec510b87&amp;price_drop=not_apply</t>
+          <t>https://terreno.mercadolibre.com.mx/MLM-2485559517-terreno-en-venta-en-toluca-san-andres-cuexcontitlan-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=24&amp;type=item&amp;tracking_id=e2a21522-489e-4892-844a-18ff9381f16b&amp;price_drop=not_apply</t>
         </is>
       </c>
     </row>
@@ -6697,7 +6697,7 @@
         </is>
       </c>
       <c r="B314" t="n">
-        <v>5625000</v>
+        <v>38634000</v>
       </c>
       <c r="C314" t="inlineStr">
         <is>
@@ -6706,7 +6706,7 @@
       </c>
       <c r="D314" t="inlineStr">
         <is>
-          <t>https://terreno.mercadolibre.com.mx/MLM-2323267483-terreno-en-venta-2250m2-en-san-felipe-tlalmimilolpan-toluca-mexico-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=25&amp;type=item&amp;tracking_id=e9f4bfe8-53e2-4bf3-90ec-22a1ec510b87&amp;price_drop=not_apply</t>
+          <t>https://terreno.mercadolibre.com.mx/MLM-2431684449-terreno-en-toluca-25756-m2-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=25&amp;type=item&amp;tracking_id=e2a21522-489e-4892-844a-18ff9381f16b&amp;price_drop=not_apply</t>
         </is>
       </c>
     </row>
@@ -6717,7 +6717,7 @@
         </is>
       </c>
       <c r="B315" t="n">
-        <v>25650000</v>
+        <v>5625000</v>
       </c>
       <c r="C315" t="inlineStr">
         <is>
@@ -6726,7 +6726,7 @@
       </c>
       <c r="D315" t="inlineStr">
         <is>
-          <t>https://terreno.mercadolibre.com.mx/MLM-4169951646-terreno-en-venta-por-las-torres-toluca-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=26&amp;type=item&amp;tracking_id=e9f4bfe8-53e2-4bf3-90ec-22a1ec510b87&amp;price_drop=not_apply</t>
+          <t>https://terreno.mercadolibre.com.mx/MLM-2323267483-terreno-en-venta-2250m2-en-san-felipe-tlalmimilolpan-toluca-mexico-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=26&amp;type=item&amp;tracking_id=e2a21522-489e-4892-844a-18ff9381f16b&amp;price_drop=not_apply</t>
         </is>
       </c>
     </row>
@@ -6737,7 +6737,7 @@
         </is>
       </c>
       <c r="B316" t="n">
-        <v>4800000</v>
+        <v>25650000</v>
       </c>
       <c r="C316" t="inlineStr">
         <is>
@@ -6746,7 +6746,7 @@
       </c>
       <c r="D316" t="inlineStr">
         <is>
-          <t>https://terreno.mercadolibre.com.mx/MLM-4416373342-terreno-en-venta-en-san-lorenzo-tepaltitlan-centro-toluca-mexico-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=27&amp;type=item&amp;tracking_id=e9f4bfe8-53e2-4bf3-90ec-22a1ec510b87&amp;price_drop=not_apply</t>
+          <t>https://terreno.mercadolibre.com.mx/MLM-4169951646-terreno-en-venta-por-las-torres-toluca-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=27&amp;type=item&amp;tracking_id=e2a21522-489e-4892-844a-18ff9381f16b&amp;price_drop=not_apply</t>
         </is>
       </c>
     </row>
@@ -6757,7 +6757,7 @@
         </is>
       </c>
       <c r="B317" t="n">
-        <v>14490000</v>
+        <v>4800000</v>
       </c>
       <c r="C317" t="inlineStr">
         <is>
@@ -6766,7 +6766,7 @@
       </c>
       <c r="D317" t="inlineStr">
         <is>
-          <t>https://terreno.mercadolibre.com.mx/MLM-2584697469-oportunidad-de-inversion-terreno-de-9993-m-cerca-de-parque-toluca-2000-ideal-para-naves-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=28&amp;type=item&amp;tracking_id=e9f4bfe8-53e2-4bf3-90ec-22a1ec510b87&amp;price_drop=not_apply</t>
+          <t>https://terreno.mercadolibre.com.mx/MLM-4416373342-terreno-en-venta-en-san-lorenzo-tepaltitlan-centro-toluca-mexico-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=28&amp;type=item&amp;tracking_id=e2a21522-489e-4892-844a-18ff9381f16b&amp;price_drop=not_apply</t>
         </is>
       </c>
     </row>
@@ -6777,7 +6777,7 @@
         </is>
       </c>
       <c r="B318" t="n">
-        <v>24520000</v>
+        <v>14490000</v>
       </c>
       <c r="C318" t="inlineStr">
         <is>
@@ -6786,7 +6786,7 @@
       </c>
       <c r="D318" t="inlineStr">
         <is>
-          <t>https://terreno.mercadolibre.com.mx/MLM-4169951774-terreno-en-venta-por-las-torres-toluca-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=29&amp;type=item&amp;tracking_id=e9f4bfe8-53e2-4bf3-90ec-22a1ec510b87&amp;price_drop=not_apply</t>
+          <t>https://terreno.mercadolibre.com.mx/MLM-2584697469-oportunidad-de-inversion-terreno-de-9993-m-cerca-de-parque-toluca-2000-ideal-para-naves-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=29&amp;type=item&amp;tracking_id=e2a21522-489e-4892-844a-18ff9381f16b&amp;price_drop=not_apply</t>
         </is>
       </c>
     </row>
@@ -6797,7 +6797,7 @@
         </is>
       </c>
       <c r="B319" t="n">
-        <v>12024000</v>
+        <v>24520000</v>
       </c>
       <c r="C319" t="inlineStr">
         <is>
@@ -6806,7 +6806,7 @@
       </c>
       <c r="D319" t="inlineStr">
         <is>
-          <t>https://terreno.mercadolibre.com.mx/MLM-2323192153-terreno-en-venta-8016-m2-en-san-felipe-tlalmimilolpan-toluca-mexico-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=30&amp;type=item&amp;tracking_id=e9f4bfe8-53e2-4bf3-90ec-22a1ec510b87&amp;price_drop=not_apply</t>
+          <t>https://terreno.mercadolibre.com.mx/MLM-4169951774-terreno-en-venta-por-las-torres-toluca-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=30&amp;type=item&amp;tracking_id=e2a21522-489e-4892-844a-18ff9381f16b&amp;price_drop=not_apply</t>
         </is>
       </c>
     </row>
@@ -6817,7 +6817,7 @@
         </is>
       </c>
       <c r="B320" t="n">
-        <v>13650000</v>
+        <v>12024000</v>
       </c>
       <c r="C320" t="inlineStr">
         <is>
@@ -6826,7 +6826,7 @@
       </c>
       <c r="D320" t="inlineStr">
         <is>
-          <t>https://terreno.mercadolibre.com.mx/MLM-2487732477-terreno-en-venta-por-las-torres-toluca-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=31&amp;type=item&amp;tracking_id=e9f4bfe8-53e2-4bf3-90ec-22a1ec510b87&amp;price_drop=not_apply</t>
+          <t>https://terreno.mercadolibre.com.mx/MLM-2323192153-terreno-en-venta-8016-m2-en-san-felipe-tlalmimilolpan-toluca-mexico-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=31&amp;type=item&amp;tracking_id=e2a21522-489e-4892-844a-18ff9381f16b&amp;price_drop=not_apply</t>
         </is>
       </c>
     </row>
@@ -6837,7 +6837,7 @@
         </is>
       </c>
       <c r="B321" t="n">
-        <v>4725000</v>
+        <v>13650000</v>
       </c>
       <c r="C321" t="inlineStr">
         <is>
@@ -6846,7 +6846,7 @@
       </c>
       <c r="D321" t="inlineStr">
         <is>
-          <t>https://terreno.mercadolibre.com.mx/MLM-2318168399-terreno-en-venta-en-cacalomacan-a-2-cuadras-de-jinetes-cerca-de-calz-pacifico-y-colegio-paideia-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=32&amp;type=item&amp;tracking_id=e9f4bfe8-53e2-4bf3-90ec-22a1ec510b87&amp;price_drop=not_apply</t>
+          <t>https://terreno.mercadolibre.com.mx/MLM-2487732477-terreno-en-venta-por-las-torres-toluca-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=32&amp;type=item&amp;tracking_id=e2a21522-489e-4892-844a-18ff9381f16b&amp;price_drop=not_apply</t>
         </is>
       </c>
     </row>
@@ -6857,7 +6857,7 @@
         </is>
       </c>
       <c r="B322" t="n">
-        <v>11500000</v>
+        <v>4725000</v>
       </c>
       <c r="C322" t="inlineStr">
         <is>
@@ -6866,7 +6866,7 @@
       </c>
       <c r="D322" t="inlineStr">
         <is>
-          <t>https://terreno.mercadolibre.com.mx/MLM-4080259510-terreno-en-venta-en-san-martin-toltepec-toluca-mexico-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=33&amp;type=item&amp;tracking_id=e9f4bfe8-53e2-4bf3-90ec-22a1ec510b87&amp;price_drop=not_apply</t>
+          <t>https://terreno.mercadolibre.com.mx/MLM-2318168399-terreno-en-venta-en-cacalomacan-a-2-cuadras-de-jinetes-cerca-de-calz-pacifico-y-colegio-paideia-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=33&amp;type=item&amp;tracking_id=e2a21522-489e-4892-844a-18ff9381f16b&amp;price_drop=not_apply</t>
         </is>
       </c>
     </row>
@@ -6877,7 +6877,7 @@
         </is>
       </c>
       <c r="B323" t="n">
-        <v>1840590</v>
+        <v>11500000</v>
       </c>
       <c r="C323" t="inlineStr">
         <is>
@@ -6886,7 +6886,7 @@
       </c>
       <c r="D323" t="inlineStr">
         <is>
-          <t>https://terreno.mercadolibre.com.mx/MLM-4080239968-terreno-en-venta-toluca-cerca-del-aeropuerto-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=34&amp;type=item&amp;tracking_id=e9f4bfe8-53e2-4bf3-90ec-22a1ec510b87&amp;price_drop=not_apply</t>
+          <t>https://terreno.mercadolibre.com.mx/MLM-4080259510-terreno-en-venta-en-san-martin-toltepec-toluca-mexico-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=34&amp;type=item&amp;tracking_id=e2a21522-489e-4892-844a-18ff9381f16b&amp;price_drop=not_apply</t>
         </is>
       </c>
     </row>
@@ -6897,7 +6897,7 @@
         </is>
       </c>
       <c r="B324" t="n">
-        <v>8500000</v>
+        <v>1840590</v>
       </c>
       <c r="C324" t="inlineStr">
         <is>
@@ -6906,7 +6906,7 @@
       </c>
       <c r="D324" t="inlineStr">
         <is>
-          <t>https://terreno.mercadolibre.com.mx/MLM-2343423083-terreno-en-san-pedro-totoltepec-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=35&amp;type=item&amp;tracking_id=e9f4bfe8-53e2-4bf3-90ec-22a1ec510b87&amp;price_drop=not_apply</t>
+          <t>https://terreno.mercadolibre.com.mx/MLM-4080239968-terreno-en-venta-toluca-cerca-del-aeropuerto-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=35&amp;type=item&amp;tracking_id=e2a21522-489e-4892-844a-18ff9381f16b&amp;price_drop=not_apply</t>
         </is>
       </c>
     </row>
@@ -6917,7 +6917,7 @@
         </is>
       </c>
       <c r="B325" t="n">
-        <v>35000000</v>
+        <v>8500000</v>
       </c>
       <c r="C325" t="inlineStr">
         <is>
@@ -6926,7 +6926,7 @@
       </c>
       <c r="D325" t="inlineStr">
         <is>
-          <t>https://terreno.mercadolibre.com.mx/MLM-2370231281-terreno-en-venta-en-toluca-reforma-y-ferr-nac-independencia-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=36&amp;type=item&amp;tracking_id=e9f4bfe8-53e2-4bf3-90ec-22a1ec510b87&amp;price_drop=not_apply</t>
+          <t>https://terreno.mercadolibre.com.mx/MLM-2343423083-terreno-en-san-pedro-totoltepec-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=36&amp;type=item&amp;tracking_id=e2a21522-489e-4892-844a-18ff9381f16b&amp;price_drop=not_apply</t>
         </is>
       </c>
     </row>
@@ -6937,7 +6937,7 @@
         </is>
       </c>
       <c r="B326" t="n">
-        <v>2450000</v>
+        <v>35000000</v>
       </c>
       <c r="C326" t="inlineStr">
         <is>
@@ -6946,7 +6946,7 @@
       </c>
       <c r="D326" t="inlineStr">
         <is>
-          <t>https://terreno.mercadolibre.com.mx/MLM-2343569515-terreno-en-santa-maria-totoltepec-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=37&amp;type=item&amp;tracking_id=e9f4bfe8-53e2-4bf3-90ec-22a1ec510b87&amp;price_drop=not_apply</t>
+          <t>https://terreno.mercadolibre.com.mx/MLM-2370231281-terreno-en-venta-en-toluca-reforma-y-ferr-nac-independencia-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=37&amp;type=item&amp;tracking_id=e2a21522-489e-4892-844a-18ff9381f16b&amp;price_drop=not_apply</t>
         </is>
       </c>
     </row>
@@ -6957,7 +6957,7 @@
         </is>
       </c>
       <c r="B327" t="n">
-        <v>50000000</v>
+        <v>2450000</v>
       </c>
       <c r="C327" t="inlineStr">
         <is>
@@ -6966,7 +6966,7 @@
       </c>
       <c r="D327" t="inlineStr">
         <is>
-          <t>https://terreno.mercadolibre.com.mx/MLM-4558160588-terreno-en-venta-en-cipres-toluca-estado-de-mexico-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=38&amp;type=item&amp;tracking_id=e9f4bfe8-53e2-4bf3-90ec-22a1ec510b87&amp;price_drop=not_apply</t>
+          <t>https://terreno.mercadolibre.com.mx/MLM-2343569515-terreno-en-santa-maria-totoltepec-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=38&amp;type=item&amp;tracking_id=e2a21522-489e-4892-844a-18ff9381f16b&amp;price_drop=not_apply</t>
         </is>
       </c>
     </row>
@@ -6977,7 +6977,7 @@
         </is>
       </c>
       <c r="B328" t="n">
-        <v>203547204</v>
+        <v>50000000</v>
       </c>
       <c r="C328" t="inlineStr">
         <is>
@@ -6986,7 +6986,7 @@
       </c>
       <c r="D328" t="inlineStr">
         <is>
-          <t>https://terreno.mercadolibre.com.mx/MLM-4261794654-terreno-en-venta-en-industrial-en-toluca-estado-de-mexico-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=39&amp;type=item&amp;tracking_id=e9f4bfe8-53e2-4bf3-90ec-22a1ec510b87&amp;price_drop=not_apply</t>
+          <t>https://terreno.mercadolibre.com.mx/MLM-4558160588-terreno-en-venta-en-cipres-toluca-estado-de-mexico-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=39&amp;type=item&amp;tracking_id=e2a21522-489e-4892-844a-18ff9381f16b&amp;price_drop=not_apply</t>
         </is>
       </c>
     </row>
@@ -6997,7 +6997,7 @@
         </is>
       </c>
       <c r="B329" t="n">
-        <v>14571000</v>
+        <v>203547204</v>
       </c>
       <c r="C329" t="inlineStr">
         <is>
@@ -7006,7 +7006,7 @@
       </c>
       <c r="D329" t="inlineStr">
         <is>
-          <t>https://terreno.mercadolibre.com.mx/MLM-4261807760-se-vende-terreno-carretera-mexico-toluca-lerma-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=40&amp;type=item&amp;tracking_id=e9f4bfe8-53e2-4bf3-90ec-22a1ec510b87&amp;price_drop=not_apply</t>
+          <t>https://terreno.mercadolibre.com.mx/MLM-4261794654-terreno-en-venta-en-industrial-en-toluca-estado-de-mexico-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=40&amp;type=item&amp;tracking_id=e2a21522-489e-4892-844a-18ff9381f16b&amp;price_drop=not_apply</t>
         </is>
       </c>
     </row>
@@ -7017,7 +7017,7 @@
         </is>
       </c>
       <c r="B330" t="n">
-        <v>222618909</v>
+        <v>14571000</v>
       </c>
       <c r="C330" t="inlineStr">
         <is>
@@ -7026,7 +7026,7 @@
       </c>
       <c r="D330" t="inlineStr">
         <is>
-          <t>https://terreno.mercadolibre.com.mx/MLM-4261859654-terreno-en-venta-industrial-en-toluca-estado-de-mexico-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=41&amp;type=item&amp;tracking_id=e9f4bfe8-53e2-4bf3-90ec-22a1ec510b87&amp;price_drop=not_apply</t>
+          <t>https://terreno.mercadolibre.com.mx/MLM-4261807760-se-vende-terreno-carretera-mexico-toluca-lerma-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=41&amp;type=item&amp;tracking_id=e2a21522-489e-4892-844a-18ff9381f16b&amp;price_drop=not_apply</t>
         </is>
       </c>
     </row>
@@ -7037,7 +7037,7 @@
         </is>
       </c>
       <c r="B331" t="n">
-        <v>1870000</v>
+        <v>222618909</v>
       </c>
       <c r="C331" t="inlineStr">
         <is>
@@ -7046,7 +7046,7 @@
       </c>
       <c r="D331" t="inlineStr">
         <is>
-          <t>https://terreno.mercadolibre.com.mx/MLM-2811993671-terreno-en-venta-en-residencial-hacienda-san-jose-en-toluca-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=42&amp;type=item&amp;float_highlight=recent_publication&amp;tracking_id=e9f4bfe8-53e2-4bf3-90ec-22a1ec510b87&amp;price_drop=not_apply</t>
+          <t>https://terreno.mercadolibre.com.mx/MLM-4261859654-terreno-en-venta-industrial-en-toluca-estado-de-mexico-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=42&amp;type=item&amp;tracking_id=e2a21522-489e-4892-844a-18ff9381f16b&amp;price_drop=not_apply</t>
         </is>
       </c>
     </row>
@@ -7057,7 +7057,7 @@
         </is>
       </c>
       <c r="B332" t="n">
-        <v>700000</v>
+        <v>1870000</v>
       </c>
       <c r="C332" t="inlineStr">
         <is>
@@ -7066,7 +7066,7 @@
       </c>
       <c r="D332" t="inlineStr">
         <is>
-          <t>https://terreno.mercadolibre.com.mx/MLM-5058024988-terreno-en-venta-en-san-lorenzo-tepaltitlan-toluca-estado-de-mexico-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=43&amp;type=item&amp;float_highlight=recent_publication&amp;tracking_id=e9f4bfe8-53e2-4bf3-90ec-22a1ec510b87&amp;price_drop=not_apply</t>
+          <t>https://terreno.mercadolibre.com.mx/MLM-2811993671-terreno-en-venta-en-residencial-hacienda-san-jose-en-toluca-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=43&amp;type=item&amp;float_highlight=recent_publication&amp;tracking_id=e2a21522-489e-4892-844a-18ff9381f16b&amp;price_drop=not_apply</t>
         </is>
       </c>
     </row>
@@ -7077,7 +7077,7 @@
         </is>
       </c>
       <c r="B333" t="n">
-        <v>3240000</v>
+        <v>132000000</v>
       </c>
       <c r="C333" t="inlineStr">
         <is>
@@ -7086,7 +7086,7 @@
       </c>
       <c r="D333" t="inlineStr">
         <is>
-          <t>https://terreno.mercadolibre.com.mx/MLM-5058177406-terreno-en-venta-en-san-francisco-totoltepec-toluca-estado-de-mexico-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=44&amp;type=item&amp;float_highlight=recent_publication&amp;tracking_id=e9f4bfe8-53e2-4bf3-90ec-22a1ec510b87&amp;price_drop=not_apply</t>
+          <t>https://terreno.mercadolibre.com.mx/MLM-5064030156-terreno-en-venta-en-parque-industrial-el-coecillo-toluca-estado-de-mexico-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=44&amp;type=item&amp;float_highlight=recent_publication&amp;tracking_id=e2a21522-489e-4892-844a-18ff9381f16b&amp;price_drop=not_apply</t>
         </is>
       </c>
     </row>
@@ -7097,7 +7097,7 @@
         </is>
       </c>
       <c r="B334" t="n">
-        <v>132000000</v>
+        <v>279450</v>
       </c>
       <c r="C334" t="inlineStr">
         <is>
@@ -7106,7 +7106,7 @@
       </c>
       <c r="D334" t="inlineStr">
         <is>
-          <t>https://terreno.mercadolibre.com.mx/MLM-5064030156-terreno-en-venta-en-parque-industrial-el-coecillo-toluca-estado-de-mexico-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=45&amp;type=item&amp;float_highlight=recent_publication&amp;tracking_id=e9f4bfe8-53e2-4bf3-90ec-22a1ec510b87&amp;price_drop=not_apply</t>
+          <t>https://terreno.mercadolibre.com.mx/MLM-5060346586-ultimos-2-lotes-en-venta-en-san-cayetano-muy-cerca-de-la-unsa-en-toluca-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=45&amp;type=item&amp;float_highlight=recent_publication&amp;tracking_id=e2a21522-489e-4892-844a-18ff9381f16b&amp;price_drop=not_apply</t>
         </is>
       </c>
     </row>
@@ -7117,7 +7117,7 @@
         </is>
       </c>
       <c r="B335" t="n">
-        <v>279450</v>
+        <v>23500000</v>
       </c>
       <c r="C335" t="inlineStr">
         <is>
@@ -7126,7 +7126,7 @@
       </c>
       <c r="D335" t="inlineStr">
         <is>
-          <t>https://terreno.mercadolibre.com.mx/MLM-5060346586-ultimos-2-lotes-en-venta-en-san-cayetano-muy-cerca-de-la-unsa-en-toluca-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=46&amp;type=item&amp;float_highlight=recent_publication&amp;tracking_id=e9f4bfe8-53e2-4bf3-90ec-22a1ec510b87&amp;price_drop=not_apply</t>
+          <t>https://terreno.mercadolibre.com.mx/MLM-4950598656-terreno-comercial-en-venta-en-san-bernardino-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=46&amp;type=item&amp;tracking_id=e2a21522-489e-4892-844a-18ff9381f16b&amp;price_drop=not_apply</t>
         </is>
       </c>
     </row>
@@ -7137,7 +7137,7 @@
         </is>
       </c>
       <c r="B336" t="n">
-        <v>9215400</v>
+        <v>8760000</v>
       </c>
       <c r="C336" t="inlineStr">
         <is>
@@ -7146,7 +7146,7 @@
       </c>
       <c r="D336" t="inlineStr">
         <is>
-          <t>https://terreno.mercadolibre.com.mx/MLM-5047581202-terreno-comercial-en-venta-en-santa-cruz-otzacatipan-toluca-mexico-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=47&amp;type=item&amp;float_highlight=recent_publication&amp;tracking_id=e9f4bfe8-53e2-4bf3-90ec-22a1ec510b87&amp;price_drop=not_apply</t>
+          <t>https://terreno.mercadolibre.com.mx/MLM-4761562052-terreno-comercial-en-venta-en-santa-maria-totoltepec-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=47&amp;type=item&amp;tracking_id=e2a21522-489e-4892-844a-18ff9381f16b&amp;price_drop=not_apply</t>
         </is>
       </c>
     </row>
@@ -7157,7 +7157,7 @@
         </is>
       </c>
       <c r="B337" t="n">
-        <v>8502990</v>
+        <v>26320000</v>
       </c>
       <c r="C337" t="inlineStr">
         <is>
@@ -7166,7 +7166,7 @@
       </c>
       <c r="D337" t="inlineStr">
         <is>
-          <t>https://terreno.mercadolibre.com.mx/MLM-5047581198-terreno-comercial-en-venta-en-santa-cruz-otzacatipan-toluca-mexico-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=48&amp;type=item&amp;float_highlight=recent_publication&amp;tracking_id=e9f4bfe8-53e2-4bf3-90ec-22a1ec510b87&amp;price_drop=not_apply</t>
+          <t>https://terreno.mercadolibre.com.mx/MLM-4790443980-terreno-residencial-en-venta-en-la-venta-_JM#polycard_client=search-desktop&amp;search_layout=grid&amp;position=48&amp;type=item&amp;tracking_id=e2a21522-489e-4892-844a-18ff9381f16b&amp;price_drop=not_apply</t>
         </is>
       </c>
     </row>
